--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://meximp-my.sharepoint.com/personal/gbdiaz_imp_mx/Documents/Cursos/2026/Python basico posgrado/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Intro-python-cientifico-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="13_ncr:1_{539849CE-FA67-44F5-97FB-0AD98FD5AE4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65F44366-66F2-498C-96B5-D49C04D45655}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F14846A0-69D2-4CBA-80F8-80BEDF5601E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CE0BC579-6CE5-40D7-ACC9-BFD6CA7E6FB4}"/>
+    <workbookView xWindow="3150" yWindow="6060" windowWidth="26310" windowHeight="13785" xr2:uid="{CE0BC579-6CE5-40D7-ACC9-BFD6CA7E6FB4}"/>
   </bookViews>
   <sheets>
     <sheet name="ACTA CALIFICACIONES" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="62">
   <si>
     <t>ACTA DE CALIFICACIONES</t>
   </si>
@@ -250,6 +250,12 @@
   </si>
   <si>
     <t>E_total</t>
+  </si>
+  <si>
+    <t>ESPINOSA CUELLAR JOSE SAMUEL</t>
+  </si>
+  <si>
+    <t>HERNANDEZ JOSUE ANDRADE</t>
   </si>
 </sst>
 </file>
@@ -601,9 +607,72 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -616,71 +685,38 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -692,54 +728,24 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1016,7 +1022,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -1315,677 +1321,677 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AL32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AL34"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="2" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" style="2" customWidth="1"/>
-    <col min="3" max="7" width="4.88671875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="14.109375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="7.44140625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="6.5546875" style="2" customWidth="1"/>
-    <col min="11" max="23" width="6.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" style="2" customWidth="1"/>
+    <col min="3" max="7" width="4.85546875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="7.42578125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="6.5703125" style="2" customWidth="1"/>
+    <col min="11" max="23" width="6.42578125" style="2" customWidth="1"/>
     <col min="24" max="24" width="24" style="2" customWidth="1"/>
-    <col min="25" max="271" width="10.88671875" style="2"/>
-    <col min="272" max="272" width="5.88671875" style="2" customWidth="1"/>
-    <col min="273" max="273" width="13.33203125" style="2" customWidth="1"/>
-    <col min="274" max="274" width="4.88671875" style="2" customWidth="1"/>
-    <col min="275" max="275" width="33.109375" style="2" customWidth="1"/>
-    <col min="276" max="276" width="8.109375" style="2" customWidth="1"/>
-    <col min="277" max="277" width="6.88671875" style="2" customWidth="1"/>
-    <col min="278" max="278" width="14.33203125" style="2" customWidth="1"/>
-    <col min="279" max="279" width="18.88671875" style="2" customWidth="1"/>
-    <col min="280" max="280" width="13.109375" style="2" customWidth="1"/>
-    <col min="281" max="527" width="10.88671875" style="2"/>
-    <col min="528" max="528" width="5.88671875" style="2" customWidth="1"/>
-    <col min="529" max="529" width="13.33203125" style="2" customWidth="1"/>
-    <col min="530" max="530" width="4.88671875" style="2" customWidth="1"/>
-    <col min="531" max="531" width="33.109375" style="2" customWidth="1"/>
-    <col min="532" max="532" width="8.109375" style="2" customWidth="1"/>
-    <col min="533" max="533" width="6.88671875" style="2" customWidth="1"/>
-    <col min="534" max="534" width="14.33203125" style="2" customWidth="1"/>
-    <col min="535" max="535" width="18.88671875" style="2" customWidth="1"/>
-    <col min="536" max="536" width="13.109375" style="2" customWidth="1"/>
-    <col min="537" max="783" width="10.88671875" style="2"/>
-    <col min="784" max="784" width="5.88671875" style="2" customWidth="1"/>
-    <col min="785" max="785" width="13.33203125" style="2" customWidth="1"/>
-    <col min="786" max="786" width="4.88671875" style="2" customWidth="1"/>
-    <col min="787" max="787" width="33.109375" style="2" customWidth="1"/>
-    <col min="788" max="788" width="8.109375" style="2" customWidth="1"/>
-    <col min="789" max="789" width="6.88671875" style="2" customWidth="1"/>
-    <col min="790" max="790" width="14.33203125" style="2" customWidth="1"/>
-    <col min="791" max="791" width="18.88671875" style="2" customWidth="1"/>
-    <col min="792" max="792" width="13.109375" style="2" customWidth="1"/>
-    <col min="793" max="1039" width="10.88671875" style="2"/>
-    <col min="1040" max="1040" width="5.88671875" style="2" customWidth="1"/>
-    <col min="1041" max="1041" width="13.33203125" style="2" customWidth="1"/>
-    <col min="1042" max="1042" width="4.88671875" style="2" customWidth="1"/>
-    <col min="1043" max="1043" width="33.109375" style="2" customWidth="1"/>
-    <col min="1044" max="1044" width="8.109375" style="2" customWidth="1"/>
-    <col min="1045" max="1045" width="6.88671875" style="2" customWidth="1"/>
-    <col min="1046" max="1046" width="14.33203125" style="2" customWidth="1"/>
-    <col min="1047" max="1047" width="18.88671875" style="2" customWidth="1"/>
-    <col min="1048" max="1048" width="13.109375" style="2" customWidth="1"/>
-    <col min="1049" max="1295" width="10.88671875" style="2"/>
-    <col min="1296" max="1296" width="5.88671875" style="2" customWidth="1"/>
-    <col min="1297" max="1297" width="13.33203125" style="2" customWidth="1"/>
-    <col min="1298" max="1298" width="4.88671875" style="2" customWidth="1"/>
-    <col min="1299" max="1299" width="33.109375" style="2" customWidth="1"/>
-    <col min="1300" max="1300" width="8.109375" style="2" customWidth="1"/>
-    <col min="1301" max="1301" width="6.88671875" style="2" customWidth="1"/>
-    <col min="1302" max="1302" width="14.33203125" style="2" customWidth="1"/>
-    <col min="1303" max="1303" width="18.88671875" style="2" customWidth="1"/>
-    <col min="1304" max="1304" width="13.109375" style="2" customWidth="1"/>
-    <col min="1305" max="1551" width="10.88671875" style="2"/>
-    <col min="1552" max="1552" width="5.88671875" style="2" customWidth="1"/>
-    <col min="1553" max="1553" width="13.33203125" style="2" customWidth="1"/>
-    <col min="1554" max="1554" width="4.88671875" style="2" customWidth="1"/>
-    <col min="1555" max="1555" width="33.109375" style="2" customWidth="1"/>
-    <col min="1556" max="1556" width="8.109375" style="2" customWidth="1"/>
-    <col min="1557" max="1557" width="6.88671875" style="2" customWidth="1"/>
-    <col min="1558" max="1558" width="14.33203125" style="2" customWidth="1"/>
-    <col min="1559" max="1559" width="18.88671875" style="2" customWidth="1"/>
-    <col min="1560" max="1560" width="13.109375" style="2" customWidth="1"/>
-    <col min="1561" max="1807" width="10.88671875" style="2"/>
-    <col min="1808" max="1808" width="5.88671875" style="2" customWidth="1"/>
-    <col min="1809" max="1809" width="13.33203125" style="2" customWidth="1"/>
-    <col min="1810" max="1810" width="4.88671875" style="2" customWidth="1"/>
-    <col min="1811" max="1811" width="33.109375" style="2" customWidth="1"/>
-    <col min="1812" max="1812" width="8.109375" style="2" customWidth="1"/>
-    <col min="1813" max="1813" width="6.88671875" style="2" customWidth="1"/>
-    <col min="1814" max="1814" width="14.33203125" style="2" customWidth="1"/>
-    <col min="1815" max="1815" width="18.88671875" style="2" customWidth="1"/>
-    <col min="1816" max="1816" width="13.109375" style="2" customWidth="1"/>
-    <col min="1817" max="2063" width="10.88671875" style="2"/>
-    <col min="2064" max="2064" width="5.88671875" style="2" customWidth="1"/>
-    <col min="2065" max="2065" width="13.33203125" style="2" customWidth="1"/>
-    <col min="2066" max="2066" width="4.88671875" style="2" customWidth="1"/>
-    <col min="2067" max="2067" width="33.109375" style="2" customWidth="1"/>
-    <col min="2068" max="2068" width="8.109375" style="2" customWidth="1"/>
-    <col min="2069" max="2069" width="6.88671875" style="2" customWidth="1"/>
-    <col min="2070" max="2070" width="14.33203125" style="2" customWidth="1"/>
-    <col min="2071" max="2071" width="18.88671875" style="2" customWidth="1"/>
-    <col min="2072" max="2072" width="13.109375" style="2" customWidth="1"/>
-    <col min="2073" max="2319" width="10.88671875" style="2"/>
-    <col min="2320" max="2320" width="5.88671875" style="2" customWidth="1"/>
-    <col min="2321" max="2321" width="13.33203125" style="2" customWidth="1"/>
-    <col min="2322" max="2322" width="4.88671875" style="2" customWidth="1"/>
-    <col min="2323" max="2323" width="33.109375" style="2" customWidth="1"/>
-    <col min="2324" max="2324" width="8.109375" style="2" customWidth="1"/>
-    <col min="2325" max="2325" width="6.88671875" style="2" customWidth="1"/>
-    <col min="2326" max="2326" width="14.33203125" style="2" customWidth="1"/>
-    <col min="2327" max="2327" width="18.88671875" style="2" customWidth="1"/>
-    <col min="2328" max="2328" width="13.109375" style="2" customWidth="1"/>
-    <col min="2329" max="2575" width="10.88671875" style="2"/>
-    <col min="2576" max="2576" width="5.88671875" style="2" customWidth="1"/>
-    <col min="2577" max="2577" width="13.33203125" style="2" customWidth="1"/>
-    <col min="2578" max="2578" width="4.88671875" style="2" customWidth="1"/>
-    <col min="2579" max="2579" width="33.109375" style="2" customWidth="1"/>
-    <col min="2580" max="2580" width="8.109375" style="2" customWidth="1"/>
-    <col min="2581" max="2581" width="6.88671875" style="2" customWidth="1"/>
-    <col min="2582" max="2582" width="14.33203125" style="2" customWidth="1"/>
-    <col min="2583" max="2583" width="18.88671875" style="2" customWidth="1"/>
-    <col min="2584" max="2584" width="13.109375" style="2" customWidth="1"/>
-    <col min="2585" max="2831" width="10.88671875" style="2"/>
-    <col min="2832" max="2832" width="5.88671875" style="2" customWidth="1"/>
-    <col min="2833" max="2833" width="13.33203125" style="2" customWidth="1"/>
-    <col min="2834" max="2834" width="4.88671875" style="2" customWidth="1"/>
-    <col min="2835" max="2835" width="33.109375" style="2" customWidth="1"/>
-    <col min="2836" max="2836" width="8.109375" style="2" customWidth="1"/>
-    <col min="2837" max="2837" width="6.88671875" style="2" customWidth="1"/>
-    <col min="2838" max="2838" width="14.33203125" style="2" customWidth="1"/>
-    <col min="2839" max="2839" width="18.88671875" style="2" customWidth="1"/>
-    <col min="2840" max="2840" width="13.109375" style="2" customWidth="1"/>
-    <col min="2841" max="3087" width="10.88671875" style="2"/>
-    <col min="3088" max="3088" width="5.88671875" style="2" customWidth="1"/>
-    <col min="3089" max="3089" width="13.33203125" style="2" customWidth="1"/>
-    <col min="3090" max="3090" width="4.88671875" style="2" customWidth="1"/>
-    <col min="3091" max="3091" width="33.109375" style="2" customWidth="1"/>
-    <col min="3092" max="3092" width="8.109375" style="2" customWidth="1"/>
-    <col min="3093" max="3093" width="6.88671875" style="2" customWidth="1"/>
-    <col min="3094" max="3094" width="14.33203125" style="2" customWidth="1"/>
-    <col min="3095" max="3095" width="18.88671875" style="2" customWidth="1"/>
-    <col min="3096" max="3096" width="13.109375" style="2" customWidth="1"/>
-    <col min="3097" max="3343" width="10.88671875" style="2"/>
-    <col min="3344" max="3344" width="5.88671875" style="2" customWidth="1"/>
-    <col min="3345" max="3345" width="13.33203125" style="2" customWidth="1"/>
-    <col min="3346" max="3346" width="4.88671875" style="2" customWidth="1"/>
-    <col min="3347" max="3347" width="33.109375" style="2" customWidth="1"/>
-    <col min="3348" max="3348" width="8.109375" style="2" customWidth="1"/>
-    <col min="3349" max="3349" width="6.88671875" style="2" customWidth="1"/>
-    <col min="3350" max="3350" width="14.33203125" style="2" customWidth="1"/>
-    <col min="3351" max="3351" width="18.88671875" style="2" customWidth="1"/>
-    <col min="3352" max="3352" width="13.109375" style="2" customWidth="1"/>
-    <col min="3353" max="3599" width="10.88671875" style="2"/>
-    <col min="3600" max="3600" width="5.88671875" style="2" customWidth="1"/>
-    <col min="3601" max="3601" width="13.33203125" style="2" customWidth="1"/>
-    <col min="3602" max="3602" width="4.88671875" style="2" customWidth="1"/>
-    <col min="3603" max="3603" width="33.109375" style="2" customWidth="1"/>
-    <col min="3604" max="3604" width="8.109375" style="2" customWidth="1"/>
-    <col min="3605" max="3605" width="6.88671875" style="2" customWidth="1"/>
-    <col min="3606" max="3606" width="14.33203125" style="2" customWidth="1"/>
-    <col min="3607" max="3607" width="18.88671875" style="2" customWidth="1"/>
-    <col min="3608" max="3608" width="13.109375" style="2" customWidth="1"/>
-    <col min="3609" max="3855" width="10.88671875" style="2"/>
-    <col min="3856" max="3856" width="5.88671875" style="2" customWidth="1"/>
-    <col min="3857" max="3857" width="13.33203125" style="2" customWidth="1"/>
-    <col min="3858" max="3858" width="4.88671875" style="2" customWidth="1"/>
-    <col min="3859" max="3859" width="33.109375" style="2" customWidth="1"/>
-    <col min="3860" max="3860" width="8.109375" style="2" customWidth="1"/>
-    <col min="3861" max="3861" width="6.88671875" style="2" customWidth="1"/>
-    <col min="3862" max="3862" width="14.33203125" style="2" customWidth="1"/>
-    <col min="3863" max="3863" width="18.88671875" style="2" customWidth="1"/>
-    <col min="3864" max="3864" width="13.109375" style="2" customWidth="1"/>
-    <col min="3865" max="4111" width="10.88671875" style="2"/>
-    <col min="4112" max="4112" width="5.88671875" style="2" customWidth="1"/>
-    <col min="4113" max="4113" width="13.33203125" style="2" customWidth="1"/>
-    <col min="4114" max="4114" width="4.88671875" style="2" customWidth="1"/>
-    <col min="4115" max="4115" width="33.109375" style="2" customWidth="1"/>
-    <col min="4116" max="4116" width="8.109375" style="2" customWidth="1"/>
-    <col min="4117" max="4117" width="6.88671875" style="2" customWidth="1"/>
-    <col min="4118" max="4118" width="14.33203125" style="2" customWidth="1"/>
-    <col min="4119" max="4119" width="18.88671875" style="2" customWidth="1"/>
-    <col min="4120" max="4120" width="13.109375" style="2" customWidth="1"/>
-    <col min="4121" max="4367" width="10.88671875" style="2"/>
-    <col min="4368" max="4368" width="5.88671875" style="2" customWidth="1"/>
-    <col min="4369" max="4369" width="13.33203125" style="2" customWidth="1"/>
-    <col min="4370" max="4370" width="4.88671875" style="2" customWidth="1"/>
-    <col min="4371" max="4371" width="33.109375" style="2" customWidth="1"/>
-    <col min="4372" max="4372" width="8.109375" style="2" customWidth="1"/>
-    <col min="4373" max="4373" width="6.88671875" style="2" customWidth="1"/>
-    <col min="4374" max="4374" width="14.33203125" style="2" customWidth="1"/>
-    <col min="4375" max="4375" width="18.88671875" style="2" customWidth="1"/>
-    <col min="4376" max="4376" width="13.109375" style="2" customWidth="1"/>
-    <col min="4377" max="4623" width="10.88671875" style="2"/>
-    <col min="4624" max="4624" width="5.88671875" style="2" customWidth="1"/>
-    <col min="4625" max="4625" width="13.33203125" style="2" customWidth="1"/>
-    <col min="4626" max="4626" width="4.88671875" style="2" customWidth="1"/>
-    <col min="4627" max="4627" width="33.109375" style="2" customWidth="1"/>
-    <col min="4628" max="4628" width="8.109375" style="2" customWidth="1"/>
-    <col min="4629" max="4629" width="6.88671875" style="2" customWidth="1"/>
-    <col min="4630" max="4630" width="14.33203125" style="2" customWidth="1"/>
-    <col min="4631" max="4631" width="18.88671875" style="2" customWidth="1"/>
-    <col min="4632" max="4632" width="13.109375" style="2" customWidth="1"/>
-    <col min="4633" max="4879" width="10.88671875" style="2"/>
-    <col min="4880" max="4880" width="5.88671875" style="2" customWidth="1"/>
-    <col min="4881" max="4881" width="13.33203125" style="2" customWidth="1"/>
-    <col min="4882" max="4882" width="4.88671875" style="2" customWidth="1"/>
-    <col min="4883" max="4883" width="33.109375" style="2" customWidth="1"/>
-    <col min="4884" max="4884" width="8.109375" style="2" customWidth="1"/>
-    <col min="4885" max="4885" width="6.88671875" style="2" customWidth="1"/>
-    <col min="4886" max="4886" width="14.33203125" style="2" customWidth="1"/>
-    <col min="4887" max="4887" width="18.88671875" style="2" customWidth="1"/>
-    <col min="4888" max="4888" width="13.109375" style="2" customWidth="1"/>
-    <col min="4889" max="5135" width="10.88671875" style="2"/>
-    <col min="5136" max="5136" width="5.88671875" style="2" customWidth="1"/>
-    <col min="5137" max="5137" width="13.33203125" style="2" customWidth="1"/>
-    <col min="5138" max="5138" width="4.88671875" style="2" customWidth="1"/>
-    <col min="5139" max="5139" width="33.109375" style="2" customWidth="1"/>
-    <col min="5140" max="5140" width="8.109375" style="2" customWidth="1"/>
-    <col min="5141" max="5141" width="6.88671875" style="2" customWidth="1"/>
-    <col min="5142" max="5142" width="14.33203125" style="2" customWidth="1"/>
-    <col min="5143" max="5143" width="18.88671875" style="2" customWidth="1"/>
-    <col min="5144" max="5144" width="13.109375" style="2" customWidth="1"/>
-    <col min="5145" max="5391" width="10.88671875" style="2"/>
-    <col min="5392" max="5392" width="5.88671875" style="2" customWidth="1"/>
-    <col min="5393" max="5393" width="13.33203125" style="2" customWidth="1"/>
-    <col min="5394" max="5394" width="4.88671875" style="2" customWidth="1"/>
-    <col min="5395" max="5395" width="33.109375" style="2" customWidth="1"/>
-    <col min="5396" max="5396" width="8.109375" style="2" customWidth="1"/>
-    <col min="5397" max="5397" width="6.88671875" style="2" customWidth="1"/>
-    <col min="5398" max="5398" width="14.33203125" style="2" customWidth="1"/>
-    <col min="5399" max="5399" width="18.88671875" style="2" customWidth="1"/>
-    <col min="5400" max="5400" width="13.109375" style="2" customWidth="1"/>
-    <col min="5401" max="5647" width="10.88671875" style="2"/>
-    <col min="5648" max="5648" width="5.88671875" style="2" customWidth="1"/>
-    <col min="5649" max="5649" width="13.33203125" style="2" customWidth="1"/>
-    <col min="5650" max="5650" width="4.88671875" style="2" customWidth="1"/>
-    <col min="5651" max="5651" width="33.109375" style="2" customWidth="1"/>
-    <col min="5652" max="5652" width="8.109375" style="2" customWidth="1"/>
-    <col min="5653" max="5653" width="6.88671875" style="2" customWidth="1"/>
-    <col min="5654" max="5654" width="14.33203125" style="2" customWidth="1"/>
-    <col min="5655" max="5655" width="18.88671875" style="2" customWidth="1"/>
-    <col min="5656" max="5656" width="13.109375" style="2" customWidth="1"/>
-    <col min="5657" max="5903" width="10.88671875" style="2"/>
-    <col min="5904" max="5904" width="5.88671875" style="2" customWidth="1"/>
-    <col min="5905" max="5905" width="13.33203125" style="2" customWidth="1"/>
-    <col min="5906" max="5906" width="4.88671875" style="2" customWidth="1"/>
-    <col min="5907" max="5907" width="33.109375" style="2" customWidth="1"/>
-    <col min="5908" max="5908" width="8.109375" style="2" customWidth="1"/>
-    <col min="5909" max="5909" width="6.88671875" style="2" customWidth="1"/>
-    <col min="5910" max="5910" width="14.33203125" style="2" customWidth="1"/>
-    <col min="5911" max="5911" width="18.88671875" style="2" customWidth="1"/>
-    <col min="5912" max="5912" width="13.109375" style="2" customWidth="1"/>
-    <col min="5913" max="6159" width="10.88671875" style="2"/>
-    <col min="6160" max="6160" width="5.88671875" style="2" customWidth="1"/>
-    <col min="6161" max="6161" width="13.33203125" style="2" customWidth="1"/>
-    <col min="6162" max="6162" width="4.88671875" style="2" customWidth="1"/>
-    <col min="6163" max="6163" width="33.109375" style="2" customWidth="1"/>
-    <col min="6164" max="6164" width="8.109375" style="2" customWidth="1"/>
-    <col min="6165" max="6165" width="6.88671875" style="2" customWidth="1"/>
-    <col min="6166" max="6166" width="14.33203125" style="2" customWidth="1"/>
-    <col min="6167" max="6167" width="18.88671875" style="2" customWidth="1"/>
-    <col min="6168" max="6168" width="13.109375" style="2" customWidth="1"/>
-    <col min="6169" max="6415" width="10.88671875" style="2"/>
-    <col min="6416" max="6416" width="5.88671875" style="2" customWidth="1"/>
-    <col min="6417" max="6417" width="13.33203125" style="2" customWidth="1"/>
-    <col min="6418" max="6418" width="4.88671875" style="2" customWidth="1"/>
-    <col min="6419" max="6419" width="33.109375" style="2" customWidth="1"/>
-    <col min="6420" max="6420" width="8.109375" style="2" customWidth="1"/>
-    <col min="6421" max="6421" width="6.88671875" style="2" customWidth="1"/>
-    <col min="6422" max="6422" width="14.33203125" style="2" customWidth="1"/>
-    <col min="6423" max="6423" width="18.88671875" style="2" customWidth="1"/>
-    <col min="6424" max="6424" width="13.109375" style="2" customWidth="1"/>
-    <col min="6425" max="6671" width="10.88671875" style="2"/>
-    <col min="6672" max="6672" width="5.88671875" style="2" customWidth="1"/>
-    <col min="6673" max="6673" width="13.33203125" style="2" customWidth="1"/>
-    <col min="6674" max="6674" width="4.88671875" style="2" customWidth="1"/>
-    <col min="6675" max="6675" width="33.109375" style="2" customWidth="1"/>
-    <col min="6676" max="6676" width="8.109375" style="2" customWidth="1"/>
-    <col min="6677" max="6677" width="6.88671875" style="2" customWidth="1"/>
-    <col min="6678" max="6678" width="14.33203125" style="2" customWidth="1"/>
-    <col min="6679" max="6679" width="18.88671875" style="2" customWidth="1"/>
-    <col min="6680" max="6680" width="13.109375" style="2" customWidth="1"/>
-    <col min="6681" max="6927" width="10.88671875" style="2"/>
-    <col min="6928" max="6928" width="5.88671875" style="2" customWidth="1"/>
-    <col min="6929" max="6929" width="13.33203125" style="2" customWidth="1"/>
-    <col min="6930" max="6930" width="4.88671875" style="2" customWidth="1"/>
-    <col min="6931" max="6931" width="33.109375" style="2" customWidth="1"/>
-    <col min="6932" max="6932" width="8.109375" style="2" customWidth="1"/>
-    <col min="6933" max="6933" width="6.88671875" style="2" customWidth="1"/>
-    <col min="6934" max="6934" width="14.33203125" style="2" customWidth="1"/>
-    <col min="6935" max="6935" width="18.88671875" style="2" customWidth="1"/>
-    <col min="6936" max="6936" width="13.109375" style="2" customWidth="1"/>
-    <col min="6937" max="7183" width="10.88671875" style="2"/>
-    <col min="7184" max="7184" width="5.88671875" style="2" customWidth="1"/>
-    <col min="7185" max="7185" width="13.33203125" style="2" customWidth="1"/>
-    <col min="7186" max="7186" width="4.88671875" style="2" customWidth="1"/>
-    <col min="7187" max="7187" width="33.109375" style="2" customWidth="1"/>
-    <col min="7188" max="7188" width="8.109375" style="2" customWidth="1"/>
-    <col min="7189" max="7189" width="6.88671875" style="2" customWidth="1"/>
-    <col min="7190" max="7190" width="14.33203125" style="2" customWidth="1"/>
-    <col min="7191" max="7191" width="18.88671875" style="2" customWidth="1"/>
-    <col min="7192" max="7192" width="13.109375" style="2" customWidth="1"/>
-    <col min="7193" max="7439" width="10.88671875" style="2"/>
-    <col min="7440" max="7440" width="5.88671875" style="2" customWidth="1"/>
-    <col min="7441" max="7441" width="13.33203125" style="2" customWidth="1"/>
-    <col min="7442" max="7442" width="4.88671875" style="2" customWidth="1"/>
-    <col min="7443" max="7443" width="33.109375" style="2" customWidth="1"/>
-    <col min="7444" max="7444" width="8.109375" style="2" customWidth="1"/>
-    <col min="7445" max="7445" width="6.88671875" style="2" customWidth="1"/>
-    <col min="7446" max="7446" width="14.33203125" style="2" customWidth="1"/>
-    <col min="7447" max="7447" width="18.88671875" style="2" customWidth="1"/>
-    <col min="7448" max="7448" width="13.109375" style="2" customWidth="1"/>
-    <col min="7449" max="7695" width="10.88671875" style="2"/>
-    <col min="7696" max="7696" width="5.88671875" style="2" customWidth="1"/>
-    <col min="7697" max="7697" width="13.33203125" style="2" customWidth="1"/>
-    <col min="7698" max="7698" width="4.88671875" style="2" customWidth="1"/>
-    <col min="7699" max="7699" width="33.109375" style="2" customWidth="1"/>
-    <col min="7700" max="7700" width="8.109375" style="2" customWidth="1"/>
-    <col min="7701" max="7701" width="6.88671875" style="2" customWidth="1"/>
-    <col min="7702" max="7702" width="14.33203125" style="2" customWidth="1"/>
-    <col min="7703" max="7703" width="18.88671875" style="2" customWidth="1"/>
-    <col min="7704" max="7704" width="13.109375" style="2" customWidth="1"/>
-    <col min="7705" max="7951" width="10.88671875" style="2"/>
-    <col min="7952" max="7952" width="5.88671875" style="2" customWidth="1"/>
-    <col min="7953" max="7953" width="13.33203125" style="2" customWidth="1"/>
-    <col min="7954" max="7954" width="4.88671875" style="2" customWidth="1"/>
-    <col min="7955" max="7955" width="33.109375" style="2" customWidth="1"/>
-    <col min="7956" max="7956" width="8.109375" style="2" customWidth="1"/>
-    <col min="7957" max="7957" width="6.88671875" style="2" customWidth="1"/>
-    <col min="7958" max="7958" width="14.33203125" style="2" customWidth="1"/>
-    <col min="7959" max="7959" width="18.88671875" style="2" customWidth="1"/>
-    <col min="7960" max="7960" width="13.109375" style="2" customWidth="1"/>
-    <col min="7961" max="8207" width="10.88671875" style="2"/>
-    <col min="8208" max="8208" width="5.88671875" style="2" customWidth="1"/>
-    <col min="8209" max="8209" width="13.33203125" style="2" customWidth="1"/>
-    <col min="8210" max="8210" width="4.88671875" style="2" customWidth="1"/>
-    <col min="8211" max="8211" width="33.109375" style="2" customWidth="1"/>
-    <col min="8212" max="8212" width="8.109375" style="2" customWidth="1"/>
-    <col min="8213" max="8213" width="6.88671875" style="2" customWidth="1"/>
-    <col min="8214" max="8214" width="14.33203125" style="2" customWidth="1"/>
-    <col min="8215" max="8215" width="18.88671875" style="2" customWidth="1"/>
-    <col min="8216" max="8216" width="13.109375" style="2" customWidth="1"/>
-    <col min="8217" max="8463" width="10.88671875" style="2"/>
-    <col min="8464" max="8464" width="5.88671875" style="2" customWidth="1"/>
-    <col min="8465" max="8465" width="13.33203125" style="2" customWidth="1"/>
-    <col min="8466" max="8466" width="4.88671875" style="2" customWidth="1"/>
-    <col min="8467" max="8467" width="33.109375" style="2" customWidth="1"/>
-    <col min="8468" max="8468" width="8.109375" style="2" customWidth="1"/>
-    <col min="8469" max="8469" width="6.88671875" style="2" customWidth="1"/>
-    <col min="8470" max="8470" width="14.33203125" style="2" customWidth="1"/>
-    <col min="8471" max="8471" width="18.88671875" style="2" customWidth="1"/>
-    <col min="8472" max="8472" width="13.109375" style="2" customWidth="1"/>
-    <col min="8473" max="8719" width="10.88671875" style="2"/>
-    <col min="8720" max="8720" width="5.88671875" style="2" customWidth="1"/>
-    <col min="8721" max="8721" width="13.33203125" style="2" customWidth="1"/>
-    <col min="8722" max="8722" width="4.88671875" style="2" customWidth="1"/>
-    <col min="8723" max="8723" width="33.109375" style="2" customWidth="1"/>
-    <col min="8724" max="8724" width="8.109375" style="2" customWidth="1"/>
-    <col min="8725" max="8725" width="6.88671875" style="2" customWidth="1"/>
-    <col min="8726" max="8726" width="14.33203125" style="2" customWidth="1"/>
-    <col min="8727" max="8727" width="18.88671875" style="2" customWidth="1"/>
-    <col min="8728" max="8728" width="13.109375" style="2" customWidth="1"/>
-    <col min="8729" max="8975" width="10.88671875" style="2"/>
-    <col min="8976" max="8976" width="5.88671875" style="2" customWidth="1"/>
-    <col min="8977" max="8977" width="13.33203125" style="2" customWidth="1"/>
-    <col min="8978" max="8978" width="4.88671875" style="2" customWidth="1"/>
-    <col min="8979" max="8979" width="33.109375" style="2" customWidth="1"/>
-    <col min="8980" max="8980" width="8.109375" style="2" customWidth="1"/>
-    <col min="8981" max="8981" width="6.88671875" style="2" customWidth="1"/>
-    <col min="8982" max="8982" width="14.33203125" style="2" customWidth="1"/>
-    <col min="8983" max="8983" width="18.88671875" style="2" customWidth="1"/>
-    <col min="8984" max="8984" width="13.109375" style="2" customWidth="1"/>
-    <col min="8985" max="9231" width="10.88671875" style="2"/>
-    <col min="9232" max="9232" width="5.88671875" style="2" customWidth="1"/>
-    <col min="9233" max="9233" width="13.33203125" style="2" customWidth="1"/>
-    <col min="9234" max="9234" width="4.88671875" style="2" customWidth="1"/>
-    <col min="9235" max="9235" width="33.109375" style="2" customWidth="1"/>
-    <col min="9236" max="9236" width="8.109375" style="2" customWidth="1"/>
-    <col min="9237" max="9237" width="6.88671875" style="2" customWidth="1"/>
-    <col min="9238" max="9238" width="14.33203125" style="2" customWidth="1"/>
-    <col min="9239" max="9239" width="18.88671875" style="2" customWidth="1"/>
-    <col min="9240" max="9240" width="13.109375" style="2" customWidth="1"/>
-    <col min="9241" max="9487" width="10.88671875" style="2"/>
-    <col min="9488" max="9488" width="5.88671875" style="2" customWidth="1"/>
-    <col min="9489" max="9489" width="13.33203125" style="2" customWidth="1"/>
-    <col min="9490" max="9490" width="4.88671875" style="2" customWidth="1"/>
-    <col min="9491" max="9491" width="33.109375" style="2" customWidth="1"/>
-    <col min="9492" max="9492" width="8.109375" style="2" customWidth="1"/>
-    <col min="9493" max="9493" width="6.88671875" style="2" customWidth="1"/>
-    <col min="9494" max="9494" width="14.33203125" style="2" customWidth="1"/>
-    <col min="9495" max="9495" width="18.88671875" style="2" customWidth="1"/>
-    <col min="9496" max="9496" width="13.109375" style="2" customWidth="1"/>
-    <col min="9497" max="9743" width="10.88671875" style="2"/>
-    <col min="9744" max="9744" width="5.88671875" style="2" customWidth="1"/>
-    <col min="9745" max="9745" width="13.33203125" style="2" customWidth="1"/>
-    <col min="9746" max="9746" width="4.88671875" style="2" customWidth="1"/>
-    <col min="9747" max="9747" width="33.109375" style="2" customWidth="1"/>
-    <col min="9748" max="9748" width="8.109375" style="2" customWidth="1"/>
-    <col min="9749" max="9749" width="6.88671875" style="2" customWidth="1"/>
-    <col min="9750" max="9750" width="14.33203125" style="2" customWidth="1"/>
-    <col min="9751" max="9751" width="18.88671875" style="2" customWidth="1"/>
-    <col min="9752" max="9752" width="13.109375" style="2" customWidth="1"/>
-    <col min="9753" max="9999" width="10.88671875" style="2"/>
-    <col min="10000" max="10000" width="5.88671875" style="2" customWidth="1"/>
-    <col min="10001" max="10001" width="13.33203125" style="2" customWidth="1"/>
-    <col min="10002" max="10002" width="4.88671875" style="2" customWidth="1"/>
-    <col min="10003" max="10003" width="33.109375" style="2" customWidth="1"/>
-    <col min="10004" max="10004" width="8.109375" style="2" customWidth="1"/>
-    <col min="10005" max="10005" width="6.88671875" style="2" customWidth="1"/>
-    <col min="10006" max="10006" width="14.33203125" style="2" customWidth="1"/>
-    <col min="10007" max="10007" width="18.88671875" style="2" customWidth="1"/>
-    <col min="10008" max="10008" width="13.109375" style="2" customWidth="1"/>
-    <col min="10009" max="10255" width="10.88671875" style="2"/>
-    <col min="10256" max="10256" width="5.88671875" style="2" customWidth="1"/>
-    <col min="10257" max="10257" width="13.33203125" style="2" customWidth="1"/>
-    <col min="10258" max="10258" width="4.88671875" style="2" customWidth="1"/>
-    <col min="10259" max="10259" width="33.109375" style="2" customWidth="1"/>
-    <col min="10260" max="10260" width="8.109375" style="2" customWidth="1"/>
-    <col min="10261" max="10261" width="6.88671875" style="2" customWidth="1"/>
-    <col min="10262" max="10262" width="14.33203125" style="2" customWidth="1"/>
-    <col min="10263" max="10263" width="18.88671875" style="2" customWidth="1"/>
-    <col min="10264" max="10264" width="13.109375" style="2" customWidth="1"/>
-    <col min="10265" max="10511" width="10.88671875" style="2"/>
-    <col min="10512" max="10512" width="5.88671875" style="2" customWidth="1"/>
-    <col min="10513" max="10513" width="13.33203125" style="2" customWidth="1"/>
-    <col min="10514" max="10514" width="4.88671875" style="2" customWidth="1"/>
-    <col min="10515" max="10515" width="33.109375" style="2" customWidth="1"/>
-    <col min="10516" max="10516" width="8.109375" style="2" customWidth="1"/>
-    <col min="10517" max="10517" width="6.88671875" style="2" customWidth="1"/>
-    <col min="10518" max="10518" width="14.33203125" style="2" customWidth="1"/>
-    <col min="10519" max="10519" width="18.88671875" style="2" customWidth="1"/>
-    <col min="10520" max="10520" width="13.109375" style="2" customWidth="1"/>
-    <col min="10521" max="10767" width="10.88671875" style="2"/>
-    <col min="10768" max="10768" width="5.88671875" style="2" customWidth="1"/>
-    <col min="10769" max="10769" width="13.33203125" style="2" customWidth="1"/>
-    <col min="10770" max="10770" width="4.88671875" style="2" customWidth="1"/>
-    <col min="10771" max="10771" width="33.109375" style="2" customWidth="1"/>
-    <col min="10772" max="10772" width="8.109375" style="2" customWidth="1"/>
-    <col min="10773" max="10773" width="6.88671875" style="2" customWidth="1"/>
-    <col min="10774" max="10774" width="14.33203125" style="2" customWidth="1"/>
-    <col min="10775" max="10775" width="18.88671875" style="2" customWidth="1"/>
-    <col min="10776" max="10776" width="13.109375" style="2" customWidth="1"/>
-    <col min="10777" max="11023" width="10.88671875" style="2"/>
-    <col min="11024" max="11024" width="5.88671875" style="2" customWidth="1"/>
-    <col min="11025" max="11025" width="13.33203125" style="2" customWidth="1"/>
-    <col min="11026" max="11026" width="4.88671875" style="2" customWidth="1"/>
-    <col min="11027" max="11027" width="33.109375" style="2" customWidth="1"/>
-    <col min="11028" max="11028" width="8.109375" style="2" customWidth="1"/>
-    <col min="11029" max="11029" width="6.88671875" style="2" customWidth="1"/>
-    <col min="11030" max="11030" width="14.33203125" style="2" customWidth="1"/>
-    <col min="11031" max="11031" width="18.88671875" style="2" customWidth="1"/>
-    <col min="11032" max="11032" width="13.109375" style="2" customWidth="1"/>
-    <col min="11033" max="11279" width="10.88671875" style="2"/>
-    <col min="11280" max="11280" width="5.88671875" style="2" customWidth="1"/>
-    <col min="11281" max="11281" width="13.33203125" style="2" customWidth="1"/>
-    <col min="11282" max="11282" width="4.88671875" style="2" customWidth="1"/>
-    <col min="11283" max="11283" width="33.109375" style="2" customWidth="1"/>
-    <col min="11284" max="11284" width="8.109375" style="2" customWidth="1"/>
-    <col min="11285" max="11285" width="6.88671875" style="2" customWidth="1"/>
-    <col min="11286" max="11286" width="14.33203125" style="2" customWidth="1"/>
-    <col min="11287" max="11287" width="18.88671875" style="2" customWidth="1"/>
-    <col min="11288" max="11288" width="13.109375" style="2" customWidth="1"/>
-    <col min="11289" max="11535" width="10.88671875" style="2"/>
-    <col min="11536" max="11536" width="5.88671875" style="2" customWidth="1"/>
-    <col min="11537" max="11537" width="13.33203125" style="2" customWidth="1"/>
-    <col min="11538" max="11538" width="4.88671875" style="2" customWidth="1"/>
-    <col min="11539" max="11539" width="33.109375" style="2" customWidth="1"/>
-    <col min="11540" max="11540" width="8.109375" style="2" customWidth="1"/>
-    <col min="11541" max="11541" width="6.88671875" style="2" customWidth="1"/>
-    <col min="11542" max="11542" width="14.33203125" style="2" customWidth="1"/>
-    <col min="11543" max="11543" width="18.88671875" style="2" customWidth="1"/>
-    <col min="11544" max="11544" width="13.109375" style="2" customWidth="1"/>
-    <col min="11545" max="11791" width="10.88671875" style="2"/>
-    <col min="11792" max="11792" width="5.88671875" style="2" customWidth="1"/>
-    <col min="11793" max="11793" width="13.33203125" style="2" customWidth="1"/>
-    <col min="11794" max="11794" width="4.88671875" style="2" customWidth="1"/>
-    <col min="11795" max="11795" width="33.109375" style="2" customWidth="1"/>
-    <col min="11796" max="11796" width="8.109375" style="2" customWidth="1"/>
-    <col min="11797" max="11797" width="6.88671875" style="2" customWidth="1"/>
-    <col min="11798" max="11798" width="14.33203125" style="2" customWidth="1"/>
-    <col min="11799" max="11799" width="18.88671875" style="2" customWidth="1"/>
-    <col min="11800" max="11800" width="13.109375" style="2" customWidth="1"/>
-    <col min="11801" max="12047" width="10.88671875" style="2"/>
-    <col min="12048" max="12048" width="5.88671875" style="2" customWidth="1"/>
-    <col min="12049" max="12049" width="13.33203125" style="2" customWidth="1"/>
-    <col min="12050" max="12050" width="4.88671875" style="2" customWidth="1"/>
-    <col min="12051" max="12051" width="33.109375" style="2" customWidth="1"/>
-    <col min="12052" max="12052" width="8.109375" style="2" customWidth="1"/>
-    <col min="12053" max="12053" width="6.88671875" style="2" customWidth="1"/>
-    <col min="12054" max="12054" width="14.33203125" style="2" customWidth="1"/>
-    <col min="12055" max="12055" width="18.88671875" style="2" customWidth="1"/>
-    <col min="12056" max="12056" width="13.109375" style="2" customWidth="1"/>
-    <col min="12057" max="12303" width="10.88671875" style="2"/>
-    <col min="12304" max="12304" width="5.88671875" style="2" customWidth="1"/>
-    <col min="12305" max="12305" width="13.33203125" style="2" customWidth="1"/>
-    <col min="12306" max="12306" width="4.88671875" style="2" customWidth="1"/>
-    <col min="12307" max="12307" width="33.109375" style="2" customWidth="1"/>
-    <col min="12308" max="12308" width="8.109375" style="2" customWidth="1"/>
-    <col min="12309" max="12309" width="6.88671875" style="2" customWidth="1"/>
-    <col min="12310" max="12310" width="14.33203125" style="2" customWidth="1"/>
-    <col min="12311" max="12311" width="18.88671875" style="2" customWidth="1"/>
-    <col min="12312" max="12312" width="13.109375" style="2" customWidth="1"/>
-    <col min="12313" max="12559" width="10.88671875" style="2"/>
-    <col min="12560" max="12560" width="5.88671875" style="2" customWidth="1"/>
-    <col min="12561" max="12561" width="13.33203125" style="2" customWidth="1"/>
-    <col min="12562" max="12562" width="4.88671875" style="2" customWidth="1"/>
-    <col min="12563" max="12563" width="33.109375" style="2" customWidth="1"/>
-    <col min="12564" max="12564" width="8.109375" style="2" customWidth="1"/>
-    <col min="12565" max="12565" width="6.88671875" style="2" customWidth="1"/>
-    <col min="12566" max="12566" width="14.33203125" style="2" customWidth="1"/>
-    <col min="12567" max="12567" width="18.88671875" style="2" customWidth="1"/>
-    <col min="12568" max="12568" width="13.109375" style="2" customWidth="1"/>
-    <col min="12569" max="12815" width="10.88671875" style="2"/>
-    <col min="12816" max="12816" width="5.88671875" style="2" customWidth="1"/>
-    <col min="12817" max="12817" width="13.33203125" style="2" customWidth="1"/>
-    <col min="12818" max="12818" width="4.88671875" style="2" customWidth="1"/>
-    <col min="12819" max="12819" width="33.109375" style="2" customWidth="1"/>
-    <col min="12820" max="12820" width="8.109375" style="2" customWidth="1"/>
-    <col min="12821" max="12821" width="6.88671875" style="2" customWidth="1"/>
-    <col min="12822" max="12822" width="14.33203125" style="2" customWidth="1"/>
-    <col min="12823" max="12823" width="18.88671875" style="2" customWidth="1"/>
-    <col min="12824" max="12824" width="13.109375" style="2" customWidth="1"/>
-    <col min="12825" max="13071" width="10.88671875" style="2"/>
-    <col min="13072" max="13072" width="5.88671875" style="2" customWidth="1"/>
-    <col min="13073" max="13073" width="13.33203125" style="2" customWidth="1"/>
-    <col min="13074" max="13074" width="4.88671875" style="2" customWidth="1"/>
-    <col min="13075" max="13075" width="33.109375" style="2" customWidth="1"/>
-    <col min="13076" max="13076" width="8.109375" style="2" customWidth="1"/>
-    <col min="13077" max="13077" width="6.88671875" style="2" customWidth="1"/>
-    <col min="13078" max="13078" width="14.33203125" style="2" customWidth="1"/>
-    <col min="13079" max="13079" width="18.88671875" style="2" customWidth="1"/>
-    <col min="13080" max="13080" width="13.109375" style="2" customWidth="1"/>
-    <col min="13081" max="13327" width="10.88671875" style="2"/>
-    <col min="13328" max="13328" width="5.88671875" style="2" customWidth="1"/>
-    <col min="13329" max="13329" width="13.33203125" style="2" customWidth="1"/>
-    <col min="13330" max="13330" width="4.88671875" style="2" customWidth="1"/>
-    <col min="13331" max="13331" width="33.109375" style="2" customWidth="1"/>
-    <col min="13332" max="13332" width="8.109375" style="2" customWidth="1"/>
-    <col min="13333" max="13333" width="6.88671875" style="2" customWidth="1"/>
-    <col min="13334" max="13334" width="14.33203125" style="2" customWidth="1"/>
-    <col min="13335" max="13335" width="18.88671875" style="2" customWidth="1"/>
-    <col min="13336" max="13336" width="13.109375" style="2" customWidth="1"/>
-    <col min="13337" max="13583" width="10.88671875" style="2"/>
-    <col min="13584" max="13584" width="5.88671875" style="2" customWidth="1"/>
-    <col min="13585" max="13585" width="13.33203125" style="2" customWidth="1"/>
-    <col min="13586" max="13586" width="4.88671875" style="2" customWidth="1"/>
-    <col min="13587" max="13587" width="33.109375" style="2" customWidth="1"/>
-    <col min="13588" max="13588" width="8.109375" style="2" customWidth="1"/>
-    <col min="13589" max="13589" width="6.88671875" style="2" customWidth="1"/>
-    <col min="13590" max="13590" width="14.33203125" style="2" customWidth="1"/>
-    <col min="13591" max="13591" width="18.88671875" style="2" customWidth="1"/>
-    <col min="13592" max="13592" width="13.109375" style="2" customWidth="1"/>
-    <col min="13593" max="13839" width="10.88671875" style="2"/>
-    <col min="13840" max="13840" width="5.88671875" style="2" customWidth="1"/>
-    <col min="13841" max="13841" width="13.33203125" style="2" customWidth="1"/>
-    <col min="13842" max="13842" width="4.88671875" style="2" customWidth="1"/>
-    <col min="13843" max="13843" width="33.109375" style="2" customWidth="1"/>
-    <col min="13844" max="13844" width="8.109375" style="2" customWidth="1"/>
-    <col min="13845" max="13845" width="6.88671875" style="2" customWidth="1"/>
-    <col min="13846" max="13846" width="14.33203125" style="2" customWidth="1"/>
-    <col min="13847" max="13847" width="18.88671875" style="2" customWidth="1"/>
-    <col min="13848" max="13848" width="13.109375" style="2" customWidth="1"/>
-    <col min="13849" max="14095" width="10.88671875" style="2"/>
-    <col min="14096" max="14096" width="5.88671875" style="2" customWidth="1"/>
-    <col min="14097" max="14097" width="13.33203125" style="2" customWidth="1"/>
-    <col min="14098" max="14098" width="4.88671875" style="2" customWidth="1"/>
-    <col min="14099" max="14099" width="33.109375" style="2" customWidth="1"/>
-    <col min="14100" max="14100" width="8.109375" style="2" customWidth="1"/>
-    <col min="14101" max="14101" width="6.88671875" style="2" customWidth="1"/>
-    <col min="14102" max="14102" width="14.33203125" style="2" customWidth="1"/>
-    <col min="14103" max="14103" width="18.88671875" style="2" customWidth="1"/>
-    <col min="14104" max="14104" width="13.109375" style="2" customWidth="1"/>
-    <col min="14105" max="14351" width="10.88671875" style="2"/>
-    <col min="14352" max="14352" width="5.88671875" style="2" customWidth="1"/>
-    <col min="14353" max="14353" width="13.33203125" style="2" customWidth="1"/>
-    <col min="14354" max="14354" width="4.88671875" style="2" customWidth="1"/>
-    <col min="14355" max="14355" width="33.109375" style="2" customWidth="1"/>
-    <col min="14356" max="14356" width="8.109375" style="2" customWidth="1"/>
-    <col min="14357" max="14357" width="6.88671875" style="2" customWidth="1"/>
-    <col min="14358" max="14358" width="14.33203125" style="2" customWidth="1"/>
-    <col min="14359" max="14359" width="18.88671875" style="2" customWidth="1"/>
-    <col min="14360" max="14360" width="13.109375" style="2" customWidth="1"/>
-    <col min="14361" max="14607" width="10.88671875" style="2"/>
-    <col min="14608" max="14608" width="5.88671875" style="2" customWidth="1"/>
-    <col min="14609" max="14609" width="13.33203125" style="2" customWidth="1"/>
-    <col min="14610" max="14610" width="4.88671875" style="2" customWidth="1"/>
-    <col min="14611" max="14611" width="33.109375" style="2" customWidth="1"/>
-    <col min="14612" max="14612" width="8.109375" style="2" customWidth="1"/>
-    <col min="14613" max="14613" width="6.88671875" style="2" customWidth="1"/>
-    <col min="14614" max="14614" width="14.33203125" style="2" customWidth="1"/>
-    <col min="14615" max="14615" width="18.88671875" style="2" customWidth="1"/>
-    <col min="14616" max="14616" width="13.109375" style="2" customWidth="1"/>
-    <col min="14617" max="14863" width="10.88671875" style="2"/>
-    <col min="14864" max="14864" width="5.88671875" style="2" customWidth="1"/>
-    <col min="14865" max="14865" width="13.33203125" style="2" customWidth="1"/>
-    <col min="14866" max="14866" width="4.88671875" style="2" customWidth="1"/>
-    <col min="14867" max="14867" width="33.109375" style="2" customWidth="1"/>
-    <col min="14868" max="14868" width="8.109375" style="2" customWidth="1"/>
-    <col min="14869" max="14869" width="6.88671875" style="2" customWidth="1"/>
-    <col min="14870" max="14870" width="14.33203125" style="2" customWidth="1"/>
-    <col min="14871" max="14871" width="18.88671875" style="2" customWidth="1"/>
-    <col min="14872" max="14872" width="13.109375" style="2" customWidth="1"/>
-    <col min="14873" max="15119" width="10.88671875" style="2"/>
-    <col min="15120" max="15120" width="5.88671875" style="2" customWidth="1"/>
-    <col min="15121" max="15121" width="13.33203125" style="2" customWidth="1"/>
-    <col min="15122" max="15122" width="4.88671875" style="2" customWidth="1"/>
-    <col min="15123" max="15123" width="33.109375" style="2" customWidth="1"/>
-    <col min="15124" max="15124" width="8.109375" style="2" customWidth="1"/>
-    <col min="15125" max="15125" width="6.88671875" style="2" customWidth="1"/>
-    <col min="15126" max="15126" width="14.33203125" style="2" customWidth="1"/>
-    <col min="15127" max="15127" width="18.88671875" style="2" customWidth="1"/>
-    <col min="15128" max="15128" width="13.109375" style="2" customWidth="1"/>
-    <col min="15129" max="15375" width="10.88671875" style="2"/>
-    <col min="15376" max="15376" width="5.88671875" style="2" customWidth="1"/>
-    <col min="15377" max="15377" width="13.33203125" style="2" customWidth="1"/>
-    <col min="15378" max="15378" width="4.88671875" style="2" customWidth="1"/>
-    <col min="15379" max="15379" width="33.109375" style="2" customWidth="1"/>
-    <col min="15380" max="15380" width="8.109375" style="2" customWidth="1"/>
-    <col min="15381" max="15381" width="6.88671875" style="2" customWidth="1"/>
-    <col min="15382" max="15382" width="14.33203125" style="2" customWidth="1"/>
-    <col min="15383" max="15383" width="18.88671875" style="2" customWidth="1"/>
-    <col min="15384" max="15384" width="13.109375" style="2" customWidth="1"/>
-    <col min="15385" max="15631" width="10.88671875" style="2"/>
-    <col min="15632" max="15632" width="5.88671875" style="2" customWidth="1"/>
-    <col min="15633" max="15633" width="13.33203125" style="2" customWidth="1"/>
-    <col min="15634" max="15634" width="4.88671875" style="2" customWidth="1"/>
-    <col min="15635" max="15635" width="33.109375" style="2" customWidth="1"/>
-    <col min="15636" max="15636" width="8.109375" style="2" customWidth="1"/>
-    <col min="15637" max="15637" width="6.88671875" style="2" customWidth="1"/>
-    <col min="15638" max="15638" width="14.33203125" style="2" customWidth="1"/>
-    <col min="15639" max="15639" width="18.88671875" style="2" customWidth="1"/>
-    <col min="15640" max="15640" width="13.109375" style="2" customWidth="1"/>
-    <col min="15641" max="15887" width="10.88671875" style="2"/>
-    <col min="15888" max="15888" width="5.88671875" style="2" customWidth="1"/>
-    <col min="15889" max="15889" width="13.33203125" style="2" customWidth="1"/>
-    <col min="15890" max="15890" width="4.88671875" style="2" customWidth="1"/>
-    <col min="15891" max="15891" width="33.109375" style="2" customWidth="1"/>
-    <col min="15892" max="15892" width="8.109375" style="2" customWidth="1"/>
-    <col min="15893" max="15893" width="6.88671875" style="2" customWidth="1"/>
-    <col min="15894" max="15894" width="14.33203125" style="2" customWidth="1"/>
-    <col min="15895" max="15895" width="18.88671875" style="2" customWidth="1"/>
-    <col min="15896" max="15896" width="13.109375" style="2" customWidth="1"/>
-    <col min="15897" max="16143" width="10.88671875" style="2"/>
-    <col min="16144" max="16144" width="5.88671875" style="2" customWidth="1"/>
-    <col min="16145" max="16145" width="13.33203125" style="2" customWidth="1"/>
-    <col min="16146" max="16146" width="4.88671875" style="2" customWidth="1"/>
-    <col min="16147" max="16147" width="33.109375" style="2" customWidth="1"/>
-    <col min="16148" max="16148" width="8.109375" style="2" customWidth="1"/>
-    <col min="16149" max="16149" width="6.88671875" style="2" customWidth="1"/>
-    <col min="16150" max="16150" width="14.33203125" style="2" customWidth="1"/>
-    <col min="16151" max="16151" width="18.88671875" style="2" customWidth="1"/>
-    <col min="16152" max="16152" width="13.109375" style="2" customWidth="1"/>
-    <col min="16153" max="16384" width="10.88671875" style="2"/>
+    <col min="25" max="271" width="10.85546875" style="2"/>
+    <col min="272" max="272" width="5.85546875" style="2" customWidth="1"/>
+    <col min="273" max="273" width="13.28515625" style="2" customWidth="1"/>
+    <col min="274" max="274" width="4.85546875" style="2" customWidth="1"/>
+    <col min="275" max="275" width="33.140625" style="2" customWidth="1"/>
+    <col min="276" max="276" width="8.140625" style="2" customWidth="1"/>
+    <col min="277" max="277" width="6.85546875" style="2" customWidth="1"/>
+    <col min="278" max="278" width="14.28515625" style="2" customWidth="1"/>
+    <col min="279" max="279" width="18.85546875" style="2" customWidth="1"/>
+    <col min="280" max="280" width="13.140625" style="2" customWidth="1"/>
+    <col min="281" max="527" width="10.85546875" style="2"/>
+    <col min="528" max="528" width="5.85546875" style="2" customWidth="1"/>
+    <col min="529" max="529" width="13.28515625" style="2" customWidth="1"/>
+    <col min="530" max="530" width="4.85546875" style="2" customWidth="1"/>
+    <col min="531" max="531" width="33.140625" style="2" customWidth="1"/>
+    <col min="532" max="532" width="8.140625" style="2" customWidth="1"/>
+    <col min="533" max="533" width="6.85546875" style="2" customWidth="1"/>
+    <col min="534" max="534" width="14.28515625" style="2" customWidth="1"/>
+    <col min="535" max="535" width="18.85546875" style="2" customWidth="1"/>
+    <col min="536" max="536" width="13.140625" style="2" customWidth="1"/>
+    <col min="537" max="783" width="10.85546875" style="2"/>
+    <col min="784" max="784" width="5.85546875" style="2" customWidth="1"/>
+    <col min="785" max="785" width="13.28515625" style="2" customWidth="1"/>
+    <col min="786" max="786" width="4.85546875" style="2" customWidth="1"/>
+    <col min="787" max="787" width="33.140625" style="2" customWidth="1"/>
+    <col min="788" max="788" width="8.140625" style="2" customWidth="1"/>
+    <col min="789" max="789" width="6.85546875" style="2" customWidth="1"/>
+    <col min="790" max="790" width="14.28515625" style="2" customWidth="1"/>
+    <col min="791" max="791" width="18.85546875" style="2" customWidth="1"/>
+    <col min="792" max="792" width="13.140625" style="2" customWidth="1"/>
+    <col min="793" max="1039" width="10.85546875" style="2"/>
+    <col min="1040" max="1040" width="5.85546875" style="2" customWidth="1"/>
+    <col min="1041" max="1041" width="13.28515625" style="2" customWidth="1"/>
+    <col min="1042" max="1042" width="4.85546875" style="2" customWidth="1"/>
+    <col min="1043" max="1043" width="33.140625" style="2" customWidth="1"/>
+    <col min="1044" max="1044" width="8.140625" style="2" customWidth="1"/>
+    <col min="1045" max="1045" width="6.85546875" style="2" customWidth="1"/>
+    <col min="1046" max="1046" width="14.28515625" style="2" customWidth="1"/>
+    <col min="1047" max="1047" width="18.85546875" style="2" customWidth="1"/>
+    <col min="1048" max="1048" width="13.140625" style="2" customWidth="1"/>
+    <col min="1049" max="1295" width="10.85546875" style="2"/>
+    <col min="1296" max="1296" width="5.85546875" style="2" customWidth="1"/>
+    <col min="1297" max="1297" width="13.28515625" style="2" customWidth="1"/>
+    <col min="1298" max="1298" width="4.85546875" style="2" customWidth="1"/>
+    <col min="1299" max="1299" width="33.140625" style="2" customWidth="1"/>
+    <col min="1300" max="1300" width="8.140625" style="2" customWidth="1"/>
+    <col min="1301" max="1301" width="6.85546875" style="2" customWidth="1"/>
+    <col min="1302" max="1302" width="14.28515625" style="2" customWidth="1"/>
+    <col min="1303" max="1303" width="18.85546875" style="2" customWidth="1"/>
+    <col min="1304" max="1304" width="13.140625" style="2" customWidth="1"/>
+    <col min="1305" max="1551" width="10.85546875" style="2"/>
+    <col min="1552" max="1552" width="5.85546875" style="2" customWidth="1"/>
+    <col min="1553" max="1553" width="13.28515625" style="2" customWidth="1"/>
+    <col min="1554" max="1554" width="4.85546875" style="2" customWidth="1"/>
+    <col min="1555" max="1555" width="33.140625" style="2" customWidth="1"/>
+    <col min="1556" max="1556" width="8.140625" style="2" customWidth="1"/>
+    <col min="1557" max="1557" width="6.85546875" style="2" customWidth="1"/>
+    <col min="1558" max="1558" width="14.28515625" style="2" customWidth="1"/>
+    <col min="1559" max="1559" width="18.85546875" style="2" customWidth="1"/>
+    <col min="1560" max="1560" width="13.140625" style="2" customWidth="1"/>
+    <col min="1561" max="1807" width="10.85546875" style="2"/>
+    <col min="1808" max="1808" width="5.85546875" style="2" customWidth="1"/>
+    <col min="1809" max="1809" width="13.28515625" style="2" customWidth="1"/>
+    <col min="1810" max="1810" width="4.85546875" style="2" customWidth="1"/>
+    <col min="1811" max="1811" width="33.140625" style="2" customWidth="1"/>
+    <col min="1812" max="1812" width="8.140625" style="2" customWidth="1"/>
+    <col min="1813" max="1813" width="6.85546875" style="2" customWidth="1"/>
+    <col min="1814" max="1814" width="14.28515625" style="2" customWidth="1"/>
+    <col min="1815" max="1815" width="18.85546875" style="2" customWidth="1"/>
+    <col min="1816" max="1816" width="13.140625" style="2" customWidth="1"/>
+    <col min="1817" max="2063" width="10.85546875" style="2"/>
+    <col min="2064" max="2064" width="5.85546875" style="2" customWidth="1"/>
+    <col min="2065" max="2065" width="13.28515625" style="2" customWidth="1"/>
+    <col min="2066" max="2066" width="4.85546875" style="2" customWidth="1"/>
+    <col min="2067" max="2067" width="33.140625" style="2" customWidth="1"/>
+    <col min="2068" max="2068" width="8.140625" style="2" customWidth="1"/>
+    <col min="2069" max="2069" width="6.85546875" style="2" customWidth="1"/>
+    <col min="2070" max="2070" width="14.28515625" style="2" customWidth="1"/>
+    <col min="2071" max="2071" width="18.85546875" style="2" customWidth="1"/>
+    <col min="2072" max="2072" width="13.140625" style="2" customWidth="1"/>
+    <col min="2073" max="2319" width="10.85546875" style="2"/>
+    <col min="2320" max="2320" width="5.85546875" style="2" customWidth="1"/>
+    <col min="2321" max="2321" width="13.28515625" style="2" customWidth="1"/>
+    <col min="2322" max="2322" width="4.85546875" style="2" customWidth="1"/>
+    <col min="2323" max="2323" width="33.140625" style="2" customWidth="1"/>
+    <col min="2324" max="2324" width="8.140625" style="2" customWidth="1"/>
+    <col min="2325" max="2325" width="6.85546875" style="2" customWidth="1"/>
+    <col min="2326" max="2326" width="14.28515625" style="2" customWidth="1"/>
+    <col min="2327" max="2327" width="18.85546875" style="2" customWidth="1"/>
+    <col min="2328" max="2328" width="13.140625" style="2" customWidth="1"/>
+    <col min="2329" max="2575" width="10.85546875" style="2"/>
+    <col min="2576" max="2576" width="5.85546875" style="2" customWidth="1"/>
+    <col min="2577" max="2577" width="13.28515625" style="2" customWidth="1"/>
+    <col min="2578" max="2578" width="4.85546875" style="2" customWidth="1"/>
+    <col min="2579" max="2579" width="33.140625" style="2" customWidth="1"/>
+    <col min="2580" max="2580" width="8.140625" style="2" customWidth="1"/>
+    <col min="2581" max="2581" width="6.85546875" style="2" customWidth="1"/>
+    <col min="2582" max="2582" width="14.28515625" style="2" customWidth="1"/>
+    <col min="2583" max="2583" width="18.85546875" style="2" customWidth="1"/>
+    <col min="2584" max="2584" width="13.140625" style="2" customWidth="1"/>
+    <col min="2585" max="2831" width="10.85546875" style="2"/>
+    <col min="2832" max="2832" width="5.85546875" style="2" customWidth="1"/>
+    <col min="2833" max="2833" width="13.28515625" style="2" customWidth="1"/>
+    <col min="2834" max="2834" width="4.85546875" style="2" customWidth="1"/>
+    <col min="2835" max="2835" width="33.140625" style="2" customWidth="1"/>
+    <col min="2836" max="2836" width="8.140625" style="2" customWidth="1"/>
+    <col min="2837" max="2837" width="6.85546875" style="2" customWidth="1"/>
+    <col min="2838" max="2838" width="14.28515625" style="2" customWidth="1"/>
+    <col min="2839" max="2839" width="18.85546875" style="2" customWidth="1"/>
+    <col min="2840" max="2840" width="13.140625" style="2" customWidth="1"/>
+    <col min="2841" max="3087" width="10.85546875" style="2"/>
+    <col min="3088" max="3088" width="5.85546875" style="2" customWidth="1"/>
+    <col min="3089" max="3089" width="13.28515625" style="2" customWidth="1"/>
+    <col min="3090" max="3090" width="4.85546875" style="2" customWidth="1"/>
+    <col min="3091" max="3091" width="33.140625" style="2" customWidth="1"/>
+    <col min="3092" max="3092" width="8.140625" style="2" customWidth="1"/>
+    <col min="3093" max="3093" width="6.85546875" style="2" customWidth="1"/>
+    <col min="3094" max="3094" width="14.28515625" style="2" customWidth="1"/>
+    <col min="3095" max="3095" width="18.85546875" style="2" customWidth="1"/>
+    <col min="3096" max="3096" width="13.140625" style="2" customWidth="1"/>
+    <col min="3097" max="3343" width="10.85546875" style="2"/>
+    <col min="3344" max="3344" width="5.85546875" style="2" customWidth="1"/>
+    <col min="3345" max="3345" width="13.28515625" style="2" customWidth="1"/>
+    <col min="3346" max="3346" width="4.85546875" style="2" customWidth="1"/>
+    <col min="3347" max="3347" width="33.140625" style="2" customWidth="1"/>
+    <col min="3348" max="3348" width="8.140625" style="2" customWidth="1"/>
+    <col min="3349" max="3349" width="6.85546875" style="2" customWidth="1"/>
+    <col min="3350" max="3350" width="14.28515625" style="2" customWidth="1"/>
+    <col min="3351" max="3351" width="18.85546875" style="2" customWidth="1"/>
+    <col min="3352" max="3352" width="13.140625" style="2" customWidth="1"/>
+    <col min="3353" max="3599" width="10.85546875" style="2"/>
+    <col min="3600" max="3600" width="5.85546875" style="2" customWidth="1"/>
+    <col min="3601" max="3601" width="13.28515625" style="2" customWidth="1"/>
+    <col min="3602" max="3602" width="4.85546875" style="2" customWidth="1"/>
+    <col min="3603" max="3603" width="33.140625" style="2" customWidth="1"/>
+    <col min="3604" max="3604" width="8.140625" style="2" customWidth="1"/>
+    <col min="3605" max="3605" width="6.85546875" style="2" customWidth="1"/>
+    <col min="3606" max="3606" width="14.28515625" style="2" customWidth="1"/>
+    <col min="3607" max="3607" width="18.85546875" style="2" customWidth="1"/>
+    <col min="3608" max="3608" width="13.140625" style="2" customWidth="1"/>
+    <col min="3609" max="3855" width="10.85546875" style="2"/>
+    <col min="3856" max="3856" width="5.85546875" style="2" customWidth="1"/>
+    <col min="3857" max="3857" width="13.28515625" style="2" customWidth="1"/>
+    <col min="3858" max="3858" width="4.85546875" style="2" customWidth="1"/>
+    <col min="3859" max="3859" width="33.140625" style="2" customWidth="1"/>
+    <col min="3860" max="3860" width="8.140625" style="2" customWidth="1"/>
+    <col min="3861" max="3861" width="6.85546875" style="2" customWidth="1"/>
+    <col min="3862" max="3862" width="14.28515625" style="2" customWidth="1"/>
+    <col min="3863" max="3863" width="18.85546875" style="2" customWidth="1"/>
+    <col min="3864" max="3864" width="13.140625" style="2" customWidth="1"/>
+    <col min="3865" max="4111" width="10.85546875" style="2"/>
+    <col min="4112" max="4112" width="5.85546875" style="2" customWidth="1"/>
+    <col min="4113" max="4113" width="13.28515625" style="2" customWidth="1"/>
+    <col min="4114" max="4114" width="4.85546875" style="2" customWidth="1"/>
+    <col min="4115" max="4115" width="33.140625" style="2" customWidth="1"/>
+    <col min="4116" max="4116" width="8.140625" style="2" customWidth="1"/>
+    <col min="4117" max="4117" width="6.85546875" style="2" customWidth="1"/>
+    <col min="4118" max="4118" width="14.28515625" style="2" customWidth="1"/>
+    <col min="4119" max="4119" width="18.85546875" style="2" customWidth="1"/>
+    <col min="4120" max="4120" width="13.140625" style="2" customWidth="1"/>
+    <col min="4121" max="4367" width="10.85546875" style="2"/>
+    <col min="4368" max="4368" width="5.85546875" style="2" customWidth="1"/>
+    <col min="4369" max="4369" width="13.28515625" style="2" customWidth="1"/>
+    <col min="4370" max="4370" width="4.85546875" style="2" customWidth="1"/>
+    <col min="4371" max="4371" width="33.140625" style="2" customWidth="1"/>
+    <col min="4372" max="4372" width="8.140625" style="2" customWidth="1"/>
+    <col min="4373" max="4373" width="6.85546875" style="2" customWidth="1"/>
+    <col min="4374" max="4374" width="14.28515625" style="2" customWidth="1"/>
+    <col min="4375" max="4375" width="18.85546875" style="2" customWidth="1"/>
+    <col min="4376" max="4376" width="13.140625" style="2" customWidth="1"/>
+    <col min="4377" max="4623" width="10.85546875" style="2"/>
+    <col min="4624" max="4624" width="5.85546875" style="2" customWidth="1"/>
+    <col min="4625" max="4625" width="13.28515625" style="2" customWidth="1"/>
+    <col min="4626" max="4626" width="4.85546875" style="2" customWidth="1"/>
+    <col min="4627" max="4627" width="33.140625" style="2" customWidth="1"/>
+    <col min="4628" max="4628" width="8.140625" style="2" customWidth="1"/>
+    <col min="4629" max="4629" width="6.85546875" style="2" customWidth="1"/>
+    <col min="4630" max="4630" width="14.28515625" style="2" customWidth="1"/>
+    <col min="4631" max="4631" width="18.85546875" style="2" customWidth="1"/>
+    <col min="4632" max="4632" width="13.140625" style="2" customWidth="1"/>
+    <col min="4633" max="4879" width="10.85546875" style="2"/>
+    <col min="4880" max="4880" width="5.85546875" style="2" customWidth="1"/>
+    <col min="4881" max="4881" width="13.28515625" style="2" customWidth="1"/>
+    <col min="4882" max="4882" width="4.85546875" style="2" customWidth="1"/>
+    <col min="4883" max="4883" width="33.140625" style="2" customWidth="1"/>
+    <col min="4884" max="4884" width="8.140625" style="2" customWidth="1"/>
+    <col min="4885" max="4885" width="6.85546875" style="2" customWidth="1"/>
+    <col min="4886" max="4886" width="14.28515625" style="2" customWidth="1"/>
+    <col min="4887" max="4887" width="18.85546875" style="2" customWidth="1"/>
+    <col min="4888" max="4888" width="13.140625" style="2" customWidth="1"/>
+    <col min="4889" max="5135" width="10.85546875" style="2"/>
+    <col min="5136" max="5136" width="5.85546875" style="2" customWidth="1"/>
+    <col min="5137" max="5137" width="13.28515625" style="2" customWidth="1"/>
+    <col min="5138" max="5138" width="4.85546875" style="2" customWidth="1"/>
+    <col min="5139" max="5139" width="33.140625" style="2" customWidth="1"/>
+    <col min="5140" max="5140" width="8.140625" style="2" customWidth="1"/>
+    <col min="5141" max="5141" width="6.85546875" style="2" customWidth="1"/>
+    <col min="5142" max="5142" width="14.28515625" style="2" customWidth="1"/>
+    <col min="5143" max="5143" width="18.85546875" style="2" customWidth="1"/>
+    <col min="5144" max="5144" width="13.140625" style="2" customWidth="1"/>
+    <col min="5145" max="5391" width="10.85546875" style="2"/>
+    <col min="5392" max="5392" width="5.85546875" style="2" customWidth="1"/>
+    <col min="5393" max="5393" width="13.28515625" style="2" customWidth="1"/>
+    <col min="5394" max="5394" width="4.85546875" style="2" customWidth="1"/>
+    <col min="5395" max="5395" width="33.140625" style="2" customWidth="1"/>
+    <col min="5396" max="5396" width="8.140625" style="2" customWidth="1"/>
+    <col min="5397" max="5397" width="6.85546875" style="2" customWidth="1"/>
+    <col min="5398" max="5398" width="14.28515625" style="2" customWidth="1"/>
+    <col min="5399" max="5399" width="18.85546875" style="2" customWidth="1"/>
+    <col min="5400" max="5400" width="13.140625" style="2" customWidth="1"/>
+    <col min="5401" max="5647" width="10.85546875" style="2"/>
+    <col min="5648" max="5648" width="5.85546875" style="2" customWidth="1"/>
+    <col min="5649" max="5649" width="13.28515625" style="2" customWidth="1"/>
+    <col min="5650" max="5650" width="4.85546875" style="2" customWidth="1"/>
+    <col min="5651" max="5651" width="33.140625" style="2" customWidth="1"/>
+    <col min="5652" max="5652" width="8.140625" style="2" customWidth="1"/>
+    <col min="5653" max="5653" width="6.85546875" style="2" customWidth="1"/>
+    <col min="5654" max="5654" width="14.28515625" style="2" customWidth="1"/>
+    <col min="5655" max="5655" width="18.85546875" style="2" customWidth="1"/>
+    <col min="5656" max="5656" width="13.140625" style="2" customWidth="1"/>
+    <col min="5657" max="5903" width="10.85546875" style="2"/>
+    <col min="5904" max="5904" width="5.85546875" style="2" customWidth="1"/>
+    <col min="5905" max="5905" width="13.28515625" style="2" customWidth="1"/>
+    <col min="5906" max="5906" width="4.85546875" style="2" customWidth="1"/>
+    <col min="5907" max="5907" width="33.140625" style="2" customWidth="1"/>
+    <col min="5908" max="5908" width="8.140625" style="2" customWidth="1"/>
+    <col min="5909" max="5909" width="6.85546875" style="2" customWidth="1"/>
+    <col min="5910" max="5910" width="14.28515625" style="2" customWidth="1"/>
+    <col min="5911" max="5911" width="18.85546875" style="2" customWidth="1"/>
+    <col min="5912" max="5912" width="13.140625" style="2" customWidth="1"/>
+    <col min="5913" max="6159" width="10.85546875" style="2"/>
+    <col min="6160" max="6160" width="5.85546875" style="2" customWidth="1"/>
+    <col min="6161" max="6161" width="13.28515625" style="2" customWidth="1"/>
+    <col min="6162" max="6162" width="4.85546875" style="2" customWidth="1"/>
+    <col min="6163" max="6163" width="33.140625" style="2" customWidth="1"/>
+    <col min="6164" max="6164" width="8.140625" style="2" customWidth="1"/>
+    <col min="6165" max="6165" width="6.85546875" style="2" customWidth="1"/>
+    <col min="6166" max="6166" width="14.28515625" style="2" customWidth="1"/>
+    <col min="6167" max="6167" width="18.85546875" style="2" customWidth="1"/>
+    <col min="6168" max="6168" width="13.140625" style="2" customWidth="1"/>
+    <col min="6169" max="6415" width="10.85546875" style="2"/>
+    <col min="6416" max="6416" width="5.85546875" style="2" customWidth="1"/>
+    <col min="6417" max="6417" width="13.28515625" style="2" customWidth="1"/>
+    <col min="6418" max="6418" width="4.85546875" style="2" customWidth="1"/>
+    <col min="6419" max="6419" width="33.140625" style="2" customWidth="1"/>
+    <col min="6420" max="6420" width="8.140625" style="2" customWidth="1"/>
+    <col min="6421" max="6421" width="6.85546875" style="2" customWidth="1"/>
+    <col min="6422" max="6422" width="14.28515625" style="2" customWidth="1"/>
+    <col min="6423" max="6423" width="18.85546875" style="2" customWidth="1"/>
+    <col min="6424" max="6424" width="13.140625" style="2" customWidth="1"/>
+    <col min="6425" max="6671" width="10.85546875" style="2"/>
+    <col min="6672" max="6672" width="5.85546875" style="2" customWidth="1"/>
+    <col min="6673" max="6673" width="13.28515625" style="2" customWidth="1"/>
+    <col min="6674" max="6674" width="4.85546875" style="2" customWidth="1"/>
+    <col min="6675" max="6675" width="33.140625" style="2" customWidth="1"/>
+    <col min="6676" max="6676" width="8.140625" style="2" customWidth="1"/>
+    <col min="6677" max="6677" width="6.85546875" style="2" customWidth="1"/>
+    <col min="6678" max="6678" width="14.28515625" style="2" customWidth="1"/>
+    <col min="6679" max="6679" width="18.85546875" style="2" customWidth="1"/>
+    <col min="6680" max="6680" width="13.140625" style="2" customWidth="1"/>
+    <col min="6681" max="6927" width="10.85546875" style="2"/>
+    <col min="6928" max="6928" width="5.85546875" style="2" customWidth="1"/>
+    <col min="6929" max="6929" width="13.28515625" style="2" customWidth="1"/>
+    <col min="6930" max="6930" width="4.85546875" style="2" customWidth="1"/>
+    <col min="6931" max="6931" width="33.140625" style="2" customWidth="1"/>
+    <col min="6932" max="6932" width="8.140625" style="2" customWidth="1"/>
+    <col min="6933" max="6933" width="6.85546875" style="2" customWidth="1"/>
+    <col min="6934" max="6934" width="14.28515625" style="2" customWidth="1"/>
+    <col min="6935" max="6935" width="18.85546875" style="2" customWidth="1"/>
+    <col min="6936" max="6936" width="13.140625" style="2" customWidth="1"/>
+    <col min="6937" max="7183" width="10.85546875" style="2"/>
+    <col min="7184" max="7184" width="5.85546875" style="2" customWidth="1"/>
+    <col min="7185" max="7185" width="13.28515625" style="2" customWidth="1"/>
+    <col min="7186" max="7186" width="4.85546875" style="2" customWidth="1"/>
+    <col min="7187" max="7187" width="33.140625" style="2" customWidth="1"/>
+    <col min="7188" max="7188" width="8.140625" style="2" customWidth="1"/>
+    <col min="7189" max="7189" width="6.85546875" style="2" customWidth="1"/>
+    <col min="7190" max="7190" width="14.28515625" style="2" customWidth="1"/>
+    <col min="7191" max="7191" width="18.85546875" style="2" customWidth="1"/>
+    <col min="7192" max="7192" width="13.140625" style="2" customWidth="1"/>
+    <col min="7193" max="7439" width="10.85546875" style="2"/>
+    <col min="7440" max="7440" width="5.85546875" style="2" customWidth="1"/>
+    <col min="7441" max="7441" width="13.28515625" style="2" customWidth="1"/>
+    <col min="7442" max="7442" width="4.85546875" style="2" customWidth="1"/>
+    <col min="7443" max="7443" width="33.140625" style="2" customWidth="1"/>
+    <col min="7444" max="7444" width="8.140625" style="2" customWidth="1"/>
+    <col min="7445" max="7445" width="6.85546875" style="2" customWidth="1"/>
+    <col min="7446" max="7446" width="14.28515625" style="2" customWidth="1"/>
+    <col min="7447" max="7447" width="18.85546875" style="2" customWidth="1"/>
+    <col min="7448" max="7448" width="13.140625" style="2" customWidth="1"/>
+    <col min="7449" max="7695" width="10.85546875" style="2"/>
+    <col min="7696" max="7696" width="5.85546875" style="2" customWidth="1"/>
+    <col min="7697" max="7697" width="13.28515625" style="2" customWidth="1"/>
+    <col min="7698" max="7698" width="4.85546875" style="2" customWidth="1"/>
+    <col min="7699" max="7699" width="33.140625" style="2" customWidth="1"/>
+    <col min="7700" max="7700" width="8.140625" style="2" customWidth="1"/>
+    <col min="7701" max="7701" width="6.85546875" style="2" customWidth="1"/>
+    <col min="7702" max="7702" width="14.28515625" style="2" customWidth="1"/>
+    <col min="7703" max="7703" width="18.85546875" style="2" customWidth="1"/>
+    <col min="7704" max="7704" width="13.140625" style="2" customWidth="1"/>
+    <col min="7705" max="7951" width="10.85546875" style="2"/>
+    <col min="7952" max="7952" width="5.85546875" style="2" customWidth="1"/>
+    <col min="7953" max="7953" width="13.28515625" style="2" customWidth="1"/>
+    <col min="7954" max="7954" width="4.85546875" style="2" customWidth="1"/>
+    <col min="7955" max="7955" width="33.140625" style="2" customWidth="1"/>
+    <col min="7956" max="7956" width="8.140625" style="2" customWidth="1"/>
+    <col min="7957" max="7957" width="6.85546875" style="2" customWidth="1"/>
+    <col min="7958" max="7958" width="14.28515625" style="2" customWidth="1"/>
+    <col min="7959" max="7959" width="18.85546875" style="2" customWidth="1"/>
+    <col min="7960" max="7960" width="13.140625" style="2" customWidth="1"/>
+    <col min="7961" max="8207" width="10.85546875" style="2"/>
+    <col min="8208" max="8208" width="5.85546875" style="2" customWidth="1"/>
+    <col min="8209" max="8209" width="13.28515625" style="2" customWidth="1"/>
+    <col min="8210" max="8210" width="4.85546875" style="2" customWidth="1"/>
+    <col min="8211" max="8211" width="33.140625" style="2" customWidth="1"/>
+    <col min="8212" max="8212" width="8.140625" style="2" customWidth="1"/>
+    <col min="8213" max="8213" width="6.85546875" style="2" customWidth="1"/>
+    <col min="8214" max="8214" width="14.28515625" style="2" customWidth="1"/>
+    <col min="8215" max="8215" width="18.85546875" style="2" customWidth="1"/>
+    <col min="8216" max="8216" width="13.140625" style="2" customWidth="1"/>
+    <col min="8217" max="8463" width="10.85546875" style="2"/>
+    <col min="8464" max="8464" width="5.85546875" style="2" customWidth="1"/>
+    <col min="8465" max="8465" width="13.28515625" style="2" customWidth="1"/>
+    <col min="8466" max="8466" width="4.85546875" style="2" customWidth="1"/>
+    <col min="8467" max="8467" width="33.140625" style="2" customWidth="1"/>
+    <col min="8468" max="8468" width="8.140625" style="2" customWidth="1"/>
+    <col min="8469" max="8469" width="6.85546875" style="2" customWidth="1"/>
+    <col min="8470" max="8470" width="14.28515625" style="2" customWidth="1"/>
+    <col min="8471" max="8471" width="18.85546875" style="2" customWidth="1"/>
+    <col min="8472" max="8472" width="13.140625" style="2" customWidth="1"/>
+    <col min="8473" max="8719" width="10.85546875" style="2"/>
+    <col min="8720" max="8720" width="5.85546875" style="2" customWidth="1"/>
+    <col min="8721" max="8721" width="13.28515625" style="2" customWidth="1"/>
+    <col min="8722" max="8722" width="4.85546875" style="2" customWidth="1"/>
+    <col min="8723" max="8723" width="33.140625" style="2" customWidth="1"/>
+    <col min="8724" max="8724" width="8.140625" style="2" customWidth="1"/>
+    <col min="8725" max="8725" width="6.85546875" style="2" customWidth="1"/>
+    <col min="8726" max="8726" width="14.28515625" style="2" customWidth="1"/>
+    <col min="8727" max="8727" width="18.85546875" style="2" customWidth="1"/>
+    <col min="8728" max="8728" width="13.140625" style="2" customWidth="1"/>
+    <col min="8729" max="8975" width="10.85546875" style="2"/>
+    <col min="8976" max="8976" width="5.85546875" style="2" customWidth="1"/>
+    <col min="8977" max="8977" width="13.28515625" style="2" customWidth="1"/>
+    <col min="8978" max="8978" width="4.85546875" style="2" customWidth="1"/>
+    <col min="8979" max="8979" width="33.140625" style="2" customWidth="1"/>
+    <col min="8980" max="8980" width="8.140625" style="2" customWidth="1"/>
+    <col min="8981" max="8981" width="6.85546875" style="2" customWidth="1"/>
+    <col min="8982" max="8982" width="14.28515625" style="2" customWidth="1"/>
+    <col min="8983" max="8983" width="18.85546875" style="2" customWidth="1"/>
+    <col min="8984" max="8984" width="13.140625" style="2" customWidth="1"/>
+    <col min="8985" max="9231" width="10.85546875" style="2"/>
+    <col min="9232" max="9232" width="5.85546875" style="2" customWidth="1"/>
+    <col min="9233" max="9233" width="13.28515625" style="2" customWidth="1"/>
+    <col min="9234" max="9234" width="4.85546875" style="2" customWidth="1"/>
+    <col min="9235" max="9235" width="33.140625" style="2" customWidth="1"/>
+    <col min="9236" max="9236" width="8.140625" style="2" customWidth="1"/>
+    <col min="9237" max="9237" width="6.85546875" style="2" customWidth="1"/>
+    <col min="9238" max="9238" width="14.28515625" style="2" customWidth="1"/>
+    <col min="9239" max="9239" width="18.85546875" style="2" customWidth="1"/>
+    <col min="9240" max="9240" width="13.140625" style="2" customWidth="1"/>
+    <col min="9241" max="9487" width="10.85546875" style="2"/>
+    <col min="9488" max="9488" width="5.85546875" style="2" customWidth="1"/>
+    <col min="9489" max="9489" width="13.28515625" style="2" customWidth="1"/>
+    <col min="9490" max="9490" width="4.85546875" style="2" customWidth="1"/>
+    <col min="9491" max="9491" width="33.140625" style="2" customWidth="1"/>
+    <col min="9492" max="9492" width="8.140625" style="2" customWidth="1"/>
+    <col min="9493" max="9493" width="6.85546875" style="2" customWidth="1"/>
+    <col min="9494" max="9494" width="14.28515625" style="2" customWidth="1"/>
+    <col min="9495" max="9495" width="18.85546875" style="2" customWidth="1"/>
+    <col min="9496" max="9496" width="13.140625" style="2" customWidth="1"/>
+    <col min="9497" max="9743" width="10.85546875" style="2"/>
+    <col min="9744" max="9744" width="5.85546875" style="2" customWidth="1"/>
+    <col min="9745" max="9745" width="13.28515625" style="2" customWidth="1"/>
+    <col min="9746" max="9746" width="4.85546875" style="2" customWidth="1"/>
+    <col min="9747" max="9747" width="33.140625" style="2" customWidth="1"/>
+    <col min="9748" max="9748" width="8.140625" style="2" customWidth="1"/>
+    <col min="9749" max="9749" width="6.85546875" style="2" customWidth="1"/>
+    <col min="9750" max="9750" width="14.28515625" style="2" customWidth="1"/>
+    <col min="9751" max="9751" width="18.85546875" style="2" customWidth="1"/>
+    <col min="9752" max="9752" width="13.140625" style="2" customWidth="1"/>
+    <col min="9753" max="9999" width="10.85546875" style="2"/>
+    <col min="10000" max="10000" width="5.85546875" style="2" customWidth="1"/>
+    <col min="10001" max="10001" width="13.28515625" style="2" customWidth="1"/>
+    <col min="10002" max="10002" width="4.85546875" style="2" customWidth="1"/>
+    <col min="10003" max="10003" width="33.140625" style="2" customWidth="1"/>
+    <col min="10004" max="10004" width="8.140625" style="2" customWidth="1"/>
+    <col min="10005" max="10005" width="6.85546875" style="2" customWidth="1"/>
+    <col min="10006" max="10006" width="14.28515625" style="2" customWidth="1"/>
+    <col min="10007" max="10007" width="18.85546875" style="2" customWidth="1"/>
+    <col min="10008" max="10008" width="13.140625" style="2" customWidth="1"/>
+    <col min="10009" max="10255" width="10.85546875" style="2"/>
+    <col min="10256" max="10256" width="5.85546875" style="2" customWidth="1"/>
+    <col min="10257" max="10257" width="13.28515625" style="2" customWidth="1"/>
+    <col min="10258" max="10258" width="4.85546875" style="2" customWidth="1"/>
+    <col min="10259" max="10259" width="33.140625" style="2" customWidth="1"/>
+    <col min="10260" max="10260" width="8.140625" style="2" customWidth="1"/>
+    <col min="10261" max="10261" width="6.85546875" style="2" customWidth="1"/>
+    <col min="10262" max="10262" width="14.28515625" style="2" customWidth="1"/>
+    <col min="10263" max="10263" width="18.85546875" style="2" customWidth="1"/>
+    <col min="10264" max="10264" width="13.140625" style="2" customWidth="1"/>
+    <col min="10265" max="10511" width="10.85546875" style="2"/>
+    <col min="10512" max="10512" width="5.85546875" style="2" customWidth="1"/>
+    <col min="10513" max="10513" width="13.28515625" style="2" customWidth="1"/>
+    <col min="10514" max="10514" width="4.85546875" style="2" customWidth="1"/>
+    <col min="10515" max="10515" width="33.140625" style="2" customWidth="1"/>
+    <col min="10516" max="10516" width="8.140625" style="2" customWidth="1"/>
+    <col min="10517" max="10517" width="6.85546875" style="2" customWidth="1"/>
+    <col min="10518" max="10518" width="14.28515625" style="2" customWidth="1"/>
+    <col min="10519" max="10519" width="18.85546875" style="2" customWidth="1"/>
+    <col min="10520" max="10520" width="13.140625" style="2" customWidth="1"/>
+    <col min="10521" max="10767" width="10.85546875" style="2"/>
+    <col min="10768" max="10768" width="5.85546875" style="2" customWidth="1"/>
+    <col min="10769" max="10769" width="13.28515625" style="2" customWidth="1"/>
+    <col min="10770" max="10770" width="4.85546875" style="2" customWidth="1"/>
+    <col min="10771" max="10771" width="33.140625" style="2" customWidth="1"/>
+    <col min="10772" max="10772" width="8.140625" style="2" customWidth="1"/>
+    <col min="10773" max="10773" width="6.85546875" style="2" customWidth="1"/>
+    <col min="10774" max="10774" width="14.28515625" style="2" customWidth="1"/>
+    <col min="10775" max="10775" width="18.85546875" style="2" customWidth="1"/>
+    <col min="10776" max="10776" width="13.140625" style="2" customWidth="1"/>
+    <col min="10777" max="11023" width="10.85546875" style="2"/>
+    <col min="11024" max="11024" width="5.85546875" style="2" customWidth="1"/>
+    <col min="11025" max="11025" width="13.28515625" style="2" customWidth="1"/>
+    <col min="11026" max="11026" width="4.85546875" style="2" customWidth="1"/>
+    <col min="11027" max="11027" width="33.140625" style="2" customWidth="1"/>
+    <col min="11028" max="11028" width="8.140625" style="2" customWidth="1"/>
+    <col min="11029" max="11029" width="6.85546875" style="2" customWidth="1"/>
+    <col min="11030" max="11030" width="14.28515625" style="2" customWidth="1"/>
+    <col min="11031" max="11031" width="18.85546875" style="2" customWidth="1"/>
+    <col min="11032" max="11032" width="13.140625" style="2" customWidth="1"/>
+    <col min="11033" max="11279" width="10.85546875" style="2"/>
+    <col min="11280" max="11280" width="5.85546875" style="2" customWidth="1"/>
+    <col min="11281" max="11281" width="13.28515625" style="2" customWidth="1"/>
+    <col min="11282" max="11282" width="4.85546875" style="2" customWidth="1"/>
+    <col min="11283" max="11283" width="33.140625" style="2" customWidth="1"/>
+    <col min="11284" max="11284" width="8.140625" style="2" customWidth="1"/>
+    <col min="11285" max="11285" width="6.85546875" style="2" customWidth="1"/>
+    <col min="11286" max="11286" width="14.28515625" style="2" customWidth="1"/>
+    <col min="11287" max="11287" width="18.85546875" style="2" customWidth="1"/>
+    <col min="11288" max="11288" width="13.140625" style="2" customWidth="1"/>
+    <col min="11289" max="11535" width="10.85546875" style="2"/>
+    <col min="11536" max="11536" width="5.85546875" style="2" customWidth="1"/>
+    <col min="11537" max="11537" width="13.28515625" style="2" customWidth="1"/>
+    <col min="11538" max="11538" width="4.85546875" style="2" customWidth="1"/>
+    <col min="11539" max="11539" width="33.140625" style="2" customWidth="1"/>
+    <col min="11540" max="11540" width="8.140625" style="2" customWidth="1"/>
+    <col min="11541" max="11541" width="6.85546875" style="2" customWidth="1"/>
+    <col min="11542" max="11542" width="14.28515625" style="2" customWidth="1"/>
+    <col min="11543" max="11543" width="18.85546875" style="2" customWidth="1"/>
+    <col min="11544" max="11544" width="13.140625" style="2" customWidth="1"/>
+    <col min="11545" max="11791" width="10.85546875" style="2"/>
+    <col min="11792" max="11792" width="5.85546875" style="2" customWidth="1"/>
+    <col min="11793" max="11793" width="13.28515625" style="2" customWidth="1"/>
+    <col min="11794" max="11794" width="4.85546875" style="2" customWidth="1"/>
+    <col min="11795" max="11795" width="33.140625" style="2" customWidth="1"/>
+    <col min="11796" max="11796" width="8.140625" style="2" customWidth="1"/>
+    <col min="11797" max="11797" width="6.85546875" style="2" customWidth="1"/>
+    <col min="11798" max="11798" width="14.28515625" style="2" customWidth="1"/>
+    <col min="11799" max="11799" width="18.85546875" style="2" customWidth="1"/>
+    <col min="11800" max="11800" width="13.140625" style="2" customWidth="1"/>
+    <col min="11801" max="12047" width="10.85546875" style="2"/>
+    <col min="12048" max="12048" width="5.85546875" style="2" customWidth="1"/>
+    <col min="12049" max="12049" width="13.28515625" style="2" customWidth="1"/>
+    <col min="12050" max="12050" width="4.85546875" style="2" customWidth="1"/>
+    <col min="12051" max="12051" width="33.140625" style="2" customWidth="1"/>
+    <col min="12052" max="12052" width="8.140625" style="2" customWidth="1"/>
+    <col min="12053" max="12053" width="6.85546875" style="2" customWidth="1"/>
+    <col min="12054" max="12054" width="14.28515625" style="2" customWidth="1"/>
+    <col min="12055" max="12055" width="18.85546875" style="2" customWidth="1"/>
+    <col min="12056" max="12056" width="13.140625" style="2" customWidth="1"/>
+    <col min="12057" max="12303" width="10.85546875" style="2"/>
+    <col min="12304" max="12304" width="5.85546875" style="2" customWidth="1"/>
+    <col min="12305" max="12305" width="13.28515625" style="2" customWidth="1"/>
+    <col min="12306" max="12306" width="4.85546875" style="2" customWidth="1"/>
+    <col min="12307" max="12307" width="33.140625" style="2" customWidth="1"/>
+    <col min="12308" max="12308" width="8.140625" style="2" customWidth="1"/>
+    <col min="12309" max="12309" width="6.85546875" style="2" customWidth="1"/>
+    <col min="12310" max="12310" width="14.28515625" style="2" customWidth="1"/>
+    <col min="12311" max="12311" width="18.85546875" style="2" customWidth="1"/>
+    <col min="12312" max="12312" width="13.140625" style="2" customWidth="1"/>
+    <col min="12313" max="12559" width="10.85546875" style="2"/>
+    <col min="12560" max="12560" width="5.85546875" style="2" customWidth="1"/>
+    <col min="12561" max="12561" width="13.28515625" style="2" customWidth="1"/>
+    <col min="12562" max="12562" width="4.85546875" style="2" customWidth="1"/>
+    <col min="12563" max="12563" width="33.140625" style="2" customWidth="1"/>
+    <col min="12564" max="12564" width="8.140625" style="2" customWidth="1"/>
+    <col min="12565" max="12565" width="6.85546875" style="2" customWidth="1"/>
+    <col min="12566" max="12566" width="14.28515625" style="2" customWidth="1"/>
+    <col min="12567" max="12567" width="18.85546875" style="2" customWidth="1"/>
+    <col min="12568" max="12568" width="13.140625" style="2" customWidth="1"/>
+    <col min="12569" max="12815" width="10.85546875" style="2"/>
+    <col min="12816" max="12816" width="5.85546875" style="2" customWidth="1"/>
+    <col min="12817" max="12817" width="13.28515625" style="2" customWidth="1"/>
+    <col min="12818" max="12818" width="4.85546875" style="2" customWidth="1"/>
+    <col min="12819" max="12819" width="33.140625" style="2" customWidth="1"/>
+    <col min="12820" max="12820" width="8.140625" style="2" customWidth="1"/>
+    <col min="12821" max="12821" width="6.85546875" style="2" customWidth="1"/>
+    <col min="12822" max="12822" width="14.28515625" style="2" customWidth="1"/>
+    <col min="12823" max="12823" width="18.85546875" style="2" customWidth="1"/>
+    <col min="12824" max="12824" width="13.140625" style="2" customWidth="1"/>
+    <col min="12825" max="13071" width="10.85546875" style="2"/>
+    <col min="13072" max="13072" width="5.85546875" style="2" customWidth="1"/>
+    <col min="13073" max="13073" width="13.28515625" style="2" customWidth="1"/>
+    <col min="13074" max="13074" width="4.85546875" style="2" customWidth="1"/>
+    <col min="13075" max="13075" width="33.140625" style="2" customWidth="1"/>
+    <col min="13076" max="13076" width="8.140625" style="2" customWidth="1"/>
+    <col min="13077" max="13077" width="6.85546875" style="2" customWidth="1"/>
+    <col min="13078" max="13078" width="14.28515625" style="2" customWidth="1"/>
+    <col min="13079" max="13079" width="18.85546875" style="2" customWidth="1"/>
+    <col min="13080" max="13080" width="13.140625" style="2" customWidth="1"/>
+    <col min="13081" max="13327" width="10.85546875" style="2"/>
+    <col min="13328" max="13328" width="5.85546875" style="2" customWidth="1"/>
+    <col min="13329" max="13329" width="13.28515625" style="2" customWidth="1"/>
+    <col min="13330" max="13330" width="4.85546875" style="2" customWidth="1"/>
+    <col min="13331" max="13331" width="33.140625" style="2" customWidth="1"/>
+    <col min="13332" max="13332" width="8.140625" style="2" customWidth="1"/>
+    <col min="13333" max="13333" width="6.85546875" style="2" customWidth="1"/>
+    <col min="13334" max="13334" width="14.28515625" style="2" customWidth="1"/>
+    <col min="13335" max="13335" width="18.85546875" style="2" customWidth="1"/>
+    <col min="13336" max="13336" width="13.140625" style="2" customWidth="1"/>
+    <col min="13337" max="13583" width="10.85546875" style="2"/>
+    <col min="13584" max="13584" width="5.85546875" style="2" customWidth="1"/>
+    <col min="13585" max="13585" width="13.28515625" style="2" customWidth="1"/>
+    <col min="13586" max="13586" width="4.85546875" style="2" customWidth="1"/>
+    <col min="13587" max="13587" width="33.140625" style="2" customWidth="1"/>
+    <col min="13588" max="13588" width="8.140625" style="2" customWidth="1"/>
+    <col min="13589" max="13589" width="6.85546875" style="2" customWidth="1"/>
+    <col min="13590" max="13590" width="14.28515625" style="2" customWidth="1"/>
+    <col min="13591" max="13591" width="18.85546875" style="2" customWidth="1"/>
+    <col min="13592" max="13592" width="13.140625" style="2" customWidth="1"/>
+    <col min="13593" max="13839" width="10.85546875" style="2"/>
+    <col min="13840" max="13840" width="5.85546875" style="2" customWidth="1"/>
+    <col min="13841" max="13841" width="13.28515625" style="2" customWidth="1"/>
+    <col min="13842" max="13842" width="4.85546875" style="2" customWidth="1"/>
+    <col min="13843" max="13843" width="33.140625" style="2" customWidth="1"/>
+    <col min="13844" max="13844" width="8.140625" style="2" customWidth="1"/>
+    <col min="13845" max="13845" width="6.85546875" style="2" customWidth="1"/>
+    <col min="13846" max="13846" width="14.28515625" style="2" customWidth="1"/>
+    <col min="13847" max="13847" width="18.85546875" style="2" customWidth="1"/>
+    <col min="13848" max="13848" width="13.140625" style="2" customWidth="1"/>
+    <col min="13849" max="14095" width="10.85546875" style="2"/>
+    <col min="14096" max="14096" width="5.85546875" style="2" customWidth="1"/>
+    <col min="14097" max="14097" width="13.28515625" style="2" customWidth="1"/>
+    <col min="14098" max="14098" width="4.85546875" style="2" customWidth="1"/>
+    <col min="14099" max="14099" width="33.140625" style="2" customWidth="1"/>
+    <col min="14100" max="14100" width="8.140625" style="2" customWidth="1"/>
+    <col min="14101" max="14101" width="6.85546875" style="2" customWidth="1"/>
+    <col min="14102" max="14102" width="14.28515625" style="2" customWidth="1"/>
+    <col min="14103" max="14103" width="18.85546875" style="2" customWidth="1"/>
+    <col min="14104" max="14104" width="13.140625" style="2" customWidth="1"/>
+    <col min="14105" max="14351" width="10.85546875" style="2"/>
+    <col min="14352" max="14352" width="5.85546875" style="2" customWidth="1"/>
+    <col min="14353" max="14353" width="13.28515625" style="2" customWidth="1"/>
+    <col min="14354" max="14354" width="4.85546875" style="2" customWidth="1"/>
+    <col min="14355" max="14355" width="33.140625" style="2" customWidth="1"/>
+    <col min="14356" max="14356" width="8.140625" style="2" customWidth="1"/>
+    <col min="14357" max="14357" width="6.85546875" style="2" customWidth="1"/>
+    <col min="14358" max="14358" width="14.28515625" style="2" customWidth="1"/>
+    <col min="14359" max="14359" width="18.85546875" style="2" customWidth="1"/>
+    <col min="14360" max="14360" width="13.140625" style="2" customWidth="1"/>
+    <col min="14361" max="14607" width="10.85546875" style="2"/>
+    <col min="14608" max="14608" width="5.85546875" style="2" customWidth="1"/>
+    <col min="14609" max="14609" width="13.28515625" style="2" customWidth="1"/>
+    <col min="14610" max="14610" width="4.85546875" style="2" customWidth="1"/>
+    <col min="14611" max="14611" width="33.140625" style="2" customWidth="1"/>
+    <col min="14612" max="14612" width="8.140625" style="2" customWidth="1"/>
+    <col min="14613" max="14613" width="6.85546875" style="2" customWidth="1"/>
+    <col min="14614" max="14614" width="14.28515625" style="2" customWidth="1"/>
+    <col min="14615" max="14615" width="18.85546875" style="2" customWidth="1"/>
+    <col min="14616" max="14616" width="13.140625" style="2" customWidth="1"/>
+    <col min="14617" max="14863" width="10.85546875" style="2"/>
+    <col min="14864" max="14864" width="5.85546875" style="2" customWidth="1"/>
+    <col min="14865" max="14865" width="13.28515625" style="2" customWidth="1"/>
+    <col min="14866" max="14866" width="4.85546875" style="2" customWidth="1"/>
+    <col min="14867" max="14867" width="33.140625" style="2" customWidth="1"/>
+    <col min="14868" max="14868" width="8.140625" style="2" customWidth="1"/>
+    <col min="14869" max="14869" width="6.85546875" style="2" customWidth="1"/>
+    <col min="14870" max="14870" width="14.28515625" style="2" customWidth="1"/>
+    <col min="14871" max="14871" width="18.85546875" style="2" customWidth="1"/>
+    <col min="14872" max="14872" width="13.140625" style="2" customWidth="1"/>
+    <col min="14873" max="15119" width="10.85546875" style="2"/>
+    <col min="15120" max="15120" width="5.85546875" style="2" customWidth="1"/>
+    <col min="15121" max="15121" width="13.28515625" style="2" customWidth="1"/>
+    <col min="15122" max="15122" width="4.85546875" style="2" customWidth="1"/>
+    <col min="15123" max="15123" width="33.140625" style="2" customWidth="1"/>
+    <col min="15124" max="15124" width="8.140625" style="2" customWidth="1"/>
+    <col min="15125" max="15125" width="6.85546875" style="2" customWidth="1"/>
+    <col min="15126" max="15126" width="14.28515625" style="2" customWidth="1"/>
+    <col min="15127" max="15127" width="18.85546875" style="2" customWidth="1"/>
+    <col min="15128" max="15128" width="13.140625" style="2" customWidth="1"/>
+    <col min="15129" max="15375" width="10.85546875" style="2"/>
+    <col min="15376" max="15376" width="5.85546875" style="2" customWidth="1"/>
+    <col min="15377" max="15377" width="13.28515625" style="2" customWidth="1"/>
+    <col min="15378" max="15378" width="4.85546875" style="2" customWidth="1"/>
+    <col min="15379" max="15379" width="33.140625" style="2" customWidth="1"/>
+    <col min="15380" max="15380" width="8.140625" style="2" customWidth="1"/>
+    <col min="15381" max="15381" width="6.85546875" style="2" customWidth="1"/>
+    <col min="15382" max="15382" width="14.28515625" style="2" customWidth="1"/>
+    <col min="15383" max="15383" width="18.85546875" style="2" customWidth="1"/>
+    <col min="15384" max="15384" width="13.140625" style="2" customWidth="1"/>
+    <col min="15385" max="15631" width="10.85546875" style="2"/>
+    <col min="15632" max="15632" width="5.85546875" style="2" customWidth="1"/>
+    <col min="15633" max="15633" width="13.28515625" style="2" customWidth="1"/>
+    <col min="15634" max="15634" width="4.85546875" style="2" customWidth="1"/>
+    <col min="15635" max="15635" width="33.140625" style="2" customWidth="1"/>
+    <col min="15636" max="15636" width="8.140625" style="2" customWidth="1"/>
+    <col min="15637" max="15637" width="6.85546875" style="2" customWidth="1"/>
+    <col min="15638" max="15638" width="14.28515625" style="2" customWidth="1"/>
+    <col min="15639" max="15639" width="18.85546875" style="2" customWidth="1"/>
+    <col min="15640" max="15640" width="13.140625" style="2" customWidth="1"/>
+    <col min="15641" max="15887" width="10.85546875" style="2"/>
+    <col min="15888" max="15888" width="5.85546875" style="2" customWidth="1"/>
+    <col min="15889" max="15889" width="13.28515625" style="2" customWidth="1"/>
+    <col min="15890" max="15890" width="4.85546875" style="2" customWidth="1"/>
+    <col min="15891" max="15891" width="33.140625" style="2" customWidth="1"/>
+    <col min="15892" max="15892" width="8.140625" style="2" customWidth="1"/>
+    <col min="15893" max="15893" width="6.85546875" style="2" customWidth="1"/>
+    <col min="15894" max="15894" width="14.28515625" style="2" customWidth="1"/>
+    <col min="15895" max="15895" width="18.85546875" style="2" customWidth="1"/>
+    <col min="15896" max="15896" width="13.140625" style="2" customWidth="1"/>
+    <col min="15897" max="16143" width="10.85546875" style="2"/>
+    <col min="16144" max="16144" width="5.85546875" style="2" customWidth="1"/>
+    <col min="16145" max="16145" width="13.28515625" style="2" customWidth="1"/>
+    <col min="16146" max="16146" width="4.85546875" style="2" customWidth="1"/>
+    <col min="16147" max="16147" width="33.140625" style="2" customWidth="1"/>
+    <col min="16148" max="16148" width="8.140625" style="2" customWidth="1"/>
+    <col min="16149" max="16149" width="6.85546875" style="2" customWidth="1"/>
+    <col min="16150" max="16150" width="14.28515625" style="2" customWidth="1"/>
+    <col min="16151" max="16151" width="18.85546875" style="2" customWidth="1"/>
+    <col min="16152" max="16152" width="13.140625" style="2" customWidth="1"/>
+    <col min="16153" max="16384" width="10.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:38" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="43"/>
-      <c r="S1" s="43"/>
-      <c r="T1" s="43"/>
-      <c r="U1" s="43"/>
-      <c r="V1" s="43"/>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="34"/>
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
@@ -2001,33 +2007,33 @@
       <c r="AK1" s="1"/>
       <c r="AL1" s="1"/>
     </row>
-    <row r="2" spans="1:38" ht="18" x14ac:dyDescent="0.3">
-      <c r="A2" s="43" t="s">
+    <row r="2" spans="1:38" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="43"/>
-      <c r="O2" s="43"/>
-      <c r="P2" s="43"/>
-      <c r="Q2" s="43"/>
-      <c r="R2" s="43"/>
-      <c r="S2" s="43"/>
-      <c r="T2" s="43"/>
-      <c r="U2" s="43"/>
-      <c r="V2" s="43"/>
-      <c r="W2" s="43"/>
-      <c r="X2" s="43"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
+      <c r="N2" s="34"/>
+      <c r="O2" s="34"/>
+      <c r="P2" s="34"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
+      <c r="T2" s="34"/>
+      <c r="U2" s="34"/>
+      <c r="V2" s="34"/>
+      <c r="W2" s="34"/>
+      <c r="X2" s="34"/>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
       <c r="AA2" s="1"/>
@@ -2043,33 +2049,33 @@
       <c r="AK2" s="1"/>
       <c r="AL2" s="1"/>
     </row>
-    <row r="3" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="44" t="s">
+    <row r="3" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
-      <c r="N3" s="44"/>
-      <c r="O3" s="44"/>
-      <c r="P3" s="44"/>
-      <c r="Q3" s="44"/>
-      <c r="R3" s="44"/>
-      <c r="S3" s="44"/>
-      <c r="T3" s="44"/>
-      <c r="U3" s="44"/>
-      <c r="V3" s="44"/>
-      <c r="W3" s="44"/>
-      <c r="X3" s="44"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
+      <c r="O3" s="35"/>
+      <c r="P3" s="35"/>
+      <c r="Q3" s="35"/>
+      <c r="R3" s="35"/>
+      <c r="S3" s="35"/>
+      <c r="T3" s="35"/>
+      <c r="U3" s="35"/>
+      <c r="V3" s="35"/>
+      <c r="W3" s="35"/>
+      <c r="X3" s="35"/>
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
       <c r="AA3" s="3"/>
@@ -2085,33 +2091,33 @@
       <c r="AK3" s="3"/>
       <c r="AL3" s="3"/>
     </row>
-    <row r="4" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="44" t="s">
+    <row r="4" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="44"/>
-      <c r="M4" s="44"/>
-      <c r="N4" s="44"/>
-      <c r="O4" s="44"/>
-      <c r="P4" s="44"/>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="44"/>
-      <c r="S4" s="44"/>
-      <c r="T4" s="44"/>
-      <c r="U4" s="44"/>
-      <c r="V4" s="44"/>
-      <c r="W4" s="44"/>
-      <c r="X4" s="44"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="35"/>
+      <c r="O4" s="35"/>
+      <c r="P4" s="35"/>
+      <c r="Q4" s="35"/>
+      <c r="R4" s="35"/>
+      <c r="S4" s="35"/>
+      <c r="T4" s="35"/>
+      <c r="U4" s="35"/>
+      <c r="V4" s="35"/>
+      <c r="W4" s="35"/>
+      <c r="X4" s="35"/>
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
       <c r="AA4" s="3"/>
@@ -2127,7 +2133,7 @@
       <c r="AK4" s="3"/>
       <c r="AL4" s="3"/>
     </row>
-    <row r="5" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -2167,25 +2173,25 @@
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
     </row>
-    <row r="6" spans="1:38" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:38" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="46" t="s">
+      <c r="B6" s="37"/>
+      <c r="C6" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49" t="s">
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="50" t="s">
+      <c r="H6" s="41"/>
+      <c r="I6" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="J6" s="51"/>
+      <c r="J6" s="43"/>
       <c r="K6" s="29"/>
       <c r="L6" s="29"/>
       <c r="M6" s="29"/>
@@ -2202,114 +2208,114 @@
       <c r="X6" s="28"/>
       <c r="Y6" s="5"/>
     </row>
-    <row r="7" spans="1:38" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="35" t="s">
+    <row r="7" spans="1:38" ht="29.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="35"/>
+      <c r="B7" s="44"/>
       <c r="C7" s="36"/>
-      <c r="D7" s="30" t="s">
+      <c r="D7" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="30"/>
-      <c r="O7" s="30"/>
-      <c r="P7" s="30"/>
-      <c r="Q7" s="30"/>
-      <c r="R7" s="30"/>
-      <c r="S7" s="30"/>
-      <c r="T7" s="30"/>
-      <c r="U7" s="30"/>
-      <c r="V7" s="30"/>
-      <c r="W7" s="30"/>
-      <c r="X7" s="37"/>
-    </row>
-    <row r="8" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="35" t="s">
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="45"/>
+      <c r="L7" s="45"/>
+      <c r="M7" s="45"/>
+      <c r="N7" s="45"/>
+      <c r="O7" s="45"/>
+      <c r="P7" s="45"/>
+      <c r="Q7" s="45"/>
+      <c r="R7" s="45"/>
+      <c r="S7" s="45"/>
+      <c r="T7" s="45"/>
+      <c r="U7" s="45"/>
+      <c r="V7" s="45"/>
+      <c r="W7" s="45"/>
+      <c r="X7" s="46"/>
+    </row>
+    <row r="8" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="38" t="s">
+      <c r="B8" s="44"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="39"/>
-      <c r="K8" s="39"/>
-      <c r="L8" s="39"/>
-      <c r="M8" s="39"/>
-      <c r="N8" s="39"/>
-      <c r="O8" s="39"/>
-      <c r="P8" s="39"/>
-      <c r="Q8" s="39"/>
-      <c r="R8" s="39"/>
-      <c r="S8" s="39"/>
-      <c r="T8" s="39"/>
-      <c r="U8" s="39"/>
-      <c r="V8" s="39"/>
-      <c r="W8" s="39"/>
-      <c r="X8" s="40"/>
-    </row>
-    <row r="9" spans="1:38" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="48"/>
+      <c r="N8" s="48"/>
+      <c r="O8" s="48"/>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="48"/>
+      <c r="R8" s="48"/>
+      <c r="S8" s="48"/>
+      <c r="T8" s="48"/>
+      <c r="U8" s="48"/>
+      <c r="V8" s="48"/>
+      <c r="W8" s="48"/>
+      <c r="X8" s="49"/>
+    </row>
+    <row r="9" spans="1:38" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="6"/>
     </row>
-    <row r="10" spans="1:38" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="41" t="s">
+    <row r="10" spans="1:38" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
       <c r="I10" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J10" s="52" t="s">
+      <c r="J10" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="K10" s="53"/>
-      <c r="L10" s="53"/>
-      <c r="M10" s="53"/>
-      <c r="N10" s="53"/>
-      <c r="O10" s="53"/>
-      <c r="P10" s="53"/>
-      <c r="Q10" s="53"/>
-      <c r="R10" s="53"/>
-      <c r="S10" s="53"/>
-      <c r="T10" s="53"/>
-      <c r="U10" s="53"/>
-      <c r="V10" s="53"/>
-      <c r="W10" s="53"/>
-      <c r="X10" s="55"/>
-    </row>
-    <row r="11" spans="1:38" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="41"/>
-      <c r="B11" s="41"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="31"/>
+      <c r="R10" s="31"/>
+      <c r="S10" s="31"/>
+      <c r="T10" s="31"/>
+      <c r="U10" s="31"/>
+      <c r="V10" s="31"/>
+      <c r="W10" s="31"/>
+      <c r="X10" s="32"/>
+    </row>
+    <row r="11" spans="1:38" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="50"/>
+      <c r="B11" s="50"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
       <c r="I11" s="10" t="s">
         <v>10</v>
       </c>
@@ -2355,9 +2361,9 @@
       <c r="W11" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="X11" s="56"/>
-    </row>
-    <row r="12" spans="1:38" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X11" s="33"/>
+    </row>
+    <row r="12" spans="1:38" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>1</v>
       </c>
@@ -2375,10 +2381,18 @@
       <c r="I12" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="J12" s="27"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="24"/>
+      <c r="J12" s="27">
+        <v>8</v>
+      </c>
+      <c r="K12" s="24">
+        <v>10</v>
+      </c>
+      <c r="L12" s="24">
+        <v>8</v>
+      </c>
+      <c r="M12" s="24">
+        <v>10</v>
+      </c>
       <c r="N12" s="24"/>
       <c r="O12" s="24"/>
       <c r="P12" s="24"/>
@@ -2391,7 +2405,7 @@
       <c r="W12" s="24"/>
       <c r="X12" s="11"/>
     </row>
-    <row r="13" spans="1:38" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:38" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>2</v>
       </c>
@@ -2409,10 +2423,18 @@
       <c r="I13" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="J13" s="27"/>
-      <c r="K13" s="24"/>
-      <c r="L13" s="24"/>
-      <c r="M13" s="24"/>
+      <c r="J13" s="27">
+        <v>4</v>
+      </c>
+      <c r="K13" s="24">
+        <v>8</v>
+      </c>
+      <c r="L13" s="24">
+        <v>10</v>
+      </c>
+      <c r="M13" s="24">
+        <v>10</v>
+      </c>
       <c r="N13" s="24"/>
       <c r="O13" s="24"/>
       <c r="P13" s="24"/>
@@ -2425,7 +2447,7 @@
       <c r="W13" s="24"/>
       <c r="X13" s="11"/>
     </row>
-    <row r="14" spans="1:38" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:38" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>3</v>
       </c>
@@ -2443,10 +2465,16 @@
       <c r="I14" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="J14" s="27"/>
+      <c r="J14" s="27">
+        <v>4</v>
+      </c>
       <c r="K14" s="24"/>
-      <c r="L14" s="24"/>
-      <c r="M14" s="24"/>
+      <c r="L14" s="24">
+        <v>4</v>
+      </c>
+      <c r="M14" s="24">
+        <v>8</v>
+      </c>
       <c r="N14" s="24"/>
       <c r="O14" s="24"/>
       <c r="P14" s="24"/>
@@ -2459,7 +2487,7 @@
       <c r="W14" s="24"/>
       <c r="X14" s="11"/>
     </row>
-    <row r="15" spans="1:38" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:38" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>4</v>
       </c>
@@ -2477,10 +2505,18 @@
       <c r="I15" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="J15" s="27"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="24"/>
+      <c r="J15" s="27">
+        <v>4</v>
+      </c>
+      <c r="K15" s="24">
+        <v>10</v>
+      </c>
+      <c r="L15" s="24">
+        <v>10</v>
+      </c>
+      <c r="M15" s="24">
+        <v>10</v>
+      </c>
       <c r="N15" s="24"/>
       <c r="O15" s="24"/>
       <c r="P15" s="24"/>
@@ -2493,7 +2529,7 @@
       <c r="W15" s="24"/>
       <c r="X15" s="11"/>
     </row>
-    <row r="16" spans="1:38" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:38" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>5</v>
       </c>
@@ -2511,10 +2547,18 @@
       <c r="I16" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="J16" s="27"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="24"/>
+      <c r="J16" s="27">
+        <v>4</v>
+      </c>
+      <c r="K16" s="24">
+        <v>6</v>
+      </c>
+      <c r="L16" s="24">
+        <v>8</v>
+      </c>
+      <c r="M16" s="24">
+        <v>10</v>
+      </c>
       <c r="N16" s="24"/>
       <c r="O16" s="24"/>
       <c r="P16" s="24"/>
@@ -2527,7 +2571,7 @@
       <c r="W16" s="24"/>
       <c r="X16" s="11"/>
     </row>
-    <row r="17" spans="1:24" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:24" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>6</v>
       </c>
@@ -2545,10 +2589,18 @@
       <c r="I17" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="J17" s="27"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="24"/>
-      <c r="M17" s="24"/>
+      <c r="J17" s="27">
+        <v>6</v>
+      </c>
+      <c r="K17" s="24">
+        <v>6</v>
+      </c>
+      <c r="L17" s="24">
+        <v>6</v>
+      </c>
+      <c r="M17" s="24">
+        <v>8</v>
+      </c>
       <c r="N17" s="24"/>
       <c r="O17" s="24"/>
       <c r="P17" s="24"/>
@@ -2561,7 +2613,7 @@
       <c r="W17" s="24"/>
       <c r="X17" s="11"/>
     </row>
-    <row r="18" spans="1:24" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:24" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>7</v>
       </c>
@@ -2579,10 +2631,18 @@
       <c r="I18" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="J18" s="27"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
-      <c r="M18" s="24"/>
+      <c r="J18" s="27">
+        <v>4</v>
+      </c>
+      <c r="K18" s="24">
+        <v>10</v>
+      </c>
+      <c r="L18" s="24">
+        <v>8</v>
+      </c>
+      <c r="M18" s="24">
+        <v>10</v>
+      </c>
       <c r="N18" s="24"/>
       <c r="O18" s="24"/>
       <c r="P18" s="24"/>
@@ -2595,7 +2655,7 @@
       <c r="W18" s="24"/>
       <c r="X18" s="11"/>
     </row>
-    <row r="19" spans="1:24" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:24" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="7">
         <v>8</v>
       </c>
@@ -2613,10 +2673,18 @@
       <c r="I19" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="J19" s="27"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="24"/>
+      <c r="J19" s="27">
+        <v>6</v>
+      </c>
+      <c r="K19" s="24">
+        <v>10</v>
+      </c>
+      <c r="L19" s="24">
+        <v>8</v>
+      </c>
+      <c r="M19" s="24">
+        <v>8</v>
+      </c>
       <c r="N19" s="24"/>
       <c r="O19" s="24"/>
       <c r="P19" s="24"/>
@@ -2629,7 +2697,7 @@
       <c r="W19" s="24"/>
       <c r="X19" s="11"/>
     </row>
-    <row r="20" spans="1:24" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:24" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>9</v>
       </c>
@@ -2647,10 +2715,18 @@
       <c r="I20" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="J20" s="27"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="24"/>
+      <c r="J20" s="27">
+        <v>6</v>
+      </c>
+      <c r="K20" s="24">
+        <v>10</v>
+      </c>
+      <c r="L20" s="24">
+        <v>8</v>
+      </c>
+      <c r="M20" s="24">
+        <v>8</v>
+      </c>
       <c r="N20" s="24"/>
       <c r="O20" s="24"/>
       <c r="P20" s="24"/>
@@ -2663,7 +2739,7 @@
       <c r="W20" s="24"/>
       <c r="X20" s="11"/>
     </row>
-    <row r="21" spans="1:24" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:24" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="7">
         <v>10</v>
       </c>
@@ -2681,10 +2757,18 @@
       <c r="I21" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="J21" s="27"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="24"/>
+      <c r="J21" s="27">
+        <v>0</v>
+      </c>
+      <c r="K21" s="24">
+        <v>8</v>
+      </c>
+      <c r="L21" s="24">
+        <v>10</v>
+      </c>
+      <c r="M21" s="24">
+        <v>10</v>
+      </c>
       <c r="N21" s="24"/>
       <c r="O21" s="24"/>
       <c r="P21" s="24"/>
@@ -2697,7 +2781,7 @@
       <c r="W21" s="24"/>
       <c r="X21" s="11"/>
     </row>
-    <row r="22" spans="1:24" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:24" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="7">
         <v>11</v>
       </c>
@@ -2715,10 +2799,18 @@
       <c r="I22" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="J22" s="27"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="24"/>
+      <c r="J22" s="27">
+        <v>0</v>
+      </c>
+      <c r="K22" s="24">
+        <v>10</v>
+      </c>
+      <c r="L22" s="24">
+        <v>10</v>
+      </c>
+      <c r="M22" s="24">
+        <v>8</v>
+      </c>
       <c r="N22" s="24"/>
       <c r="O22" s="24"/>
       <c r="P22" s="24"/>
@@ -2731,7 +2823,7 @@
       <c r="W22" s="24"/>
       <c r="X22" s="11"/>
     </row>
-    <row r="23" spans="1:24" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:24" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="7">
         <v>12</v>
       </c>
@@ -2749,10 +2841,18 @@
       <c r="I23" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="J23" s="27"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
+      <c r="J23" s="27">
+        <v>2</v>
+      </c>
+      <c r="K23" s="24">
+        <v>10</v>
+      </c>
+      <c r="L23" s="24">
+        <v>10</v>
+      </c>
+      <c r="M23" s="24">
+        <v>10</v>
+      </c>
       <c r="N23" s="24"/>
       <c r="O23" s="24"/>
       <c r="P23" s="24"/>
@@ -2765,7 +2865,7 @@
       <c r="W23" s="24"/>
       <c r="X23" s="11"/>
     </row>
-    <row r="24" spans="1:24" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:24" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="7">
         <v>13</v>
       </c>
@@ -2783,10 +2883,18 @@
       <c r="I24" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="J24" s="27"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
-      <c r="M24" s="24"/>
+      <c r="J24" s="27">
+        <v>2</v>
+      </c>
+      <c r="K24" s="24">
+        <v>8</v>
+      </c>
+      <c r="L24" s="24">
+        <v>8</v>
+      </c>
+      <c r="M24" s="24">
+        <v>8</v>
+      </c>
       <c r="N24" s="24"/>
       <c r="O24" s="24"/>
       <c r="P24" s="24"/>
@@ -2799,138 +2907,225 @@
       <c r="W24" s="24"/>
       <c r="X24" s="11"/>
     </row>
-    <row r="25" spans="1:24" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="8" t="s">
+    <row r="25" spans="1:24" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="7">
+        <v>14</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="J25" s="27">
+        <v>8</v>
+      </c>
+      <c r="K25" s="24">
+        <v>10</v>
+      </c>
+      <c r="L25" s="24">
+        <v>10</v>
+      </c>
+      <c r="M25" s="24">
+        <v>10</v>
+      </c>
+      <c r="N25" s="24"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="24"/>
+      <c r="R25" s="24"/>
+      <c r="S25" s="24"/>
+      <c r="T25" s="24"/>
+      <c r="U25" s="24"/>
+      <c r="V25" s="24"/>
+      <c r="W25" s="24"/>
+      <c r="X25" s="11"/>
+    </row>
+    <row r="26" spans="1:24" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="7">
+        <v>15</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="27">
+        <v>2</v>
+      </c>
+      <c r="K26" s="24">
+        <v>8</v>
+      </c>
+      <c r="L26" s="24">
+        <v>4</v>
+      </c>
+      <c r="M26" s="24">
+        <v>8</v>
+      </c>
+      <c r="N26" s="24"/>
+      <c r="O26" s="24"/>
+      <c r="P26" s="24"/>
+      <c r="Q26" s="24"/>
+      <c r="R26" s="24"/>
+      <c r="S26" s="24"/>
+      <c r="T26" s="24"/>
+      <c r="U26" s="24"/>
+      <c r="V26" s="24"/>
+      <c r="W26" s="24"/>
+      <c r="X26" s="11"/>
+    </row>
+    <row r="27" spans="1:24" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B26" s="8" t="s">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="B28" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="6"/>
-    </row>
-    <row r="28" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="31" t="s">
+    <row r="29" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="6"/>
+    </row>
+    <row r="30" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="32" t="s">
+      <c r="B30" s="52"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="J28" s="33"/>
-      <c r="K28" s="33"/>
-      <c r="L28" s="33"/>
-      <c r="M28" s="33"/>
-      <c r="N28" s="33"/>
-      <c r="O28" s="33"/>
-      <c r="P28" s="33"/>
-      <c r="Q28" s="33"/>
-      <c r="R28" s="33"/>
-      <c r="S28" s="33"/>
-      <c r="T28" s="33"/>
-      <c r="U28" s="33"/>
-      <c r="V28" s="33"/>
-      <c r="W28" s="33"/>
-      <c r="X28" s="34"/>
-    </row>
-    <row r="29" spans="1:24" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="30" t="s">
+      <c r="J30" s="54"/>
+      <c r="K30" s="54"/>
+      <c r="L30" s="54"/>
+      <c r="M30" s="54"/>
+      <c r="N30" s="54"/>
+      <c r="O30" s="54"/>
+      <c r="P30" s="54"/>
+      <c r="Q30" s="54"/>
+      <c r="R30" s="54"/>
+      <c r="S30" s="54"/>
+      <c r="T30" s="54"/>
+      <c r="U30" s="54"/>
+      <c r="V30" s="54"/>
+      <c r="W30" s="54"/>
+      <c r="X30" s="55"/>
+    </row>
+    <row r="31" spans="1:24" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="30"/>
-      <c r="O29" s="30"/>
-      <c r="P29" s="30"/>
-      <c r="Q29" s="30"/>
-      <c r="R29" s="30"/>
-      <c r="S29" s="30"/>
-      <c r="T29" s="30"/>
-      <c r="U29" s="30"/>
-      <c r="V29" s="30"/>
-      <c r="W29" s="30"/>
-      <c r="X29" s="30"/>
-    </row>
-    <row r="30" spans="1:24" ht="45.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="30" t="s">
+      <c r="B31" s="45"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="45"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="45"/>
+      <c r="H31" s="45"/>
+      <c r="I31" s="45"/>
+      <c r="J31" s="45"/>
+      <c r="K31" s="45"/>
+      <c r="L31" s="45"/>
+      <c r="M31" s="45"/>
+      <c r="N31" s="45"/>
+      <c r="O31" s="45"/>
+      <c r="P31" s="45"/>
+      <c r="Q31" s="45"/>
+      <c r="R31" s="45"/>
+      <c r="S31" s="45"/>
+      <c r="T31" s="45"/>
+      <c r="U31" s="45"/>
+      <c r="V31" s="45"/>
+      <c r="W31" s="45"/>
+      <c r="X31" s="45"/>
+    </row>
+    <row r="32" spans="1:24" ht="45.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="30"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="30"/>
-      <c r="H30" s="30"/>
-      <c r="I30" s="30"/>
-      <c r="J30" s="30"/>
-      <c r="K30" s="30"/>
-      <c r="L30" s="30"/>
-      <c r="M30" s="30"/>
-      <c r="N30" s="30"/>
-      <c r="O30" s="30"/>
-      <c r="P30" s="30"/>
-      <c r="Q30" s="30"/>
-      <c r="R30" s="30"/>
-      <c r="S30" s="30"/>
-      <c r="T30" s="30"/>
-      <c r="U30" s="30"/>
-      <c r="V30" s="30"/>
-      <c r="W30" s="30"/>
-      <c r="X30" s="30"/>
-    </row>
-    <row r="31" spans="1:24" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="30" t="s">
+      <c r="B32" s="45"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="45"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="45"/>
+      <c r="G32" s="45"/>
+      <c r="H32" s="45"/>
+      <c r="I32" s="45"/>
+      <c r="J32" s="45"/>
+      <c r="K32" s="45"/>
+      <c r="L32" s="45"/>
+      <c r="M32" s="45"/>
+      <c r="N32" s="45"/>
+      <c r="O32" s="45"/>
+      <c r="P32" s="45"/>
+      <c r="Q32" s="45"/>
+      <c r="R32" s="45"/>
+      <c r="S32" s="45"/>
+      <c r="T32" s="45"/>
+      <c r="U32" s="45"/>
+      <c r="V32" s="45"/>
+      <c r="W32" s="45"/>
+      <c r="X32" s="45"/>
+    </row>
+    <row r="33" spans="1:24" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="B31" s="30"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="30"/>
-      <c r="H31" s="30"/>
-      <c r="I31" s="30" t="s">
+      <c r="B33" s="45"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="45"/>
+      <c r="H33" s="45"/>
+      <c r="I33" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="J31" s="30"/>
-      <c r="K31" s="30"/>
-      <c r="L31" s="30"/>
-      <c r="M31" s="30"/>
-      <c r="N31" s="30"/>
-      <c r="O31" s="30"/>
-      <c r="P31" s="30"/>
-      <c r="Q31" s="30"/>
-      <c r="R31" s="30"/>
-      <c r="S31" s="30"/>
-      <c r="T31" s="30"/>
-      <c r="U31" s="30"/>
-      <c r="V31" s="30"/>
-      <c r="W31" s="30"/>
-      <c r="X31" s="30"/>
-    </row>
-    <row r="32" spans="1:24" ht="26.25" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="J33" s="45"/>
+      <c r="K33" s="45"/>
+      <c r="L33" s="45"/>
+      <c r="M33" s="45"/>
+      <c r="N33" s="45"/>
+      <c r="O33" s="45"/>
+      <c r="P33" s="45"/>
+      <c r="Q33" s="45"/>
+      <c r="R33" s="45"/>
+      <c r="S33" s="45"/>
+      <c r="T33" s="45"/>
+      <c r="U33" s="45"/>
+      <c r="V33" s="45"/>
+      <c r="W33" s="45"/>
+      <c r="X33" s="45"/>
+    </row>
+    <row r="34" spans="1:24" ht="26.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="C10:H11"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="I33:X33"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="I30:X30"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="I31:X31"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="I32:X32"/>
     <mergeCell ref="J10:W10"/>
     <mergeCell ref="X10:X11"/>
     <mergeCell ref="A1:X1"/>
@@ -2947,15 +3142,6 @@
     <mergeCell ref="D8:X8"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:H11"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="I31:X31"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="I28:X28"/>
-    <mergeCell ref="A29:H29"/>
-    <mergeCell ref="I29:X29"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="I30:X30"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -2970,828 +3156,828 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AO32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.88671875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" style="2" customWidth="1"/>
-    <col min="3" max="7" width="4.88671875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="14.109375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="7.109375" style="2" customWidth="1"/>
-    <col min="10" max="41" width="3.6640625" style="2" customWidth="1"/>
-    <col min="42" max="248" width="10.88671875" style="2"/>
-    <col min="249" max="249" width="5.88671875" style="2" customWidth="1"/>
-    <col min="250" max="250" width="13.33203125" style="2" customWidth="1"/>
-    <col min="251" max="251" width="4.88671875" style="2" customWidth="1"/>
-    <col min="252" max="252" width="33.109375" style="2" customWidth="1"/>
-    <col min="253" max="253" width="8.109375" style="2" customWidth="1"/>
-    <col min="254" max="254" width="6.88671875" style="2" customWidth="1"/>
-    <col min="255" max="255" width="14.33203125" style="2" customWidth="1"/>
-    <col min="256" max="256" width="18.88671875" style="2" customWidth="1"/>
-    <col min="257" max="257" width="13.109375" style="2" customWidth="1"/>
-    <col min="258" max="504" width="10.88671875" style="2"/>
-    <col min="505" max="505" width="5.88671875" style="2" customWidth="1"/>
-    <col min="506" max="506" width="13.33203125" style="2" customWidth="1"/>
-    <col min="507" max="507" width="4.88671875" style="2" customWidth="1"/>
-    <col min="508" max="508" width="33.109375" style="2" customWidth="1"/>
-    <col min="509" max="509" width="8.109375" style="2" customWidth="1"/>
-    <col min="510" max="510" width="6.88671875" style="2" customWidth="1"/>
-    <col min="511" max="511" width="14.33203125" style="2" customWidth="1"/>
-    <col min="512" max="512" width="18.88671875" style="2" customWidth="1"/>
-    <col min="513" max="513" width="13.109375" style="2" customWidth="1"/>
-    <col min="514" max="760" width="10.88671875" style="2"/>
-    <col min="761" max="761" width="5.88671875" style="2" customWidth="1"/>
-    <col min="762" max="762" width="13.33203125" style="2" customWidth="1"/>
-    <col min="763" max="763" width="4.88671875" style="2" customWidth="1"/>
-    <col min="764" max="764" width="33.109375" style="2" customWidth="1"/>
-    <col min="765" max="765" width="8.109375" style="2" customWidth="1"/>
-    <col min="766" max="766" width="6.88671875" style="2" customWidth="1"/>
-    <col min="767" max="767" width="14.33203125" style="2" customWidth="1"/>
-    <col min="768" max="768" width="18.88671875" style="2" customWidth="1"/>
-    <col min="769" max="769" width="13.109375" style="2" customWidth="1"/>
-    <col min="770" max="1016" width="10.88671875" style="2"/>
-    <col min="1017" max="1017" width="5.88671875" style="2" customWidth="1"/>
-    <col min="1018" max="1018" width="13.33203125" style="2" customWidth="1"/>
-    <col min="1019" max="1019" width="4.88671875" style="2" customWidth="1"/>
-    <col min="1020" max="1020" width="33.109375" style="2" customWidth="1"/>
-    <col min="1021" max="1021" width="8.109375" style="2" customWidth="1"/>
-    <col min="1022" max="1022" width="6.88671875" style="2" customWidth="1"/>
-    <col min="1023" max="1023" width="14.33203125" style="2" customWidth="1"/>
-    <col min="1024" max="1024" width="18.88671875" style="2" customWidth="1"/>
-    <col min="1025" max="1025" width="13.109375" style="2" customWidth="1"/>
-    <col min="1026" max="1272" width="10.88671875" style="2"/>
-    <col min="1273" max="1273" width="5.88671875" style="2" customWidth="1"/>
-    <col min="1274" max="1274" width="13.33203125" style="2" customWidth="1"/>
-    <col min="1275" max="1275" width="4.88671875" style="2" customWidth="1"/>
-    <col min="1276" max="1276" width="33.109375" style="2" customWidth="1"/>
-    <col min="1277" max="1277" width="8.109375" style="2" customWidth="1"/>
-    <col min="1278" max="1278" width="6.88671875" style="2" customWidth="1"/>
-    <col min="1279" max="1279" width="14.33203125" style="2" customWidth="1"/>
-    <col min="1280" max="1280" width="18.88671875" style="2" customWidth="1"/>
-    <col min="1281" max="1281" width="13.109375" style="2" customWidth="1"/>
-    <col min="1282" max="1528" width="10.88671875" style="2"/>
-    <col min="1529" max="1529" width="5.88671875" style="2" customWidth="1"/>
-    <col min="1530" max="1530" width="13.33203125" style="2" customWidth="1"/>
-    <col min="1531" max="1531" width="4.88671875" style="2" customWidth="1"/>
-    <col min="1532" max="1532" width="33.109375" style="2" customWidth="1"/>
-    <col min="1533" max="1533" width="8.109375" style="2" customWidth="1"/>
-    <col min="1534" max="1534" width="6.88671875" style="2" customWidth="1"/>
-    <col min="1535" max="1535" width="14.33203125" style="2" customWidth="1"/>
-    <col min="1536" max="1536" width="18.88671875" style="2" customWidth="1"/>
-    <col min="1537" max="1537" width="13.109375" style="2" customWidth="1"/>
-    <col min="1538" max="1784" width="10.88671875" style="2"/>
-    <col min="1785" max="1785" width="5.88671875" style="2" customWidth="1"/>
-    <col min="1786" max="1786" width="13.33203125" style="2" customWidth="1"/>
-    <col min="1787" max="1787" width="4.88671875" style="2" customWidth="1"/>
-    <col min="1788" max="1788" width="33.109375" style="2" customWidth="1"/>
-    <col min="1789" max="1789" width="8.109375" style="2" customWidth="1"/>
-    <col min="1790" max="1790" width="6.88671875" style="2" customWidth="1"/>
-    <col min="1791" max="1791" width="14.33203125" style="2" customWidth="1"/>
-    <col min="1792" max="1792" width="18.88671875" style="2" customWidth="1"/>
-    <col min="1793" max="1793" width="13.109375" style="2" customWidth="1"/>
-    <col min="1794" max="2040" width="10.88671875" style="2"/>
-    <col min="2041" max="2041" width="5.88671875" style="2" customWidth="1"/>
-    <col min="2042" max="2042" width="13.33203125" style="2" customWidth="1"/>
-    <col min="2043" max="2043" width="4.88671875" style="2" customWidth="1"/>
-    <col min="2044" max="2044" width="33.109375" style="2" customWidth="1"/>
-    <col min="2045" max="2045" width="8.109375" style="2" customWidth="1"/>
-    <col min="2046" max="2046" width="6.88671875" style="2" customWidth="1"/>
-    <col min="2047" max="2047" width="14.33203125" style="2" customWidth="1"/>
-    <col min="2048" max="2048" width="18.88671875" style="2" customWidth="1"/>
-    <col min="2049" max="2049" width="13.109375" style="2" customWidth="1"/>
-    <col min="2050" max="2296" width="10.88671875" style="2"/>
-    <col min="2297" max="2297" width="5.88671875" style="2" customWidth="1"/>
-    <col min="2298" max="2298" width="13.33203125" style="2" customWidth="1"/>
-    <col min="2299" max="2299" width="4.88671875" style="2" customWidth="1"/>
-    <col min="2300" max="2300" width="33.109375" style="2" customWidth="1"/>
-    <col min="2301" max="2301" width="8.109375" style="2" customWidth="1"/>
-    <col min="2302" max="2302" width="6.88671875" style="2" customWidth="1"/>
-    <col min="2303" max="2303" width="14.33203125" style="2" customWidth="1"/>
-    <col min="2304" max="2304" width="18.88671875" style="2" customWidth="1"/>
-    <col min="2305" max="2305" width="13.109375" style="2" customWidth="1"/>
-    <col min="2306" max="2552" width="10.88671875" style="2"/>
-    <col min="2553" max="2553" width="5.88671875" style="2" customWidth="1"/>
-    <col min="2554" max="2554" width="13.33203125" style="2" customWidth="1"/>
-    <col min="2555" max="2555" width="4.88671875" style="2" customWidth="1"/>
-    <col min="2556" max="2556" width="33.109375" style="2" customWidth="1"/>
-    <col min="2557" max="2557" width="8.109375" style="2" customWidth="1"/>
-    <col min="2558" max="2558" width="6.88671875" style="2" customWidth="1"/>
-    <col min="2559" max="2559" width="14.33203125" style="2" customWidth="1"/>
-    <col min="2560" max="2560" width="18.88671875" style="2" customWidth="1"/>
-    <col min="2561" max="2561" width="13.109375" style="2" customWidth="1"/>
-    <col min="2562" max="2808" width="10.88671875" style="2"/>
-    <col min="2809" max="2809" width="5.88671875" style="2" customWidth="1"/>
-    <col min="2810" max="2810" width="13.33203125" style="2" customWidth="1"/>
-    <col min="2811" max="2811" width="4.88671875" style="2" customWidth="1"/>
-    <col min="2812" max="2812" width="33.109375" style="2" customWidth="1"/>
-    <col min="2813" max="2813" width="8.109375" style="2" customWidth="1"/>
-    <col min="2814" max="2814" width="6.88671875" style="2" customWidth="1"/>
-    <col min="2815" max="2815" width="14.33203125" style="2" customWidth="1"/>
-    <col min="2816" max="2816" width="18.88671875" style="2" customWidth="1"/>
-    <col min="2817" max="2817" width="13.109375" style="2" customWidth="1"/>
-    <col min="2818" max="3064" width="10.88671875" style="2"/>
-    <col min="3065" max="3065" width="5.88671875" style="2" customWidth="1"/>
-    <col min="3066" max="3066" width="13.33203125" style="2" customWidth="1"/>
-    <col min="3067" max="3067" width="4.88671875" style="2" customWidth="1"/>
-    <col min="3068" max="3068" width="33.109375" style="2" customWidth="1"/>
-    <col min="3069" max="3069" width="8.109375" style="2" customWidth="1"/>
-    <col min="3070" max="3070" width="6.88671875" style="2" customWidth="1"/>
-    <col min="3071" max="3071" width="14.33203125" style="2" customWidth="1"/>
-    <col min="3072" max="3072" width="18.88671875" style="2" customWidth="1"/>
-    <col min="3073" max="3073" width="13.109375" style="2" customWidth="1"/>
-    <col min="3074" max="3320" width="10.88671875" style="2"/>
-    <col min="3321" max="3321" width="5.88671875" style="2" customWidth="1"/>
-    <col min="3322" max="3322" width="13.33203125" style="2" customWidth="1"/>
-    <col min="3323" max="3323" width="4.88671875" style="2" customWidth="1"/>
-    <col min="3324" max="3324" width="33.109375" style="2" customWidth="1"/>
-    <col min="3325" max="3325" width="8.109375" style="2" customWidth="1"/>
-    <col min="3326" max="3326" width="6.88671875" style="2" customWidth="1"/>
-    <col min="3327" max="3327" width="14.33203125" style="2" customWidth="1"/>
-    <col min="3328" max="3328" width="18.88671875" style="2" customWidth="1"/>
-    <col min="3329" max="3329" width="13.109375" style="2" customWidth="1"/>
-    <col min="3330" max="3576" width="10.88671875" style="2"/>
-    <col min="3577" max="3577" width="5.88671875" style="2" customWidth="1"/>
-    <col min="3578" max="3578" width="13.33203125" style="2" customWidth="1"/>
-    <col min="3579" max="3579" width="4.88671875" style="2" customWidth="1"/>
-    <col min="3580" max="3580" width="33.109375" style="2" customWidth="1"/>
-    <col min="3581" max="3581" width="8.109375" style="2" customWidth="1"/>
-    <col min="3582" max="3582" width="6.88671875" style="2" customWidth="1"/>
-    <col min="3583" max="3583" width="14.33203125" style="2" customWidth="1"/>
-    <col min="3584" max="3584" width="18.88671875" style="2" customWidth="1"/>
-    <col min="3585" max="3585" width="13.109375" style="2" customWidth="1"/>
-    <col min="3586" max="3832" width="10.88671875" style="2"/>
-    <col min="3833" max="3833" width="5.88671875" style="2" customWidth="1"/>
-    <col min="3834" max="3834" width="13.33203125" style="2" customWidth="1"/>
-    <col min="3835" max="3835" width="4.88671875" style="2" customWidth="1"/>
-    <col min="3836" max="3836" width="33.109375" style="2" customWidth="1"/>
-    <col min="3837" max="3837" width="8.109375" style="2" customWidth="1"/>
-    <col min="3838" max="3838" width="6.88671875" style="2" customWidth="1"/>
-    <col min="3839" max="3839" width="14.33203125" style="2" customWidth="1"/>
-    <col min="3840" max="3840" width="18.88671875" style="2" customWidth="1"/>
-    <col min="3841" max="3841" width="13.109375" style="2" customWidth="1"/>
-    <col min="3842" max="4088" width="10.88671875" style="2"/>
-    <col min="4089" max="4089" width="5.88671875" style="2" customWidth="1"/>
-    <col min="4090" max="4090" width="13.33203125" style="2" customWidth="1"/>
-    <col min="4091" max="4091" width="4.88671875" style="2" customWidth="1"/>
-    <col min="4092" max="4092" width="33.109375" style="2" customWidth="1"/>
-    <col min="4093" max="4093" width="8.109375" style="2" customWidth="1"/>
-    <col min="4094" max="4094" width="6.88671875" style="2" customWidth="1"/>
-    <col min="4095" max="4095" width="14.33203125" style="2" customWidth="1"/>
-    <col min="4096" max="4096" width="18.88671875" style="2" customWidth="1"/>
-    <col min="4097" max="4097" width="13.109375" style="2" customWidth="1"/>
-    <col min="4098" max="4344" width="10.88671875" style="2"/>
-    <col min="4345" max="4345" width="5.88671875" style="2" customWidth="1"/>
-    <col min="4346" max="4346" width="13.33203125" style="2" customWidth="1"/>
-    <col min="4347" max="4347" width="4.88671875" style="2" customWidth="1"/>
-    <col min="4348" max="4348" width="33.109375" style="2" customWidth="1"/>
-    <col min="4349" max="4349" width="8.109375" style="2" customWidth="1"/>
-    <col min="4350" max="4350" width="6.88671875" style="2" customWidth="1"/>
-    <col min="4351" max="4351" width="14.33203125" style="2" customWidth="1"/>
-    <col min="4352" max="4352" width="18.88671875" style="2" customWidth="1"/>
-    <col min="4353" max="4353" width="13.109375" style="2" customWidth="1"/>
-    <col min="4354" max="4600" width="10.88671875" style="2"/>
-    <col min="4601" max="4601" width="5.88671875" style="2" customWidth="1"/>
-    <col min="4602" max="4602" width="13.33203125" style="2" customWidth="1"/>
-    <col min="4603" max="4603" width="4.88671875" style="2" customWidth="1"/>
-    <col min="4604" max="4604" width="33.109375" style="2" customWidth="1"/>
-    <col min="4605" max="4605" width="8.109375" style="2" customWidth="1"/>
-    <col min="4606" max="4606" width="6.88671875" style="2" customWidth="1"/>
-    <col min="4607" max="4607" width="14.33203125" style="2" customWidth="1"/>
-    <col min="4608" max="4608" width="18.88671875" style="2" customWidth="1"/>
-    <col min="4609" max="4609" width="13.109375" style="2" customWidth="1"/>
-    <col min="4610" max="4856" width="10.88671875" style="2"/>
-    <col min="4857" max="4857" width="5.88671875" style="2" customWidth="1"/>
-    <col min="4858" max="4858" width="13.33203125" style="2" customWidth="1"/>
-    <col min="4859" max="4859" width="4.88671875" style="2" customWidth="1"/>
-    <col min="4860" max="4860" width="33.109375" style="2" customWidth="1"/>
-    <col min="4861" max="4861" width="8.109375" style="2" customWidth="1"/>
-    <col min="4862" max="4862" width="6.88671875" style="2" customWidth="1"/>
-    <col min="4863" max="4863" width="14.33203125" style="2" customWidth="1"/>
-    <col min="4864" max="4864" width="18.88671875" style="2" customWidth="1"/>
-    <col min="4865" max="4865" width="13.109375" style="2" customWidth="1"/>
-    <col min="4866" max="5112" width="10.88671875" style="2"/>
-    <col min="5113" max="5113" width="5.88671875" style="2" customWidth="1"/>
-    <col min="5114" max="5114" width="13.33203125" style="2" customWidth="1"/>
-    <col min="5115" max="5115" width="4.88671875" style="2" customWidth="1"/>
-    <col min="5116" max="5116" width="33.109375" style="2" customWidth="1"/>
-    <col min="5117" max="5117" width="8.109375" style="2" customWidth="1"/>
-    <col min="5118" max="5118" width="6.88671875" style="2" customWidth="1"/>
-    <col min="5119" max="5119" width="14.33203125" style="2" customWidth="1"/>
-    <col min="5120" max="5120" width="18.88671875" style="2" customWidth="1"/>
-    <col min="5121" max="5121" width="13.109375" style="2" customWidth="1"/>
-    <col min="5122" max="5368" width="10.88671875" style="2"/>
-    <col min="5369" max="5369" width="5.88671875" style="2" customWidth="1"/>
-    <col min="5370" max="5370" width="13.33203125" style="2" customWidth="1"/>
-    <col min="5371" max="5371" width="4.88671875" style="2" customWidth="1"/>
-    <col min="5372" max="5372" width="33.109375" style="2" customWidth="1"/>
-    <col min="5373" max="5373" width="8.109375" style="2" customWidth="1"/>
-    <col min="5374" max="5374" width="6.88671875" style="2" customWidth="1"/>
-    <col min="5375" max="5375" width="14.33203125" style="2" customWidth="1"/>
-    <col min="5376" max="5376" width="18.88671875" style="2" customWidth="1"/>
-    <col min="5377" max="5377" width="13.109375" style="2" customWidth="1"/>
-    <col min="5378" max="5624" width="10.88671875" style="2"/>
-    <col min="5625" max="5625" width="5.88671875" style="2" customWidth="1"/>
-    <col min="5626" max="5626" width="13.33203125" style="2" customWidth="1"/>
-    <col min="5627" max="5627" width="4.88671875" style="2" customWidth="1"/>
-    <col min="5628" max="5628" width="33.109375" style="2" customWidth="1"/>
-    <col min="5629" max="5629" width="8.109375" style="2" customWidth="1"/>
-    <col min="5630" max="5630" width="6.88671875" style="2" customWidth="1"/>
-    <col min="5631" max="5631" width="14.33203125" style="2" customWidth="1"/>
-    <col min="5632" max="5632" width="18.88671875" style="2" customWidth="1"/>
-    <col min="5633" max="5633" width="13.109375" style="2" customWidth="1"/>
-    <col min="5634" max="5880" width="10.88671875" style="2"/>
-    <col min="5881" max="5881" width="5.88671875" style="2" customWidth="1"/>
-    <col min="5882" max="5882" width="13.33203125" style="2" customWidth="1"/>
-    <col min="5883" max="5883" width="4.88671875" style="2" customWidth="1"/>
-    <col min="5884" max="5884" width="33.109375" style="2" customWidth="1"/>
-    <col min="5885" max="5885" width="8.109375" style="2" customWidth="1"/>
-    <col min="5886" max="5886" width="6.88671875" style="2" customWidth="1"/>
-    <col min="5887" max="5887" width="14.33203125" style="2" customWidth="1"/>
-    <col min="5888" max="5888" width="18.88671875" style="2" customWidth="1"/>
-    <col min="5889" max="5889" width="13.109375" style="2" customWidth="1"/>
-    <col min="5890" max="6136" width="10.88671875" style="2"/>
-    <col min="6137" max="6137" width="5.88671875" style="2" customWidth="1"/>
-    <col min="6138" max="6138" width="13.33203125" style="2" customWidth="1"/>
-    <col min="6139" max="6139" width="4.88671875" style="2" customWidth="1"/>
-    <col min="6140" max="6140" width="33.109375" style="2" customWidth="1"/>
-    <col min="6141" max="6141" width="8.109375" style="2" customWidth="1"/>
-    <col min="6142" max="6142" width="6.88671875" style="2" customWidth="1"/>
-    <col min="6143" max="6143" width="14.33203125" style="2" customWidth="1"/>
-    <col min="6144" max="6144" width="18.88671875" style="2" customWidth="1"/>
-    <col min="6145" max="6145" width="13.109375" style="2" customWidth="1"/>
-    <col min="6146" max="6392" width="10.88671875" style="2"/>
-    <col min="6393" max="6393" width="5.88671875" style="2" customWidth="1"/>
-    <col min="6394" max="6394" width="13.33203125" style="2" customWidth="1"/>
-    <col min="6395" max="6395" width="4.88671875" style="2" customWidth="1"/>
-    <col min="6396" max="6396" width="33.109375" style="2" customWidth="1"/>
-    <col min="6397" max="6397" width="8.109375" style="2" customWidth="1"/>
-    <col min="6398" max="6398" width="6.88671875" style="2" customWidth="1"/>
-    <col min="6399" max="6399" width="14.33203125" style="2" customWidth="1"/>
-    <col min="6400" max="6400" width="18.88671875" style="2" customWidth="1"/>
-    <col min="6401" max="6401" width="13.109375" style="2" customWidth="1"/>
-    <col min="6402" max="6648" width="10.88671875" style="2"/>
-    <col min="6649" max="6649" width="5.88671875" style="2" customWidth="1"/>
-    <col min="6650" max="6650" width="13.33203125" style="2" customWidth="1"/>
-    <col min="6651" max="6651" width="4.88671875" style="2" customWidth="1"/>
-    <col min="6652" max="6652" width="33.109375" style="2" customWidth="1"/>
-    <col min="6653" max="6653" width="8.109375" style="2" customWidth="1"/>
-    <col min="6654" max="6654" width="6.88671875" style="2" customWidth="1"/>
-    <col min="6655" max="6655" width="14.33203125" style="2" customWidth="1"/>
-    <col min="6656" max="6656" width="18.88671875" style="2" customWidth="1"/>
-    <col min="6657" max="6657" width="13.109375" style="2" customWidth="1"/>
-    <col min="6658" max="6904" width="10.88671875" style="2"/>
-    <col min="6905" max="6905" width="5.88671875" style="2" customWidth="1"/>
-    <col min="6906" max="6906" width="13.33203125" style="2" customWidth="1"/>
-    <col min="6907" max="6907" width="4.88671875" style="2" customWidth="1"/>
-    <col min="6908" max="6908" width="33.109375" style="2" customWidth="1"/>
-    <col min="6909" max="6909" width="8.109375" style="2" customWidth="1"/>
-    <col min="6910" max="6910" width="6.88671875" style="2" customWidth="1"/>
-    <col min="6911" max="6911" width="14.33203125" style="2" customWidth="1"/>
-    <col min="6912" max="6912" width="18.88671875" style="2" customWidth="1"/>
-    <col min="6913" max="6913" width="13.109375" style="2" customWidth="1"/>
-    <col min="6914" max="7160" width="10.88671875" style="2"/>
-    <col min="7161" max="7161" width="5.88671875" style="2" customWidth="1"/>
-    <col min="7162" max="7162" width="13.33203125" style="2" customWidth="1"/>
-    <col min="7163" max="7163" width="4.88671875" style="2" customWidth="1"/>
-    <col min="7164" max="7164" width="33.109375" style="2" customWidth="1"/>
-    <col min="7165" max="7165" width="8.109375" style="2" customWidth="1"/>
-    <col min="7166" max="7166" width="6.88671875" style="2" customWidth="1"/>
-    <col min="7167" max="7167" width="14.33203125" style="2" customWidth="1"/>
-    <col min="7168" max="7168" width="18.88671875" style="2" customWidth="1"/>
-    <col min="7169" max="7169" width="13.109375" style="2" customWidth="1"/>
-    <col min="7170" max="7416" width="10.88671875" style="2"/>
-    <col min="7417" max="7417" width="5.88671875" style="2" customWidth="1"/>
-    <col min="7418" max="7418" width="13.33203125" style="2" customWidth="1"/>
-    <col min="7419" max="7419" width="4.88671875" style="2" customWidth="1"/>
-    <col min="7420" max="7420" width="33.109375" style="2" customWidth="1"/>
-    <col min="7421" max="7421" width="8.109375" style="2" customWidth="1"/>
-    <col min="7422" max="7422" width="6.88671875" style="2" customWidth="1"/>
-    <col min="7423" max="7423" width="14.33203125" style="2" customWidth="1"/>
-    <col min="7424" max="7424" width="18.88671875" style="2" customWidth="1"/>
-    <col min="7425" max="7425" width="13.109375" style="2" customWidth="1"/>
-    <col min="7426" max="7672" width="10.88671875" style="2"/>
-    <col min="7673" max="7673" width="5.88671875" style="2" customWidth="1"/>
-    <col min="7674" max="7674" width="13.33203125" style="2" customWidth="1"/>
-    <col min="7675" max="7675" width="4.88671875" style="2" customWidth="1"/>
-    <col min="7676" max="7676" width="33.109375" style="2" customWidth="1"/>
-    <col min="7677" max="7677" width="8.109375" style="2" customWidth="1"/>
-    <col min="7678" max="7678" width="6.88671875" style="2" customWidth="1"/>
-    <col min="7679" max="7679" width="14.33203125" style="2" customWidth="1"/>
-    <col min="7680" max="7680" width="18.88671875" style="2" customWidth="1"/>
-    <col min="7681" max="7681" width="13.109375" style="2" customWidth="1"/>
-    <col min="7682" max="7928" width="10.88671875" style="2"/>
-    <col min="7929" max="7929" width="5.88671875" style="2" customWidth="1"/>
-    <col min="7930" max="7930" width="13.33203125" style="2" customWidth="1"/>
-    <col min="7931" max="7931" width="4.88671875" style="2" customWidth="1"/>
-    <col min="7932" max="7932" width="33.109375" style="2" customWidth="1"/>
-    <col min="7933" max="7933" width="8.109375" style="2" customWidth="1"/>
-    <col min="7934" max="7934" width="6.88671875" style="2" customWidth="1"/>
-    <col min="7935" max="7935" width="14.33203125" style="2" customWidth="1"/>
-    <col min="7936" max="7936" width="18.88671875" style="2" customWidth="1"/>
-    <col min="7937" max="7937" width="13.109375" style="2" customWidth="1"/>
-    <col min="7938" max="8184" width="10.88671875" style="2"/>
-    <col min="8185" max="8185" width="5.88671875" style="2" customWidth="1"/>
-    <col min="8186" max="8186" width="13.33203125" style="2" customWidth="1"/>
-    <col min="8187" max="8187" width="4.88671875" style="2" customWidth="1"/>
-    <col min="8188" max="8188" width="33.109375" style="2" customWidth="1"/>
-    <col min="8189" max="8189" width="8.109375" style="2" customWidth="1"/>
-    <col min="8190" max="8190" width="6.88671875" style="2" customWidth="1"/>
-    <col min="8191" max="8191" width="14.33203125" style="2" customWidth="1"/>
-    <col min="8192" max="8192" width="18.88671875" style="2" customWidth="1"/>
-    <col min="8193" max="8193" width="13.109375" style="2" customWidth="1"/>
-    <col min="8194" max="8440" width="10.88671875" style="2"/>
-    <col min="8441" max="8441" width="5.88671875" style="2" customWidth="1"/>
-    <col min="8442" max="8442" width="13.33203125" style="2" customWidth="1"/>
-    <col min="8443" max="8443" width="4.88671875" style="2" customWidth="1"/>
-    <col min="8444" max="8444" width="33.109375" style="2" customWidth="1"/>
-    <col min="8445" max="8445" width="8.109375" style="2" customWidth="1"/>
-    <col min="8446" max="8446" width="6.88671875" style="2" customWidth="1"/>
-    <col min="8447" max="8447" width="14.33203125" style="2" customWidth="1"/>
-    <col min="8448" max="8448" width="18.88671875" style="2" customWidth="1"/>
-    <col min="8449" max="8449" width="13.109375" style="2" customWidth="1"/>
-    <col min="8450" max="8696" width="10.88671875" style="2"/>
-    <col min="8697" max="8697" width="5.88671875" style="2" customWidth="1"/>
-    <col min="8698" max="8698" width="13.33203125" style="2" customWidth="1"/>
-    <col min="8699" max="8699" width="4.88671875" style="2" customWidth="1"/>
-    <col min="8700" max="8700" width="33.109375" style="2" customWidth="1"/>
-    <col min="8701" max="8701" width="8.109375" style="2" customWidth="1"/>
-    <col min="8702" max="8702" width="6.88671875" style="2" customWidth="1"/>
-    <col min="8703" max="8703" width="14.33203125" style="2" customWidth="1"/>
-    <col min="8704" max="8704" width="18.88671875" style="2" customWidth="1"/>
-    <col min="8705" max="8705" width="13.109375" style="2" customWidth="1"/>
-    <col min="8706" max="8952" width="10.88671875" style="2"/>
-    <col min="8953" max="8953" width="5.88671875" style="2" customWidth="1"/>
-    <col min="8954" max="8954" width="13.33203125" style="2" customWidth="1"/>
-    <col min="8955" max="8955" width="4.88671875" style="2" customWidth="1"/>
-    <col min="8956" max="8956" width="33.109375" style="2" customWidth="1"/>
-    <col min="8957" max="8957" width="8.109375" style="2" customWidth="1"/>
-    <col min="8958" max="8958" width="6.88671875" style="2" customWidth="1"/>
-    <col min="8959" max="8959" width="14.33203125" style="2" customWidth="1"/>
-    <col min="8960" max="8960" width="18.88671875" style="2" customWidth="1"/>
-    <col min="8961" max="8961" width="13.109375" style="2" customWidth="1"/>
-    <col min="8962" max="9208" width="10.88671875" style="2"/>
-    <col min="9209" max="9209" width="5.88671875" style="2" customWidth="1"/>
-    <col min="9210" max="9210" width="13.33203125" style="2" customWidth="1"/>
-    <col min="9211" max="9211" width="4.88671875" style="2" customWidth="1"/>
-    <col min="9212" max="9212" width="33.109375" style="2" customWidth="1"/>
-    <col min="9213" max="9213" width="8.109375" style="2" customWidth="1"/>
-    <col min="9214" max="9214" width="6.88671875" style="2" customWidth="1"/>
-    <col min="9215" max="9215" width="14.33203125" style="2" customWidth="1"/>
-    <col min="9216" max="9216" width="18.88671875" style="2" customWidth="1"/>
-    <col min="9217" max="9217" width="13.109375" style="2" customWidth="1"/>
-    <col min="9218" max="9464" width="10.88671875" style="2"/>
-    <col min="9465" max="9465" width="5.88671875" style="2" customWidth="1"/>
-    <col min="9466" max="9466" width="13.33203125" style="2" customWidth="1"/>
-    <col min="9467" max="9467" width="4.88671875" style="2" customWidth="1"/>
-    <col min="9468" max="9468" width="33.109375" style="2" customWidth="1"/>
-    <col min="9469" max="9469" width="8.109375" style="2" customWidth="1"/>
-    <col min="9470" max="9470" width="6.88671875" style="2" customWidth="1"/>
-    <col min="9471" max="9471" width="14.33203125" style="2" customWidth="1"/>
-    <col min="9472" max="9472" width="18.88671875" style="2" customWidth="1"/>
-    <col min="9473" max="9473" width="13.109375" style="2" customWidth="1"/>
-    <col min="9474" max="9720" width="10.88671875" style="2"/>
-    <col min="9721" max="9721" width="5.88671875" style="2" customWidth="1"/>
-    <col min="9722" max="9722" width="13.33203125" style="2" customWidth="1"/>
-    <col min="9723" max="9723" width="4.88671875" style="2" customWidth="1"/>
-    <col min="9724" max="9724" width="33.109375" style="2" customWidth="1"/>
-    <col min="9725" max="9725" width="8.109375" style="2" customWidth="1"/>
-    <col min="9726" max="9726" width="6.88671875" style="2" customWidth="1"/>
-    <col min="9727" max="9727" width="14.33203125" style="2" customWidth="1"/>
-    <col min="9728" max="9728" width="18.88671875" style="2" customWidth="1"/>
-    <col min="9729" max="9729" width="13.109375" style="2" customWidth="1"/>
-    <col min="9730" max="9976" width="10.88671875" style="2"/>
-    <col min="9977" max="9977" width="5.88671875" style="2" customWidth="1"/>
-    <col min="9978" max="9978" width="13.33203125" style="2" customWidth="1"/>
-    <col min="9979" max="9979" width="4.88671875" style="2" customWidth="1"/>
-    <col min="9980" max="9980" width="33.109375" style="2" customWidth="1"/>
-    <col min="9981" max="9981" width="8.109375" style="2" customWidth="1"/>
-    <col min="9982" max="9982" width="6.88671875" style="2" customWidth="1"/>
-    <col min="9983" max="9983" width="14.33203125" style="2" customWidth="1"/>
-    <col min="9984" max="9984" width="18.88671875" style="2" customWidth="1"/>
-    <col min="9985" max="9985" width="13.109375" style="2" customWidth="1"/>
-    <col min="9986" max="10232" width="10.88671875" style="2"/>
-    <col min="10233" max="10233" width="5.88671875" style="2" customWidth="1"/>
-    <col min="10234" max="10234" width="13.33203125" style="2" customWidth="1"/>
-    <col min="10235" max="10235" width="4.88671875" style="2" customWidth="1"/>
-    <col min="10236" max="10236" width="33.109375" style="2" customWidth="1"/>
-    <col min="10237" max="10237" width="8.109375" style="2" customWidth="1"/>
-    <col min="10238" max="10238" width="6.88671875" style="2" customWidth="1"/>
-    <col min="10239" max="10239" width="14.33203125" style="2" customWidth="1"/>
-    <col min="10240" max="10240" width="18.88671875" style="2" customWidth="1"/>
-    <col min="10241" max="10241" width="13.109375" style="2" customWidth="1"/>
-    <col min="10242" max="10488" width="10.88671875" style="2"/>
-    <col min="10489" max="10489" width="5.88671875" style="2" customWidth="1"/>
-    <col min="10490" max="10490" width="13.33203125" style="2" customWidth="1"/>
-    <col min="10491" max="10491" width="4.88671875" style="2" customWidth="1"/>
-    <col min="10492" max="10492" width="33.109375" style="2" customWidth="1"/>
-    <col min="10493" max="10493" width="8.109375" style="2" customWidth="1"/>
-    <col min="10494" max="10494" width="6.88671875" style="2" customWidth="1"/>
-    <col min="10495" max="10495" width="14.33203125" style="2" customWidth="1"/>
-    <col min="10496" max="10496" width="18.88671875" style="2" customWidth="1"/>
-    <col min="10497" max="10497" width="13.109375" style="2" customWidth="1"/>
-    <col min="10498" max="10744" width="10.88671875" style="2"/>
-    <col min="10745" max="10745" width="5.88671875" style="2" customWidth="1"/>
-    <col min="10746" max="10746" width="13.33203125" style="2" customWidth="1"/>
-    <col min="10747" max="10747" width="4.88671875" style="2" customWidth="1"/>
-    <col min="10748" max="10748" width="33.109375" style="2" customWidth="1"/>
-    <col min="10749" max="10749" width="8.109375" style="2" customWidth="1"/>
-    <col min="10750" max="10750" width="6.88671875" style="2" customWidth="1"/>
-    <col min="10751" max="10751" width="14.33203125" style="2" customWidth="1"/>
-    <col min="10752" max="10752" width="18.88671875" style="2" customWidth="1"/>
-    <col min="10753" max="10753" width="13.109375" style="2" customWidth="1"/>
-    <col min="10754" max="11000" width="10.88671875" style="2"/>
-    <col min="11001" max="11001" width="5.88671875" style="2" customWidth="1"/>
-    <col min="11002" max="11002" width="13.33203125" style="2" customWidth="1"/>
-    <col min="11003" max="11003" width="4.88671875" style="2" customWidth="1"/>
-    <col min="11004" max="11004" width="33.109375" style="2" customWidth="1"/>
-    <col min="11005" max="11005" width="8.109375" style="2" customWidth="1"/>
-    <col min="11006" max="11006" width="6.88671875" style="2" customWidth="1"/>
-    <col min="11007" max="11007" width="14.33203125" style="2" customWidth="1"/>
-    <col min="11008" max="11008" width="18.88671875" style="2" customWidth="1"/>
-    <col min="11009" max="11009" width="13.109375" style="2" customWidth="1"/>
-    <col min="11010" max="11256" width="10.88671875" style="2"/>
-    <col min="11257" max="11257" width="5.88671875" style="2" customWidth="1"/>
-    <col min="11258" max="11258" width="13.33203125" style="2" customWidth="1"/>
-    <col min="11259" max="11259" width="4.88671875" style="2" customWidth="1"/>
-    <col min="11260" max="11260" width="33.109375" style="2" customWidth="1"/>
-    <col min="11261" max="11261" width="8.109375" style="2" customWidth="1"/>
-    <col min="11262" max="11262" width="6.88671875" style="2" customWidth="1"/>
-    <col min="11263" max="11263" width="14.33203125" style="2" customWidth="1"/>
-    <col min="11264" max="11264" width="18.88671875" style="2" customWidth="1"/>
-    <col min="11265" max="11265" width="13.109375" style="2" customWidth="1"/>
-    <col min="11266" max="11512" width="10.88671875" style="2"/>
-    <col min="11513" max="11513" width="5.88671875" style="2" customWidth="1"/>
-    <col min="11514" max="11514" width="13.33203125" style="2" customWidth="1"/>
-    <col min="11515" max="11515" width="4.88671875" style="2" customWidth="1"/>
-    <col min="11516" max="11516" width="33.109375" style="2" customWidth="1"/>
-    <col min="11517" max="11517" width="8.109375" style="2" customWidth="1"/>
-    <col min="11518" max="11518" width="6.88671875" style="2" customWidth="1"/>
-    <col min="11519" max="11519" width="14.33203125" style="2" customWidth="1"/>
-    <col min="11520" max="11520" width="18.88671875" style="2" customWidth="1"/>
-    <col min="11521" max="11521" width="13.109375" style="2" customWidth="1"/>
-    <col min="11522" max="11768" width="10.88671875" style="2"/>
-    <col min="11769" max="11769" width="5.88671875" style="2" customWidth="1"/>
-    <col min="11770" max="11770" width="13.33203125" style="2" customWidth="1"/>
-    <col min="11771" max="11771" width="4.88671875" style="2" customWidth="1"/>
-    <col min="11772" max="11772" width="33.109375" style="2" customWidth="1"/>
-    <col min="11773" max="11773" width="8.109375" style="2" customWidth="1"/>
-    <col min="11774" max="11774" width="6.88671875" style="2" customWidth="1"/>
-    <col min="11775" max="11775" width="14.33203125" style="2" customWidth="1"/>
-    <col min="11776" max="11776" width="18.88671875" style="2" customWidth="1"/>
-    <col min="11777" max="11777" width="13.109375" style="2" customWidth="1"/>
-    <col min="11778" max="12024" width="10.88671875" style="2"/>
-    <col min="12025" max="12025" width="5.88671875" style="2" customWidth="1"/>
-    <col min="12026" max="12026" width="13.33203125" style="2" customWidth="1"/>
-    <col min="12027" max="12027" width="4.88671875" style="2" customWidth="1"/>
-    <col min="12028" max="12028" width="33.109375" style="2" customWidth="1"/>
-    <col min="12029" max="12029" width="8.109375" style="2" customWidth="1"/>
-    <col min="12030" max="12030" width="6.88671875" style="2" customWidth="1"/>
-    <col min="12031" max="12031" width="14.33203125" style="2" customWidth="1"/>
-    <col min="12032" max="12032" width="18.88671875" style="2" customWidth="1"/>
-    <col min="12033" max="12033" width="13.109375" style="2" customWidth="1"/>
-    <col min="12034" max="12280" width="10.88671875" style="2"/>
-    <col min="12281" max="12281" width="5.88671875" style="2" customWidth="1"/>
-    <col min="12282" max="12282" width="13.33203125" style="2" customWidth="1"/>
-    <col min="12283" max="12283" width="4.88671875" style="2" customWidth="1"/>
-    <col min="12284" max="12284" width="33.109375" style="2" customWidth="1"/>
-    <col min="12285" max="12285" width="8.109375" style="2" customWidth="1"/>
-    <col min="12286" max="12286" width="6.88671875" style="2" customWidth="1"/>
-    <col min="12287" max="12287" width="14.33203125" style="2" customWidth="1"/>
-    <col min="12288" max="12288" width="18.88671875" style="2" customWidth="1"/>
-    <col min="12289" max="12289" width="13.109375" style="2" customWidth="1"/>
-    <col min="12290" max="12536" width="10.88671875" style="2"/>
-    <col min="12537" max="12537" width="5.88671875" style="2" customWidth="1"/>
-    <col min="12538" max="12538" width="13.33203125" style="2" customWidth="1"/>
-    <col min="12539" max="12539" width="4.88671875" style="2" customWidth="1"/>
-    <col min="12540" max="12540" width="33.109375" style="2" customWidth="1"/>
-    <col min="12541" max="12541" width="8.109375" style="2" customWidth="1"/>
-    <col min="12542" max="12542" width="6.88671875" style="2" customWidth="1"/>
-    <col min="12543" max="12543" width="14.33203125" style="2" customWidth="1"/>
-    <col min="12544" max="12544" width="18.88671875" style="2" customWidth="1"/>
-    <col min="12545" max="12545" width="13.109375" style="2" customWidth="1"/>
-    <col min="12546" max="12792" width="10.88671875" style="2"/>
-    <col min="12793" max="12793" width="5.88671875" style="2" customWidth="1"/>
-    <col min="12794" max="12794" width="13.33203125" style="2" customWidth="1"/>
-    <col min="12795" max="12795" width="4.88671875" style="2" customWidth="1"/>
-    <col min="12796" max="12796" width="33.109375" style="2" customWidth="1"/>
-    <col min="12797" max="12797" width="8.109375" style="2" customWidth="1"/>
-    <col min="12798" max="12798" width="6.88671875" style="2" customWidth="1"/>
-    <col min="12799" max="12799" width="14.33203125" style="2" customWidth="1"/>
-    <col min="12800" max="12800" width="18.88671875" style="2" customWidth="1"/>
-    <col min="12801" max="12801" width="13.109375" style="2" customWidth="1"/>
-    <col min="12802" max="13048" width="10.88671875" style="2"/>
-    <col min="13049" max="13049" width="5.88671875" style="2" customWidth="1"/>
-    <col min="13050" max="13050" width="13.33203125" style="2" customWidth="1"/>
-    <col min="13051" max="13051" width="4.88671875" style="2" customWidth="1"/>
-    <col min="13052" max="13052" width="33.109375" style="2" customWidth="1"/>
-    <col min="13053" max="13053" width="8.109375" style="2" customWidth="1"/>
-    <col min="13054" max="13054" width="6.88671875" style="2" customWidth="1"/>
-    <col min="13055" max="13055" width="14.33203125" style="2" customWidth="1"/>
-    <col min="13056" max="13056" width="18.88671875" style="2" customWidth="1"/>
-    <col min="13057" max="13057" width="13.109375" style="2" customWidth="1"/>
-    <col min="13058" max="13304" width="10.88671875" style="2"/>
-    <col min="13305" max="13305" width="5.88671875" style="2" customWidth="1"/>
-    <col min="13306" max="13306" width="13.33203125" style="2" customWidth="1"/>
-    <col min="13307" max="13307" width="4.88671875" style="2" customWidth="1"/>
-    <col min="13308" max="13308" width="33.109375" style="2" customWidth="1"/>
-    <col min="13309" max="13309" width="8.109375" style="2" customWidth="1"/>
-    <col min="13310" max="13310" width="6.88671875" style="2" customWidth="1"/>
-    <col min="13311" max="13311" width="14.33203125" style="2" customWidth="1"/>
-    <col min="13312" max="13312" width="18.88671875" style="2" customWidth="1"/>
-    <col min="13313" max="13313" width="13.109375" style="2" customWidth="1"/>
-    <col min="13314" max="13560" width="10.88671875" style="2"/>
-    <col min="13561" max="13561" width="5.88671875" style="2" customWidth="1"/>
-    <col min="13562" max="13562" width="13.33203125" style="2" customWidth="1"/>
-    <col min="13563" max="13563" width="4.88671875" style="2" customWidth="1"/>
-    <col min="13564" max="13564" width="33.109375" style="2" customWidth="1"/>
-    <col min="13565" max="13565" width="8.109375" style="2" customWidth="1"/>
-    <col min="13566" max="13566" width="6.88671875" style="2" customWidth="1"/>
-    <col min="13567" max="13567" width="14.33203125" style="2" customWidth="1"/>
-    <col min="13568" max="13568" width="18.88671875" style="2" customWidth="1"/>
-    <col min="13569" max="13569" width="13.109375" style="2" customWidth="1"/>
-    <col min="13570" max="13816" width="10.88671875" style="2"/>
-    <col min="13817" max="13817" width="5.88671875" style="2" customWidth="1"/>
-    <col min="13818" max="13818" width="13.33203125" style="2" customWidth="1"/>
-    <col min="13819" max="13819" width="4.88671875" style="2" customWidth="1"/>
-    <col min="13820" max="13820" width="33.109375" style="2" customWidth="1"/>
-    <col min="13821" max="13821" width="8.109375" style="2" customWidth="1"/>
-    <col min="13822" max="13822" width="6.88671875" style="2" customWidth="1"/>
-    <col min="13823" max="13823" width="14.33203125" style="2" customWidth="1"/>
-    <col min="13824" max="13824" width="18.88671875" style="2" customWidth="1"/>
-    <col min="13825" max="13825" width="13.109375" style="2" customWidth="1"/>
-    <col min="13826" max="14072" width="10.88671875" style="2"/>
-    <col min="14073" max="14073" width="5.88671875" style="2" customWidth="1"/>
-    <col min="14074" max="14074" width="13.33203125" style="2" customWidth="1"/>
-    <col min="14075" max="14075" width="4.88671875" style="2" customWidth="1"/>
-    <col min="14076" max="14076" width="33.109375" style="2" customWidth="1"/>
-    <col min="14077" max="14077" width="8.109375" style="2" customWidth="1"/>
-    <col min="14078" max="14078" width="6.88671875" style="2" customWidth="1"/>
-    <col min="14079" max="14079" width="14.33203125" style="2" customWidth="1"/>
-    <col min="14080" max="14080" width="18.88671875" style="2" customWidth="1"/>
-    <col min="14081" max="14081" width="13.109375" style="2" customWidth="1"/>
-    <col min="14082" max="14328" width="10.88671875" style="2"/>
-    <col min="14329" max="14329" width="5.88671875" style="2" customWidth="1"/>
-    <col min="14330" max="14330" width="13.33203125" style="2" customWidth="1"/>
-    <col min="14331" max="14331" width="4.88671875" style="2" customWidth="1"/>
-    <col min="14332" max="14332" width="33.109375" style="2" customWidth="1"/>
-    <col min="14333" max="14333" width="8.109375" style="2" customWidth="1"/>
-    <col min="14334" max="14334" width="6.88671875" style="2" customWidth="1"/>
-    <col min="14335" max="14335" width="14.33203125" style="2" customWidth="1"/>
-    <col min="14336" max="14336" width="18.88671875" style="2" customWidth="1"/>
-    <col min="14337" max="14337" width="13.109375" style="2" customWidth="1"/>
-    <col min="14338" max="14584" width="10.88671875" style="2"/>
-    <col min="14585" max="14585" width="5.88671875" style="2" customWidth="1"/>
-    <col min="14586" max="14586" width="13.33203125" style="2" customWidth="1"/>
-    <col min="14587" max="14587" width="4.88671875" style="2" customWidth="1"/>
-    <col min="14588" max="14588" width="33.109375" style="2" customWidth="1"/>
-    <col min="14589" max="14589" width="8.109375" style="2" customWidth="1"/>
-    <col min="14590" max="14590" width="6.88671875" style="2" customWidth="1"/>
-    <col min="14591" max="14591" width="14.33203125" style="2" customWidth="1"/>
-    <col min="14592" max="14592" width="18.88671875" style="2" customWidth="1"/>
-    <col min="14593" max="14593" width="13.109375" style="2" customWidth="1"/>
-    <col min="14594" max="14840" width="10.88671875" style="2"/>
-    <col min="14841" max="14841" width="5.88671875" style="2" customWidth="1"/>
-    <col min="14842" max="14842" width="13.33203125" style="2" customWidth="1"/>
-    <col min="14843" max="14843" width="4.88671875" style="2" customWidth="1"/>
-    <col min="14844" max="14844" width="33.109375" style="2" customWidth="1"/>
-    <col min="14845" max="14845" width="8.109375" style="2" customWidth="1"/>
-    <col min="14846" max="14846" width="6.88671875" style="2" customWidth="1"/>
-    <col min="14847" max="14847" width="14.33203125" style="2" customWidth="1"/>
-    <col min="14848" max="14848" width="18.88671875" style="2" customWidth="1"/>
-    <col min="14849" max="14849" width="13.109375" style="2" customWidth="1"/>
-    <col min="14850" max="15096" width="10.88671875" style="2"/>
-    <col min="15097" max="15097" width="5.88671875" style="2" customWidth="1"/>
-    <col min="15098" max="15098" width="13.33203125" style="2" customWidth="1"/>
-    <col min="15099" max="15099" width="4.88671875" style="2" customWidth="1"/>
-    <col min="15100" max="15100" width="33.109375" style="2" customWidth="1"/>
-    <col min="15101" max="15101" width="8.109375" style="2" customWidth="1"/>
-    <col min="15102" max="15102" width="6.88671875" style="2" customWidth="1"/>
-    <col min="15103" max="15103" width="14.33203125" style="2" customWidth="1"/>
-    <col min="15104" max="15104" width="18.88671875" style="2" customWidth="1"/>
-    <col min="15105" max="15105" width="13.109375" style="2" customWidth="1"/>
-    <col min="15106" max="15352" width="10.88671875" style="2"/>
-    <col min="15353" max="15353" width="5.88671875" style="2" customWidth="1"/>
-    <col min="15354" max="15354" width="13.33203125" style="2" customWidth="1"/>
-    <col min="15355" max="15355" width="4.88671875" style="2" customWidth="1"/>
-    <col min="15356" max="15356" width="33.109375" style="2" customWidth="1"/>
-    <col min="15357" max="15357" width="8.109375" style="2" customWidth="1"/>
-    <col min="15358" max="15358" width="6.88671875" style="2" customWidth="1"/>
-    <col min="15359" max="15359" width="14.33203125" style="2" customWidth="1"/>
-    <col min="15360" max="15360" width="18.88671875" style="2" customWidth="1"/>
-    <col min="15361" max="15361" width="13.109375" style="2" customWidth="1"/>
-    <col min="15362" max="15608" width="10.88671875" style="2"/>
-    <col min="15609" max="15609" width="5.88671875" style="2" customWidth="1"/>
-    <col min="15610" max="15610" width="13.33203125" style="2" customWidth="1"/>
-    <col min="15611" max="15611" width="4.88671875" style="2" customWidth="1"/>
-    <col min="15612" max="15612" width="33.109375" style="2" customWidth="1"/>
-    <col min="15613" max="15613" width="8.109375" style="2" customWidth="1"/>
-    <col min="15614" max="15614" width="6.88671875" style="2" customWidth="1"/>
-    <col min="15615" max="15615" width="14.33203125" style="2" customWidth="1"/>
-    <col min="15616" max="15616" width="18.88671875" style="2" customWidth="1"/>
-    <col min="15617" max="15617" width="13.109375" style="2" customWidth="1"/>
-    <col min="15618" max="15864" width="10.88671875" style="2"/>
-    <col min="15865" max="15865" width="5.88671875" style="2" customWidth="1"/>
-    <col min="15866" max="15866" width="13.33203125" style="2" customWidth="1"/>
-    <col min="15867" max="15867" width="4.88671875" style="2" customWidth="1"/>
-    <col min="15868" max="15868" width="33.109375" style="2" customWidth="1"/>
-    <col min="15869" max="15869" width="8.109375" style="2" customWidth="1"/>
-    <col min="15870" max="15870" width="6.88671875" style="2" customWidth="1"/>
-    <col min="15871" max="15871" width="14.33203125" style="2" customWidth="1"/>
-    <col min="15872" max="15872" width="18.88671875" style="2" customWidth="1"/>
-    <col min="15873" max="15873" width="13.109375" style="2" customWidth="1"/>
-    <col min="15874" max="16120" width="10.88671875" style="2"/>
-    <col min="16121" max="16121" width="5.88671875" style="2" customWidth="1"/>
-    <col min="16122" max="16122" width="13.33203125" style="2" customWidth="1"/>
-    <col min="16123" max="16123" width="4.88671875" style="2" customWidth="1"/>
-    <col min="16124" max="16124" width="33.109375" style="2" customWidth="1"/>
-    <col min="16125" max="16125" width="8.109375" style="2" customWidth="1"/>
-    <col min="16126" max="16126" width="6.88671875" style="2" customWidth="1"/>
-    <col min="16127" max="16127" width="14.33203125" style="2" customWidth="1"/>
-    <col min="16128" max="16128" width="18.88671875" style="2" customWidth="1"/>
-    <col min="16129" max="16129" width="13.109375" style="2" customWidth="1"/>
-    <col min="16130" max="16384" width="10.88671875" style="2"/>
+    <col min="1" max="1" width="5.85546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" style="2" customWidth="1"/>
+    <col min="3" max="7" width="4.85546875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="7.140625" style="2" customWidth="1"/>
+    <col min="10" max="41" width="3.7109375" style="2" customWidth="1"/>
+    <col min="42" max="248" width="10.85546875" style="2"/>
+    <col min="249" max="249" width="5.85546875" style="2" customWidth="1"/>
+    <col min="250" max="250" width="13.28515625" style="2" customWidth="1"/>
+    <col min="251" max="251" width="4.85546875" style="2" customWidth="1"/>
+    <col min="252" max="252" width="33.140625" style="2" customWidth="1"/>
+    <col min="253" max="253" width="8.140625" style="2" customWidth="1"/>
+    <col min="254" max="254" width="6.85546875" style="2" customWidth="1"/>
+    <col min="255" max="255" width="14.28515625" style="2" customWidth="1"/>
+    <col min="256" max="256" width="18.85546875" style="2" customWidth="1"/>
+    <col min="257" max="257" width="13.140625" style="2" customWidth="1"/>
+    <col min="258" max="504" width="10.85546875" style="2"/>
+    <col min="505" max="505" width="5.85546875" style="2" customWidth="1"/>
+    <col min="506" max="506" width="13.28515625" style="2" customWidth="1"/>
+    <col min="507" max="507" width="4.85546875" style="2" customWidth="1"/>
+    <col min="508" max="508" width="33.140625" style="2" customWidth="1"/>
+    <col min="509" max="509" width="8.140625" style="2" customWidth="1"/>
+    <col min="510" max="510" width="6.85546875" style="2" customWidth="1"/>
+    <col min="511" max="511" width="14.28515625" style="2" customWidth="1"/>
+    <col min="512" max="512" width="18.85546875" style="2" customWidth="1"/>
+    <col min="513" max="513" width="13.140625" style="2" customWidth="1"/>
+    <col min="514" max="760" width="10.85546875" style="2"/>
+    <col min="761" max="761" width="5.85546875" style="2" customWidth="1"/>
+    <col min="762" max="762" width="13.28515625" style="2" customWidth="1"/>
+    <col min="763" max="763" width="4.85546875" style="2" customWidth="1"/>
+    <col min="764" max="764" width="33.140625" style="2" customWidth="1"/>
+    <col min="765" max="765" width="8.140625" style="2" customWidth="1"/>
+    <col min="766" max="766" width="6.85546875" style="2" customWidth="1"/>
+    <col min="767" max="767" width="14.28515625" style="2" customWidth="1"/>
+    <col min="768" max="768" width="18.85546875" style="2" customWidth="1"/>
+    <col min="769" max="769" width="13.140625" style="2" customWidth="1"/>
+    <col min="770" max="1016" width="10.85546875" style="2"/>
+    <col min="1017" max="1017" width="5.85546875" style="2" customWidth="1"/>
+    <col min="1018" max="1018" width="13.28515625" style="2" customWidth="1"/>
+    <col min="1019" max="1019" width="4.85546875" style="2" customWidth="1"/>
+    <col min="1020" max="1020" width="33.140625" style="2" customWidth="1"/>
+    <col min="1021" max="1021" width="8.140625" style="2" customWidth="1"/>
+    <col min="1022" max="1022" width="6.85546875" style="2" customWidth="1"/>
+    <col min="1023" max="1023" width="14.28515625" style="2" customWidth="1"/>
+    <col min="1024" max="1024" width="18.85546875" style="2" customWidth="1"/>
+    <col min="1025" max="1025" width="13.140625" style="2" customWidth="1"/>
+    <col min="1026" max="1272" width="10.85546875" style="2"/>
+    <col min="1273" max="1273" width="5.85546875" style="2" customWidth="1"/>
+    <col min="1274" max="1274" width="13.28515625" style="2" customWidth="1"/>
+    <col min="1275" max="1275" width="4.85546875" style="2" customWidth="1"/>
+    <col min="1276" max="1276" width="33.140625" style="2" customWidth="1"/>
+    <col min="1277" max="1277" width="8.140625" style="2" customWidth="1"/>
+    <col min="1278" max="1278" width="6.85546875" style="2" customWidth="1"/>
+    <col min="1279" max="1279" width="14.28515625" style="2" customWidth="1"/>
+    <col min="1280" max="1280" width="18.85546875" style="2" customWidth="1"/>
+    <col min="1281" max="1281" width="13.140625" style="2" customWidth="1"/>
+    <col min="1282" max="1528" width="10.85546875" style="2"/>
+    <col min="1529" max="1529" width="5.85546875" style="2" customWidth="1"/>
+    <col min="1530" max="1530" width="13.28515625" style="2" customWidth="1"/>
+    <col min="1531" max="1531" width="4.85546875" style="2" customWidth="1"/>
+    <col min="1532" max="1532" width="33.140625" style="2" customWidth="1"/>
+    <col min="1533" max="1533" width="8.140625" style="2" customWidth="1"/>
+    <col min="1534" max="1534" width="6.85546875" style="2" customWidth="1"/>
+    <col min="1535" max="1535" width="14.28515625" style="2" customWidth="1"/>
+    <col min="1536" max="1536" width="18.85546875" style="2" customWidth="1"/>
+    <col min="1537" max="1537" width="13.140625" style="2" customWidth="1"/>
+    <col min="1538" max="1784" width="10.85546875" style="2"/>
+    <col min="1785" max="1785" width="5.85546875" style="2" customWidth="1"/>
+    <col min="1786" max="1786" width="13.28515625" style="2" customWidth="1"/>
+    <col min="1787" max="1787" width="4.85546875" style="2" customWidth="1"/>
+    <col min="1788" max="1788" width="33.140625" style="2" customWidth="1"/>
+    <col min="1789" max="1789" width="8.140625" style="2" customWidth="1"/>
+    <col min="1790" max="1790" width="6.85546875" style="2" customWidth="1"/>
+    <col min="1791" max="1791" width="14.28515625" style="2" customWidth="1"/>
+    <col min="1792" max="1792" width="18.85546875" style="2" customWidth="1"/>
+    <col min="1793" max="1793" width="13.140625" style="2" customWidth="1"/>
+    <col min="1794" max="2040" width="10.85546875" style="2"/>
+    <col min="2041" max="2041" width="5.85546875" style="2" customWidth="1"/>
+    <col min="2042" max="2042" width="13.28515625" style="2" customWidth="1"/>
+    <col min="2043" max="2043" width="4.85546875" style="2" customWidth="1"/>
+    <col min="2044" max="2044" width="33.140625" style="2" customWidth="1"/>
+    <col min="2045" max="2045" width="8.140625" style="2" customWidth="1"/>
+    <col min="2046" max="2046" width="6.85546875" style="2" customWidth="1"/>
+    <col min="2047" max="2047" width="14.28515625" style="2" customWidth="1"/>
+    <col min="2048" max="2048" width="18.85546875" style="2" customWidth="1"/>
+    <col min="2049" max="2049" width="13.140625" style="2" customWidth="1"/>
+    <col min="2050" max="2296" width="10.85546875" style="2"/>
+    <col min="2297" max="2297" width="5.85546875" style="2" customWidth="1"/>
+    <col min="2298" max="2298" width="13.28515625" style="2" customWidth="1"/>
+    <col min="2299" max="2299" width="4.85546875" style="2" customWidth="1"/>
+    <col min="2300" max="2300" width="33.140625" style="2" customWidth="1"/>
+    <col min="2301" max="2301" width="8.140625" style="2" customWidth="1"/>
+    <col min="2302" max="2302" width="6.85546875" style="2" customWidth="1"/>
+    <col min="2303" max="2303" width="14.28515625" style="2" customWidth="1"/>
+    <col min="2304" max="2304" width="18.85546875" style="2" customWidth="1"/>
+    <col min="2305" max="2305" width="13.140625" style="2" customWidth="1"/>
+    <col min="2306" max="2552" width="10.85546875" style="2"/>
+    <col min="2553" max="2553" width="5.85546875" style="2" customWidth="1"/>
+    <col min="2554" max="2554" width="13.28515625" style="2" customWidth="1"/>
+    <col min="2555" max="2555" width="4.85546875" style="2" customWidth="1"/>
+    <col min="2556" max="2556" width="33.140625" style="2" customWidth="1"/>
+    <col min="2557" max="2557" width="8.140625" style="2" customWidth="1"/>
+    <col min="2558" max="2558" width="6.85546875" style="2" customWidth="1"/>
+    <col min="2559" max="2559" width="14.28515625" style="2" customWidth="1"/>
+    <col min="2560" max="2560" width="18.85546875" style="2" customWidth="1"/>
+    <col min="2561" max="2561" width="13.140625" style="2" customWidth="1"/>
+    <col min="2562" max="2808" width="10.85546875" style="2"/>
+    <col min="2809" max="2809" width="5.85546875" style="2" customWidth="1"/>
+    <col min="2810" max="2810" width="13.28515625" style="2" customWidth="1"/>
+    <col min="2811" max="2811" width="4.85546875" style="2" customWidth="1"/>
+    <col min="2812" max="2812" width="33.140625" style="2" customWidth="1"/>
+    <col min="2813" max="2813" width="8.140625" style="2" customWidth="1"/>
+    <col min="2814" max="2814" width="6.85546875" style="2" customWidth="1"/>
+    <col min="2815" max="2815" width="14.28515625" style="2" customWidth="1"/>
+    <col min="2816" max="2816" width="18.85546875" style="2" customWidth="1"/>
+    <col min="2817" max="2817" width="13.140625" style="2" customWidth="1"/>
+    <col min="2818" max="3064" width="10.85546875" style="2"/>
+    <col min="3065" max="3065" width="5.85546875" style="2" customWidth="1"/>
+    <col min="3066" max="3066" width="13.28515625" style="2" customWidth="1"/>
+    <col min="3067" max="3067" width="4.85546875" style="2" customWidth="1"/>
+    <col min="3068" max="3068" width="33.140625" style="2" customWidth="1"/>
+    <col min="3069" max="3069" width="8.140625" style="2" customWidth="1"/>
+    <col min="3070" max="3070" width="6.85546875" style="2" customWidth="1"/>
+    <col min="3071" max="3071" width="14.28515625" style="2" customWidth="1"/>
+    <col min="3072" max="3072" width="18.85546875" style="2" customWidth="1"/>
+    <col min="3073" max="3073" width="13.140625" style="2" customWidth="1"/>
+    <col min="3074" max="3320" width="10.85546875" style="2"/>
+    <col min="3321" max="3321" width="5.85546875" style="2" customWidth="1"/>
+    <col min="3322" max="3322" width="13.28515625" style="2" customWidth="1"/>
+    <col min="3323" max="3323" width="4.85546875" style="2" customWidth="1"/>
+    <col min="3324" max="3324" width="33.140625" style="2" customWidth="1"/>
+    <col min="3325" max="3325" width="8.140625" style="2" customWidth="1"/>
+    <col min="3326" max="3326" width="6.85546875" style="2" customWidth="1"/>
+    <col min="3327" max="3327" width="14.28515625" style="2" customWidth="1"/>
+    <col min="3328" max="3328" width="18.85546875" style="2" customWidth="1"/>
+    <col min="3329" max="3329" width="13.140625" style="2" customWidth="1"/>
+    <col min="3330" max="3576" width="10.85546875" style="2"/>
+    <col min="3577" max="3577" width="5.85546875" style="2" customWidth="1"/>
+    <col min="3578" max="3578" width="13.28515625" style="2" customWidth="1"/>
+    <col min="3579" max="3579" width="4.85546875" style="2" customWidth="1"/>
+    <col min="3580" max="3580" width="33.140625" style="2" customWidth="1"/>
+    <col min="3581" max="3581" width="8.140625" style="2" customWidth="1"/>
+    <col min="3582" max="3582" width="6.85546875" style="2" customWidth="1"/>
+    <col min="3583" max="3583" width="14.28515625" style="2" customWidth="1"/>
+    <col min="3584" max="3584" width="18.85546875" style="2" customWidth="1"/>
+    <col min="3585" max="3585" width="13.140625" style="2" customWidth="1"/>
+    <col min="3586" max="3832" width="10.85546875" style="2"/>
+    <col min="3833" max="3833" width="5.85546875" style="2" customWidth="1"/>
+    <col min="3834" max="3834" width="13.28515625" style="2" customWidth="1"/>
+    <col min="3835" max="3835" width="4.85546875" style="2" customWidth="1"/>
+    <col min="3836" max="3836" width="33.140625" style="2" customWidth="1"/>
+    <col min="3837" max="3837" width="8.140625" style="2" customWidth="1"/>
+    <col min="3838" max="3838" width="6.85546875" style="2" customWidth="1"/>
+    <col min="3839" max="3839" width="14.28515625" style="2" customWidth="1"/>
+    <col min="3840" max="3840" width="18.85546875" style="2" customWidth="1"/>
+    <col min="3841" max="3841" width="13.140625" style="2" customWidth="1"/>
+    <col min="3842" max="4088" width="10.85546875" style="2"/>
+    <col min="4089" max="4089" width="5.85546875" style="2" customWidth="1"/>
+    <col min="4090" max="4090" width="13.28515625" style="2" customWidth="1"/>
+    <col min="4091" max="4091" width="4.85546875" style="2" customWidth="1"/>
+    <col min="4092" max="4092" width="33.140625" style="2" customWidth="1"/>
+    <col min="4093" max="4093" width="8.140625" style="2" customWidth="1"/>
+    <col min="4094" max="4094" width="6.85546875" style="2" customWidth="1"/>
+    <col min="4095" max="4095" width="14.28515625" style="2" customWidth="1"/>
+    <col min="4096" max="4096" width="18.85546875" style="2" customWidth="1"/>
+    <col min="4097" max="4097" width="13.140625" style="2" customWidth="1"/>
+    <col min="4098" max="4344" width="10.85546875" style="2"/>
+    <col min="4345" max="4345" width="5.85546875" style="2" customWidth="1"/>
+    <col min="4346" max="4346" width="13.28515625" style="2" customWidth="1"/>
+    <col min="4347" max="4347" width="4.85546875" style="2" customWidth="1"/>
+    <col min="4348" max="4348" width="33.140625" style="2" customWidth="1"/>
+    <col min="4349" max="4349" width="8.140625" style="2" customWidth="1"/>
+    <col min="4350" max="4350" width="6.85546875" style="2" customWidth="1"/>
+    <col min="4351" max="4351" width="14.28515625" style="2" customWidth="1"/>
+    <col min="4352" max="4352" width="18.85546875" style="2" customWidth="1"/>
+    <col min="4353" max="4353" width="13.140625" style="2" customWidth="1"/>
+    <col min="4354" max="4600" width="10.85546875" style="2"/>
+    <col min="4601" max="4601" width="5.85546875" style="2" customWidth="1"/>
+    <col min="4602" max="4602" width="13.28515625" style="2" customWidth="1"/>
+    <col min="4603" max="4603" width="4.85546875" style="2" customWidth="1"/>
+    <col min="4604" max="4604" width="33.140625" style="2" customWidth="1"/>
+    <col min="4605" max="4605" width="8.140625" style="2" customWidth="1"/>
+    <col min="4606" max="4606" width="6.85546875" style="2" customWidth="1"/>
+    <col min="4607" max="4607" width="14.28515625" style="2" customWidth="1"/>
+    <col min="4608" max="4608" width="18.85546875" style="2" customWidth="1"/>
+    <col min="4609" max="4609" width="13.140625" style="2" customWidth="1"/>
+    <col min="4610" max="4856" width="10.85546875" style="2"/>
+    <col min="4857" max="4857" width="5.85546875" style="2" customWidth="1"/>
+    <col min="4858" max="4858" width="13.28515625" style="2" customWidth="1"/>
+    <col min="4859" max="4859" width="4.85546875" style="2" customWidth="1"/>
+    <col min="4860" max="4860" width="33.140625" style="2" customWidth="1"/>
+    <col min="4861" max="4861" width="8.140625" style="2" customWidth="1"/>
+    <col min="4862" max="4862" width="6.85546875" style="2" customWidth="1"/>
+    <col min="4863" max="4863" width="14.28515625" style="2" customWidth="1"/>
+    <col min="4864" max="4864" width="18.85546875" style="2" customWidth="1"/>
+    <col min="4865" max="4865" width="13.140625" style="2" customWidth="1"/>
+    <col min="4866" max="5112" width="10.85546875" style="2"/>
+    <col min="5113" max="5113" width="5.85546875" style="2" customWidth="1"/>
+    <col min="5114" max="5114" width="13.28515625" style="2" customWidth="1"/>
+    <col min="5115" max="5115" width="4.85546875" style="2" customWidth="1"/>
+    <col min="5116" max="5116" width="33.140625" style="2" customWidth="1"/>
+    <col min="5117" max="5117" width="8.140625" style="2" customWidth="1"/>
+    <col min="5118" max="5118" width="6.85546875" style="2" customWidth="1"/>
+    <col min="5119" max="5119" width="14.28515625" style="2" customWidth="1"/>
+    <col min="5120" max="5120" width="18.85546875" style="2" customWidth="1"/>
+    <col min="5121" max="5121" width="13.140625" style="2" customWidth="1"/>
+    <col min="5122" max="5368" width="10.85546875" style="2"/>
+    <col min="5369" max="5369" width="5.85546875" style="2" customWidth="1"/>
+    <col min="5370" max="5370" width="13.28515625" style="2" customWidth="1"/>
+    <col min="5371" max="5371" width="4.85546875" style="2" customWidth="1"/>
+    <col min="5372" max="5372" width="33.140625" style="2" customWidth="1"/>
+    <col min="5373" max="5373" width="8.140625" style="2" customWidth="1"/>
+    <col min="5374" max="5374" width="6.85546875" style="2" customWidth="1"/>
+    <col min="5375" max="5375" width="14.28515625" style="2" customWidth="1"/>
+    <col min="5376" max="5376" width="18.85546875" style="2" customWidth="1"/>
+    <col min="5377" max="5377" width="13.140625" style="2" customWidth="1"/>
+    <col min="5378" max="5624" width="10.85546875" style="2"/>
+    <col min="5625" max="5625" width="5.85546875" style="2" customWidth="1"/>
+    <col min="5626" max="5626" width="13.28515625" style="2" customWidth="1"/>
+    <col min="5627" max="5627" width="4.85546875" style="2" customWidth="1"/>
+    <col min="5628" max="5628" width="33.140625" style="2" customWidth="1"/>
+    <col min="5629" max="5629" width="8.140625" style="2" customWidth="1"/>
+    <col min="5630" max="5630" width="6.85546875" style="2" customWidth="1"/>
+    <col min="5631" max="5631" width="14.28515625" style="2" customWidth="1"/>
+    <col min="5632" max="5632" width="18.85546875" style="2" customWidth="1"/>
+    <col min="5633" max="5633" width="13.140625" style="2" customWidth="1"/>
+    <col min="5634" max="5880" width="10.85546875" style="2"/>
+    <col min="5881" max="5881" width="5.85546875" style="2" customWidth="1"/>
+    <col min="5882" max="5882" width="13.28515625" style="2" customWidth="1"/>
+    <col min="5883" max="5883" width="4.85546875" style="2" customWidth="1"/>
+    <col min="5884" max="5884" width="33.140625" style="2" customWidth="1"/>
+    <col min="5885" max="5885" width="8.140625" style="2" customWidth="1"/>
+    <col min="5886" max="5886" width="6.85546875" style="2" customWidth="1"/>
+    <col min="5887" max="5887" width="14.28515625" style="2" customWidth="1"/>
+    <col min="5888" max="5888" width="18.85546875" style="2" customWidth="1"/>
+    <col min="5889" max="5889" width="13.140625" style="2" customWidth="1"/>
+    <col min="5890" max="6136" width="10.85546875" style="2"/>
+    <col min="6137" max="6137" width="5.85546875" style="2" customWidth="1"/>
+    <col min="6138" max="6138" width="13.28515625" style="2" customWidth="1"/>
+    <col min="6139" max="6139" width="4.85546875" style="2" customWidth="1"/>
+    <col min="6140" max="6140" width="33.140625" style="2" customWidth="1"/>
+    <col min="6141" max="6141" width="8.140625" style="2" customWidth="1"/>
+    <col min="6142" max="6142" width="6.85546875" style="2" customWidth="1"/>
+    <col min="6143" max="6143" width="14.28515625" style="2" customWidth="1"/>
+    <col min="6144" max="6144" width="18.85546875" style="2" customWidth="1"/>
+    <col min="6145" max="6145" width="13.140625" style="2" customWidth="1"/>
+    <col min="6146" max="6392" width="10.85546875" style="2"/>
+    <col min="6393" max="6393" width="5.85546875" style="2" customWidth="1"/>
+    <col min="6394" max="6394" width="13.28515625" style="2" customWidth="1"/>
+    <col min="6395" max="6395" width="4.85546875" style="2" customWidth="1"/>
+    <col min="6396" max="6396" width="33.140625" style="2" customWidth="1"/>
+    <col min="6397" max="6397" width="8.140625" style="2" customWidth="1"/>
+    <col min="6398" max="6398" width="6.85546875" style="2" customWidth="1"/>
+    <col min="6399" max="6399" width="14.28515625" style="2" customWidth="1"/>
+    <col min="6400" max="6400" width="18.85546875" style="2" customWidth="1"/>
+    <col min="6401" max="6401" width="13.140625" style="2" customWidth="1"/>
+    <col min="6402" max="6648" width="10.85546875" style="2"/>
+    <col min="6649" max="6649" width="5.85546875" style="2" customWidth="1"/>
+    <col min="6650" max="6650" width="13.28515625" style="2" customWidth="1"/>
+    <col min="6651" max="6651" width="4.85546875" style="2" customWidth="1"/>
+    <col min="6652" max="6652" width="33.140625" style="2" customWidth="1"/>
+    <col min="6653" max="6653" width="8.140625" style="2" customWidth="1"/>
+    <col min="6654" max="6654" width="6.85546875" style="2" customWidth="1"/>
+    <col min="6655" max="6655" width="14.28515625" style="2" customWidth="1"/>
+    <col min="6656" max="6656" width="18.85546875" style="2" customWidth="1"/>
+    <col min="6657" max="6657" width="13.140625" style="2" customWidth="1"/>
+    <col min="6658" max="6904" width="10.85546875" style="2"/>
+    <col min="6905" max="6905" width="5.85546875" style="2" customWidth="1"/>
+    <col min="6906" max="6906" width="13.28515625" style="2" customWidth="1"/>
+    <col min="6907" max="6907" width="4.85546875" style="2" customWidth="1"/>
+    <col min="6908" max="6908" width="33.140625" style="2" customWidth="1"/>
+    <col min="6909" max="6909" width="8.140625" style="2" customWidth="1"/>
+    <col min="6910" max="6910" width="6.85546875" style="2" customWidth="1"/>
+    <col min="6911" max="6911" width="14.28515625" style="2" customWidth="1"/>
+    <col min="6912" max="6912" width="18.85546875" style="2" customWidth="1"/>
+    <col min="6913" max="6913" width="13.140625" style="2" customWidth="1"/>
+    <col min="6914" max="7160" width="10.85546875" style="2"/>
+    <col min="7161" max="7161" width="5.85546875" style="2" customWidth="1"/>
+    <col min="7162" max="7162" width="13.28515625" style="2" customWidth="1"/>
+    <col min="7163" max="7163" width="4.85546875" style="2" customWidth="1"/>
+    <col min="7164" max="7164" width="33.140625" style="2" customWidth="1"/>
+    <col min="7165" max="7165" width="8.140625" style="2" customWidth="1"/>
+    <col min="7166" max="7166" width="6.85546875" style="2" customWidth="1"/>
+    <col min="7167" max="7167" width="14.28515625" style="2" customWidth="1"/>
+    <col min="7168" max="7168" width="18.85546875" style="2" customWidth="1"/>
+    <col min="7169" max="7169" width="13.140625" style="2" customWidth="1"/>
+    <col min="7170" max="7416" width="10.85546875" style="2"/>
+    <col min="7417" max="7417" width="5.85546875" style="2" customWidth="1"/>
+    <col min="7418" max="7418" width="13.28515625" style="2" customWidth="1"/>
+    <col min="7419" max="7419" width="4.85546875" style="2" customWidth="1"/>
+    <col min="7420" max="7420" width="33.140625" style="2" customWidth="1"/>
+    <col min="7421" max="7421" width="8.140625" style="2" customWidth="1"/>
+    <col min="7422" max="7422" width="6.85546875" style="2" customWidth="1"/>
+    <col min="7423" max="7423" width="14.28515625" style="2" customWidth="1"/>
+    <col min="7424" max="7424" width="18.85546875" style="2" customWidth="1"/>
+    <col min="7425" max="7425" width="13.140625" style="2" customWidth="1"/>
+    <col min="7426" max="7672" width="10.85546875" style="2"/>
+    <col min="7673" max="7673" width="5.85546875" style="2" customWidth="1"/>
+    <col min="7674" max="7674" width="13.28515625" style="2" customWidth="1"/>
+    <col min="7675" max="7675" width="4.85546875" style="2" customWidth="1"/>
+    <col min="7676" max="7676" width="33.140625" style="2" customWidth="1"/>
+    <col min="7677" max="7677" width="8.140625" style="2" customWidth="1"/>
+    <col min="7678" max="7678" width="6.85546875" style="2" customWidth="1"/>
+    <col min="7679" max="7679" width="14.28515625" style="2" customWidth="1"/>
+    <col min="7680" max="7680" width="18.85546875" style="2" customWidth="1"/>
+    <col min="7681" max="7681" width="13.140625" style="2" customWidth="1"/>
+    <col min="7682" max="7928" width="10.85546875" style="2"/>
+    <col min="7929" max="7929" width="5.85546875" style="2" customWidth="1"/>
+    <col min="7930" max="7930" width="13.28515625" style="2" customWidth="1"/>
+    <col min="7931" max="7931" width="4.85546875" style="2" customWidth="1"/>
+    <col min="7932" max="7932" width="33.140625" style="2" customWidth="1"/>
+    <col min="7933" max="7933" width="8.140625" style="2" customWidth="1"/>
+    <col min="7934" max="7934" width="6.85546875" style="2" customWidth="1"/>
+    <col min="7935" max="7935" width="14.28515625" style="2" customWidth="1"/>
+    <col min="7936" max="7936" width="18.85546875" style="2" customWidth="1"/>
+    <col min="7937" max="7937" width="13.140625" style="2" customWidth="1"/>
+    <col min="7938" max="8184" width="10.85546875" style="2"/>
+    <col min="8185" max="8185" width="5.85546875" style="2" customWidth="1"/>
+    <col min="8186" max="8186" width="13.28515625" style="2" customWidth="1"/>
+    <col min="8187" max="8187" width="4.85546875" style="2" customWidth="1"/>
+    <col min="8188" max="8188" width="33.140625" style="2" customWidth="1"/>
+    <col min="8189" max="8189" width="8.140625" style="2" customWidth="1"/>
+    <col min="8190" max="8190" width="6.85546875" style="2" customWidth="1"/>
+    <col min="8191" max="8191" width="14.28515625" style="2" customWidth="1"/>
+    <col min="8192" max="8192" width="18.85546875" style="2" customWidth="1"/>
+    <col min="8193" max="8193" width="13.140625" style="2" customWidth="1"/>
+    <col min="8194" max="8440" width="10.85546875" style="2"/>
+    <col min="8441" max="8441" width="5.85546875" style="2" customWidth="1"/>
+    <col min="8442" max="8442" width="13.28515625" style="2" customWidth="1"/>
+    <col min="8443" max="8443" width="4.85546875" style="2" customWidth="1"/>
+    <col min="8444" max="8444" width="33.140625" style="2" customWidth="1"/>
+    <col min="8445" max="8445" width="8.140625" style="2" customWidth="1"/>
+    <col min="8446" max="8446" width="6.85546875" style="2" customWidth="1"/>
+    <col min="8447" max="8447" width="14.28515625" style="2" customWidth="1"/>
+    <col min="8448" max="8448" width="18.85546875" style="2" customWidth="1"/>
+    <col min="8449" max="8449" width="13.140625" style="2" customWidth="1"/>
+    <col min="8450" max="8696" width="10.85546875" style="2"/>
+    <col min="8697" max="8697" width="5.85546875" style="2" customWidth="1"/>
+    <col min="8698" max="8698" width="13.28515625" style="2" customWidth="1"/>
+    <col min="8699" max="8699" width="4.85546875" style="2" customWidth="1"/>
+    <col min="8700" max="8700" width="33.140625" style="2" customWidth="1"/>
+    <col min="8701" max="8701" width="8.140625" style="2" customWidth="1"/>
+    <col min="8702" max="8702" width="6.85546875" style="2" customWidth="1"/>
+    <col min="8703" max="8703" width="14.28515625" style="2" customWidth="1"/>
+    <col min="8704" max="8704" width="18.85546875" style="2" customWidth="1"/>
+    <col min="8705" max="8705" width="13.140625" style="2" customWidth="1"/>
+    <col min="8706" max="8952" width="10.85546875" style="2"/>
+    <col min="8953" max="8953" width="5.85546875" style="2" customWidth="1"/>
+    <col min="8954" max="8954" width="13.28515625" style="2" customWidth="1"/>
+    <col min="8955" max="8955" width="4.85546875" style="2" customWidth="1"/>
+    <col min="8956" max="8956" width="33.140625" style="2" customWidth="1"/>
+    <col min="8957" max="8957" width="8.140625" style="2" customWidth="1"/>
+    <col min="8958" max="8958" width="6.85546875" style="2" customWidth="1"/>
+    <col min="8959" max="8959" width="14.28515625" style="2" customWidth="1"/>
+    <col min="8960" max="8960" width="18.85546875" style="2" customWidth="1"/>
+    <col min="8961" max="8961" width="13.140625" style="2" customWidth="1"/>
+    <col min="8962" max="9208" width="10.85546875" style="2"/>
+    <col min="9209" max="9209" width="5.85546875" style="2" customWidth="1"/>
+    <col min="9210" max="9210" width="13.28515625" style="2" customWidth="1"/>
+    <col min="9211" max="9211" width="4.85546875" style="2" customWidth="1"/>
+    <col min="9212" max="9212" width="33.140625" style="2" customWidth="1"/>
+    <col min="9213" max="9213" width="8.140625" style="2" customWidth="1"/>
+    <col min="9214" max="9214" width="6.85546875" style="2" customWidth="1"/>
+    <col min="9215" max="9215" width="14.28515625" style="2" customWidth="1"/>
+    <col min="9216" max="9216" width="18.85546875" style="2" customWidth="1"/>
+    <col min="9217" max="9217" width="13.140625" style="2" customWidth="1"/>
+    <col min="9218" max="9464" width="10.85546875" style="2"/>
+    <col min="9465" max="9465" width="5.85546875" style="2" customWidth="1"/>
+    <col min="9466" max="9466" width="13.28515625" style="2" customWidth="1"/>
+    <col min="9467" max="9467" width="4.85546875" style="2" customWidth="1"/>
+    <col min="9468" max="9468" width="33.140625" style="2" customWidth="1"/>
+    <col min="9469" max="9469" width="8.140625" style="2" customWidth="1"/>
+    <col min="9470" max="9470" width="6.85546875" style="2" customWidth="1"/>
+    <col min="9471" max="9471" width="14.28515625" style="2" customWidth="1"/>
+    <col min="9472" max="9472" width="18.85546875" style="2" customWidth="1"/>
+    <col min="9473" max="9473" width="13.140625" style="2" customWidth="1"/>
+    <col min="9474" max="9720" width="10.85546875" style="2"/>
+    <col min="9721" max="9721" width="5.85546875" style="2" customWidth="1"/>
+    <col min="9722" max="9722" width="13.28515625" style="2" customWidth="1"/>
+    <col min="9723" max="9723" width="4.85546875" style="2" customWidth="1"/>
+    <col min="9724" max="9724" width="33.140625" style="2" customWidth="1"/>
+    <col min="9725" max="9725" width="8.140625" style="2" customWidth="1"/>
+    <col min="9726" max="9726" width="6.85546875" style="2" customWidth="1"/>
+    <col min="9727" max="9727" width="14.28515625" style="2" customWidth="1"/>
+    <col min="9728" max="9728" width="18.85546875" style="2" customWidth="1"/>
+    <col min="9729" max="9729" width="13.140625" style="2" customWidth="1"/>
+    <col min="9730" max="9976" width="10.85546875" style="2"/>
+    <col min="9977" max="9977" width="5.85546875" style="2" customWidth="1"/>
+    <col min="9978" max="9978" width="13.28515625" style="2" customWidth="1"/>
+    <col min="9979" max="9979" width="4.85546875" style="2" customWidth="1"/>
+    <col min="9980" max="9980" width="33.140625" style="2" customWidth="1"/>
+    <col min="9981" max="9981" width="8.140625" style="2" customWidth="1"/>
+    <col min="9982" max="9982" width="6.85546875" style="2" customWidth="1"/>
+    <col min="9983" max="9983" width="14.28515625" style="2" customWidth="1"/>
+    <col min="9984" max="9984" width="18.85546875" style="2" customWidth="1"/>
+    <col min="9985" max="9985" width="13.140625" style="2" customWidth="1"/>
+    <col min="9986" max="10232" width="10.85546875" style="2"/>
+    <col min="10233" max="10233" width="5.85546875" style="2" customWidth="1"/>
+    <col min="10234" max="10234" width="13.28515625" style="2" customWidth="1"/>
+    <col min="10235" max="10235" width="4.85546875" style="2" customWidth="1"/>
+    <col min="10236" max="10236" width="33.140625" style="2" customWidth="1"/>
+    <col min="10237" max="10237" width="8.140625" style="2" customWidth="1"/>
+    <col min="10238" max="10238" width="6.85546875" style="2" customWidth="1"/>
+    <col min="10239" max="10239" width="14.28515625" style="2" customWidth="1"/>
+    <col min="10240" max="10240" width="18.85546875" style="2" customWidth="1"/>
+    <col min="10241" max="10241" width="13.140625" style="2" customWidth="1"/>
+    <col min="10242" max="10488" width="10.85546875" style="2"/>
+    <col min="10489" max="10489" width="5.85546875" style="2" customWidth="1"/>
+    <col min="10490" max="10490" width="13.28515625" style="2" customWidth="1"/>
+    <col min="10491" max="10491" width="4.85546875" style="2" customWidth="1"/>
+    <col min="10492" max="10492" width="33.140625" style="2" customWidth="1"/>
+    <col min="10493" max="10493" width="8.140625" style="2" customWidth="1"/>
+    <col min="10494" max="10494" width="6.85546875" style="2" customWidth="1"/>
+    <col min="10495" max="10495" width="14.28515625" style="2" customWidth="1"/>
+    <col min="10496" max="10496" width="18.85546875" style="2" customWidth="1"/>
+    <col min="10497" max="10497" width="13.140625" style="2" customWidth="1"/>
+    <col min="10498" max="10744" width="10.85546875" style="2"/>
+    <col min="10745" max="10745" width="5.85546875" style="2" customWidth="1"/>
+    <col min="10746" max="10746" width="13.28515625" style="2" customWidth="1"/>
+    <col min="10747" max="10747" width="4.85546875" style="2" customWidth="1"/>
+    <col min="10748" max="10748" width="33.140625" style="2" customWidth="1"/>
+    <col min="10749" max="10749" width="8.140625" style="2" customWidth="1"/>
+    <col min="10750" max="10750" width="6.85546875" style="2" customWidth="1"/>
+    <col min="10751" max="10751" width="14.28515625" style="2" customWidth="1"/>
+    <col min="10752" max="10752" width="18.85546875" style="2" customWidth="1"/>
+    <col min="10753" max="10753" width="13.140625" style="2" customWidth="1"/>
+    <col min="10754" max="11000" width="10.85546875" style="2"/>
+    <col min="11001" max="11001" width="5.85546875" style="2" customWidth="1"/>
+    <col min="11002" max="11002" width="13.28515625" style="2" customWidth="1"/>
+    <col min="11003" max="11003" width="4.85546875" style="2" customWidth="1"/>
+    <col min="11004" max="11004" width="33.140625" style="2" customWidth="1"/>
+    <col min="11005" max="11005" width="8.140625" style="2" customWidth="1"/>
+    <col min="11006" max="11006" width="6.85546875" style="2" customWidth="1"/>
+    <col min="11007" max="11007" width="14.28515625" style="2" customWidth="1"/>
+    <col min="11008" max="11008" width="18.85546875" style="2" customWidth="1"/>
+    <col min="11009" max="11009" width="13.140625" style="2" customWidth="1"/>
+    <col min="11010" max="11256" width="10.85546875" style="2"/>
+    <col min="11257" max="11257" width="5.85546875" style="2" customWidth="1"/>
+    <col min="11258" max="11258" width="13.28515625" style="2" customWidth="1"/>
+    <col min="11259" max="11259" width="4.85546875" style="2" customWidth="1"/>
+    <col min="11260" max="11260" width="33.140625" style="2" customWidth="1"/>
+    <col min="11261" max="11261" width="8.140625" style="2" customWidth="1"/>
+    <col min="11262" max="11262" width="6.85546875" style="2" customWidth="1"/>
+    <col min="11263" max="11263" width="14.28515625" style="2" customWidth="1"/>
+    <col min="11264" max="11264" width="18.85546875" style="2" customWidth="1"/>
+    <col min="11265" max="11265" width="13.140625" style="2" customWidth="1"/>
+    <col min="11266" max="11512" width="10.85546875" style="2"/>
+    <col min="11513" max="11513" width="5.85546875" style="2" customWidth="1"/>
+    <col min="11514" max="11514" width="13.28515625" style="2" customWidth="1"/>
+    <col min="11515" max="11515" width="4.85546875" style="2" customWidth="1"/>
+    <col min="11516" max="11516" width="33.140625" style="2" customWidth="1"/>
+    <col min="11517" max="11517" width="8.140625" style="2" customWidth="1"/>
+    <col min="11518" max="11518" width="6.85546875" style="2" customWidth="1"/>
+    <col min="11519" max="11519" width="14.28515625" style="2" customWidth="1"/>
+    <col min="11520" max="11520" width="18.85546875" style="2" customWidth="1"/>
+    <col min="11521" max="11521" width="13.140625" style="2" customWidth="1"/>
+    <col min="11522" max="11768" width="10.85546875" style="2"/>
+    <col min="11769" max="11769" width="5.85546875" style="2" customWidth="1"/>
+    <col min="11770" max="11770" width="13.28515625" style="2" customWidth="1"/>
+    <col min="11771" max="11771" width="4.85546875" style="2" customWidth="1"/>
+    <col min="11772" max="11772" width="33.140625" style="2" customWidth="1"/>
+    <col min="11773" max="11773" width="8.140625" style="2" customWidth="1"/>
+    <col min="11774" max="11774" width="6.85546875" style="2" customWidth="1"/>
+    <col min="11775" max="11775" width="14.28515625" style="2" customWidth="1"/>
+    <col min="11776" max="11776" width="18.85546875" style="2" customWidth="1"/>
+    <col min="11777" max="11777" width="13.140625" style="2" customWidth="1"/>
+    <col min="11778" max="12024" width="10.85546875" style="2"/>
+    <col min="12025" max="12025" width="5.85546875" style="2" customWidth="1"/>
+    <col min="12026" max="12026" width="13.28515625" style="2" customWidth="1"/>
+    <col min="12027" max="12027" width="4.85546875" style="2" customWidth="1"/>
+    <col min="12028" max="12028" width="33.140625" style="2" customWidth="1"/>
+    <col min="12029" max="12029" width="8.140625" style="2" customWidth="1"/>
+    <col min="12030" max="12030" width="6.85546875" style="2" customWidth="1"/>
+    <col min="12031" max="12031" width="14.28515625" style="2" customWidth="1"/>
+    <col min="12032" max="12032" width="18.85546875" style="2" customWidth="1"/>
+    <col min="12033" max="12033" width="13.140625" style="2" customWidth="1"/>
+    <col min="12034" max="12280" width="10.85546875" style="2"/>
+    <col min="12281" max="12281" width="5.85546875" style="2" customWidth="1"/>
+    <col min="12282" max="12282" width="13.28515625" style="2" customWidth="1"/>
+    <col min="12283" max="12283" width="4.85546875" style="2" customWidth="1"/>
+    <col min="12284" max="12284" width="33.140625" style="2" customWidth="1"/>
+    <col min="12285" max="12285" width="8.140625" style="2" customWidth="1"/>
+    <col min="12286" max="12286" width="6.85546875" style="2" customWidth="1"/>
+    <col min="12287" max="12287" width="14.28515625" style="2" customWidth="1"/>
+    <col min="12288" max="12288" width="18.85546875" style="2" customWidth="1"/>
+    <col min="12289" max="12289" width="13.140625" style="2" customWidth="1"/>
+    <col min="12290" max="12536" width="10.85546875" style="2"/>
+    <col min="12537" max="12537" width="5.85546875" style="2" customWidth="1"/>
+    <col min="12538" max="12538" width="13.28515625" style="2" customWidth="1"/>
+    <col min="12539" max="12539" width="4.85546875" style="2" customWidth="1"/>
+    <col min="12540" max="12540" width="33.140625" style="2" customWidth="1"/>
+    <col min="12541" max="12541" width="8.140625" style="2" customWidth="1"/>
+    <col min="12542" max="12542" width="6.85546875" style="2" customWidth="1"/>
+    <col min="12543" max="12543" width="14.28515625" style="2" customWidth="1"/>
+    <col min="12544" max="12544" width="18.85546875" style="2" customWidth="1"/>
+    <col min="12545" max="12545" width="13.140625" style="2" customWidth="1"/>
+    <col min="12546" max="12792" width="10.85546875" style="2"/>
+    <col min="12793" max="12793" width="5.85546875" style="2" customWidth="1"/>
+    <col min="12794" max="12794" width="13.28515625" style="2" customWidth="1"/>
+    <col min="12795" max="12795" width="4.85546875" style="2" customWidth="1"/>
+    <col min="12796" max="12796" width="33.140625" style="2" customWidth="1"/>
+    <col min="12797" max="12797" width="8.140625" style="2" customWidth="1"/>
+    <col min="12798" max="12798" width="6.85546875" style="2" customWidth="1"/>
+    <col min="12799" max="12799" width="14.28515625" style="2" customWidth="1"/>
+    <col min="12800" max="12800" width="18.85546875" style="2" customWidth="1"/>
+    <col min="12801" max="12801" width="13.140625" style="2" customWidth="1"/>
+    <col min="12802" max="13048" width="10.85546875" style="2"/>
+    <col min="13049" max="13049" width="5.85546875" style="2" customWidth="1"/>
+    <col min="13050" max="13050" width="13.28515625" style="2" customWidth="1"/>
+    <col min="13051" max="13051" width="4.85546875" style="2" customWidth="1"/>
+    <col min="13052" max="13052" width="33.140625" style="2" customWidth="1"/>
+    <col min="13053" max="13053" width="8.140625" style="2" customWidth="1"/>
+    <col min="13054" max="13054" width="6.85546875" style="2" customWidth="1"/>
+    <col min="13055" max="13055" width="14.28515625" style="2" customWidth="1"/>
+    <col min="13056" max="13056" width="18.85546875" style="2" customWidth="1"/>
+    <col min="13057" max="13057" width="13.140625" style="2" customWidth="1"/>
+    <col min="13058" max="13304" width="10.85546875" style="2"/>
+    <col min="13305" max="13305" width="5.85546875" style="2" customWidth="1"/>
+    <col min="13306" max="13306" width="13.28515625" style="2" customWidth="1"/>
+    <col min="13307" max="13307" width="4.85546875" style="2" customWidth="1"/>
+    <col min="13308" max="13308" width="33.140625" style="2" customWidth="1"/>
+    <col min="13309" max="13309" width="8.140625" style="2" customWidth="1"/>
+    <col min="13310" max="13310" width="6.85546875" style="2" customWidth="1"/>
+    <col min="13311" max="13311" width="14.28515625" style="2" customWidth="1"/>
+    <col min="13312" max="13312" width="18.85546875" style="2" customWidth="1"/>
+    <col min="13313" max="13313" width="13.140625" style="2" customWidth="1"/>
+    <col min="13314" max="13560" width="10.85546875" style="2"/>
+    <col min="13561" max="13561" width="5.85546875" style="2" customWidth="1"/>
+    <col min="13562" max="13562" width="13.28515625" style="2" customWidth="1"/>
+    <col min="13563" max="13563" width="4.85546875" style="2" customWidth="1"/>
+    <col min="13564" max="13564" width="33.140625" style="2" customWidth="1"/>
+    <col min="13565" max="13565" width="8.140625" style="2" customWidth="1"/>
+    <col min="13566" max="13566" width="6.85546875" style="2" customWidth="1"/>
+    <col min="13567" max="13567" width="14.28515625" style="2" customWidth="1"/>
+    <col min="13568" max="13568" width="18.85546875" style="2" customWidth="1"/>
+    <col min="13569" max="13569" width="13.140625" style="2" customWidth="1"/>
+    <col min="13570" max="13816" width="10.85546875" style="2"/>
+    <col min="13817" max="13817" width="5.85546875" style="2" customWidth="1"/>
+    <col min="13818" max="13818" width="13.28515625" style="2" customWidth="1"/>
+    <col min="13819" max="13819" width="4.85546875" style="2" customWidth="1"/>
+    <col min="13820" max="13820" width="33.140625" style="2" customWidth="1"/>
+    <col min="13821" max="13821" width="8.140625" style="2" customWidth="1"/>
+    <col min="13822" max="13822" width="6.85546875" style="2" customWidth="1"/>
+    <col min="13823" max="13823" width="14.28515625" style="2" customWidth="1"/>
+    <col min="13824" max="13824" width="18.85546875" style="2" customWidth="1"/>
+    <col min="13825" max="13825" width="13.140625" style="2" customWidth="1"/>
+    <col min="13826" max="14072" width="10.85546875" style="2"/>
+    <col min="14073" max="14073" width="5.85546875" style="2" customWidth="1"/>
+    <col min="14074" max="14074" width="13.28515625" style="2" customWidth="1"/>
+    <col min="14075" max="14075" width="4.85546875" style="2" customWidth="1"/>
+    <col min="14076" max="14076" width="33.140625" style="2" customWidth="1"/>
+    <col min="14077" max="14077" width="8.140625" style="2" customWidth="1"/>
+    <col min="14078" max="14078" width="6.85546875" style="2" customWidth="1"/>
+    <col min="14079" max="14079" width="14.28515625" style="2" customWidth="1"/>
+    <col min="14080" max="14080" width="18.85546875" style="2" customWidth="1"/>
+    <col min="14081" max="14081" width="13.140625" style="2" customWidth="1"/>
+    <col min="14082" max="14328" width="10.85546875" style="2"/>
+    <col min="14329" max="14329" width="5.85546875" style="2" customWidth="1"/>
+    <col min="14330" max="14330" width="13.28515625" style="2" customWidth="1"/>
+    <col min="14331" max="14331" width="4.85546875" style="2" customWidth="1"/>
+    <col min="14332" max="14332" width="33.140625" style="2" customWidth="1"/>
+    <col min="14333" max="14333" width="8.140625" style="2" customWidth="1"/>
+    <col min="14334" max="14334" width="6.85546875" style="2" customWidth="1"/>
+    <col min="14335" max="14335" width="14.28515625" style="2" customWidth="1"/>
+    <col min="14336" max="14336" width="18.85546875" style="2" customWidth="1"/>
+    <col min="14337" max="14337" width="13.140625" style="2" customWidth="1"/>
+    <col min="14338" max="14584" width="10.85546875" style="2"/>
+    <col min="14585" max="14585" width="5.85546875" style="2" customWidth="1"/>
+    <col min="14586" max="14586" width="13.28515625" style="2" customWidth="1"/>
+    <col min="14587" max="14587" width="4.85546875" style="2" customWidth="1"/>
+    <col min="14588" max="14588" width="33.140625" style="2" customWidth="1"/>
+    <col min="14589" max="14589" width="8.140625" style="2" customWidth="1"/>
+    <col min="14590" max="14590" width="6.85546875" style="2" customWidth="1"/>
+    <col min="14591" max="14591" width="14.28515625" style="2" customWidth="1"/>
+    <col min="14592" max="14592" width="18.85546875" style="2" customWidth="1"/>
+    <col min="14593" max="14593" width="13.140625" style="2" customWidth="1"/>
+    <col min="14594" max="14840" width="10.85546875" style="2"/>
+    <col min="14841" max="14841" width="5.85546875" style="2" customWidth="1"/>
+    <col min="14842" max="14842" width="13.28515625" style="2" customWidth="1"/>
+    <col min="14843" max="14843" width="4.85546875" style="2" customWidth="1"/>
+    <col min="14844" max="14844" width="33.140625" style="2" customWidth="1"/>
+    <col min="14845" max="14845" width="8.140625" style="2" customWidth="1"/>
+    <col min="14846" max="14846" width="6.85546875" style="2" customWidth="1"/>
+    <col min="14847" max="14847" width="14.28515625" style="2" customWidth="1"/>
+    <col min="14848" max="14848" width="18.85546875" style="2" customWidth="1"/>
+    <col min="14849" max="14849" width="13.140625" style="2" customWidth="1"/>
+    <col min="14850" max="15096" width="10.85546875" style="2"/>
+    <col min="15097" max="15097" width="5.85546875" style="2" customWidth="1"/>
+    <col min="15098" max="15098" width="13.28515625" style="2" customWidth="1"/>
+    <col min="15099" max="15099" width="4.85546875" style="2" customWidth="1"/>
+    <col min="15100" max="15100" width="33.140625" style="2" customWidth="1"/>
+    <col min="15101" max="15101" width="8.140625" style="2" customWidth="1"/>
+    <col min="15102" max="15102" width="6.85546875" style="2" customWidth="1"/>
+    <col min="15103" max="15103" width="14.28515625" style="2" customWidth="1"/>
+    <col min="15104" max="15104" width="18.85546875" style="2" customWidth="1"/>
+    <col min="15105" max="15105" width="13.140625" style="2" customWidth="1"/>
+    <col min="15106" max="15352" width="10.85546875" style="2"/>
+    <col min="15353" max="15353" width="5.85546875" style="2" customWidth="1"/>
+    <col min="15354" max="15354" width="13.28515625" style="2" customWidth="1"/>
+    <col min="15355" max="15355" width="4.85546875" style="2" customWidth="1"/>
+    <col min="15356" max="15356" width="33.140625" style="2" customWidth="1"/>
+    <col min="15357" max="15357" width="8.140625" style="2" customWidth="1"/>
+    <col min="15358" max="15358" width="6.85546875" style="2" customWidth="1"/>
+    <col min="15359" max="15359" width="14.28515625" style="2" customWidth="1"/>
+    <col min="15360" max="15360" width="18.85546875" style="2" customWidth="1"/>
+    <col min="15361" max="15361" width="13.140625" style="2" customWidth="1"/>
+    <col min="15362" max="15608" width="10.85546875" style="2"/>
+    <col min="15609" max="15609" width="5.85546875" style="2" customWidth="1"/>
+    <col min="15610" max="15610" width="13.28515625" style="2" customWidth="1"/>
+    <col min="15611" max="15611" width="4.85546875" style="2" customWidth="1"/>
+    <col min="15612" max="15612" width="33.140625" style="2" customWidth="1"/>
+    <col min="15613" max="15613" width="8.140625" style="2" customWidth="1"/>
+    <col min="15614" max="15614" width="6.85546875" style="2" customWidth="1"/>
+    <col min="15615" max="15615" width="14.28515625" style="2" customWidth="1"/>
+    <col min="15616" max="15616" width="18.85546875" style="2" customWidth="1"/>
+    <col min="15617" max="15617" width="13.140625" style="2" customWidth="1"/>
+    <col min="15618" max="15864" width="10.85546875" style="2"/>
+    <col min="15865" max="15865" width="5.85546875" style="2" customWidth="1"/>
+    <col min="15866" max="15866" width="13.28515625" style="2" customWidth="1"/>
+    <col min="15867" max="15867" width="4.85546875" style="2" customWidth="1"/>
+    <col min="15868" max="15868" width="33.140625" style="2" customWidth="1"/>
+    <col min="15869" max="15869" width="8.140625" style="2" customWidth="1"/>
+    <col min="15870" max="15870" width="6.85546875" style="2" customWidth="1"/>
+    <col min="15871" max="15871" width="14.28515625" style="2" customWidth="1"/>
+    <col min="15872" max="15872" width="18.85546875" style="2" customWidth="1"/>
+    <col min="15873" max="15873" width="13.140625" style="2" customWidth="1"/>
+    <col min="15874" max="16120" width="10.85546875" style="2"/>
+    <col min="16121" max="16121" width="5.85546875" style="2" customWidth="1"/>
+    <col min="16122" max="16122" width="13.28515625" style="2" customWidth="1"/>
+    <col min="16123" max="16123" width="4.85546875" style="2" customWidth="1"/>
+    <col min="16124" max="16124" width="33.140625" style="2" customWidth="1"/>
+    <col min="16125" max="16125" width="8.140625" style="2" customWidth="1"/>
+    <col min="16126" max="16126" width="6.85546875" style="2" customWidth="1"/>
+    <col min="16127" max="16127" width="14.28515625" style="2" customWidth="1"/>
+    <col min="16128" max="16128" width="18.85546875" style="2" customWidth="1"/>
+    <col min="16129" max="16129" width="13.140625" style="2" customWidth="1"/>
+    <col min="16130" max="16384" width="10.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:41" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="43"/>
-      <c r="S1" s="43"/>
-      <c r="T1" s="43"/>
-      <c r="U1" s="43"/>
-      <c r="V1" s="43"/>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
-      <c r="AB1" s="43"/>
-      <c r="AC1" s="43"/>
-      <c r="AD1" s="43"/>
-      <c r="AE1" s="43"/>
-      <c r="AF1" s="43"/>
-      <c r="AG1" s="43"/>
-      <c r="AH1" s="43"/>
-      <c r="AI1" s="43"/>
-      <c r="AJ1" s="43"/>
-      <c r="AK1" s="43"/>
-      <c r="AL1" s="43"/>
-      <c r="AM1" s="43"/>
-      <c r="AN1" s="43"/>
-      <c r="AO1" s="43"/>
-    </row>
-    <row r="2" spans="1:41" ht="18" x14ac:dyDescent="0.3">
-      <c r="A2" s="43" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="34"/>
+      <c r="AA1" s="34"/>
+      <c r="AB1" s="34"/>
+      <c r="AC1" s="34"/>
+      <c r="AD1" s="34"/>
+      <c r="AE1" s="34"/>
+      <c r="AF1" s="34"/>
+      <c r="AG1" s="34"/>
+      <c r="AH1" s="34"/>
+      <c r="AI1" s="34"/>
+      <c r="AJ1" s="34"/>
+      <c r="AK1" s="34"/>
+      <c r="AL1" s="34"/>
+      <c r="AM1" s="34"/>
+      <c r="AN1" s="34"/>
+      <c r="AO1" s="34"/>
+    </row>
+    <row r="2" spans="1:41" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="43"/>
-      <c r="O2" s="43"/>
-      <c r="P2" s="43"/>
-      <c r="Q2" s="43"/>
-      <c r="R2" s="43"/>
-      <c r="S2" s="43"/>
-      <c r="T2" s="43"/>
-      <c r="U2" s="43"/>
-      <c r="V2" s="43"/>
-      <c r="W2" s="43"/>
-      <c r="X2" s="43"/>
-      <c r="Y2" s="43"/>
-      <c r="Z2" s="43"/>
-      <c r="AA2" s="43"/>
-      <c r="AB2" s="43"/>
-      <c r="AC2" s="43"/>
-      <c r="AD2" s="43"/>
-      <c r="AE2" s="43"/>
-      <c r="AF2" s="43"/>
-      <c r="AG2" s="43"/>
-      <c r="AH2" s="43"/>
-      <c r="AI2" s="43"/>
-      <c r="AJ2" s="43"/>
-      <c r="AK2" s="43"/>
-      <c r="AL2" s="43"/>
-      <c r="AM2" s="43"/>
-      <c r="AN2" s="43"/>
-      <c r="AO2" s="43"/>
-    </row>
-    <row r="3" spans="1:41" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="43" t="s">
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
+      <c r="N2" s="34"/>
+      <c r="O2" s="34"/>
+      <c r="P2" s="34"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
+      <c r="T2" s="34"/>
+      <c r="U2" s="34"/>
+      <c r="V2" s="34"/>
+      <c r="W2" s="34"/>
+      <c r="X2" s="34"/>
+      <c r="Y2" s="34"/>
+      <c r="Z2" s="34"/>
+      <c r="AA2" s="34"/>
+      <c r="AB2" s="34"/>
+      <c r="AC2" s="34"/>
+      <c r="AD2" s="34"/>
+      <c r="AE2" s="34"/>
+      <c r="AF2" s="34"/>
+      <c r="AG2" s="34"/>
+      <c r="AH2" s="34"/>
+      <c r="AI2" s="34"/>
+      <c r="AJ2" s="34"/>
+      <c r="AK2" s="34"/>
+      <c r="AL2" s="34"/>
+      <c r="AM2" s="34"/>
+      <c r="AN2" s="34"/>
+      <c r="AO2" s="34"/>
+    </row>
+    <row r="3" spans="1:41" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="43"/>
-      <c r="M3" s="43"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="43"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="43"/>
-      <c r="S3" s="43"/>
-      <c r="T3" s="43"/>
-      <c r="U3" s="43"/>
-      <c r="V3" s="43"/>
-      <c r="W3" s="43"/>
-      <c r="X3" s="43"/>
-      <c r="Y3" s="43"/>
-      <c r="Z3" s="43"/>
-      <c r="AA3" s="43"/>
-      <c r="AB3" s="43"/>
-      <c r="AC3" s="43"/>
-      <c r="AD3" s="43"/>
-      <c r="AE3" s="43"/>
-      <c r="AF3" s="43"/>
-      <c r="AG3" s="43"/>
-      <c r="AH3" s="43"/>
-      <c r="AI3" s="43"/>
-      <c r="AJ3" s="43"/>
-      <c r="AK3" s="43"/>
-      <c r="AL3" s="43"/>
-      <c r="AM3" s="43"/>
-      <c r="AN3" s="43"/>
-      <c r="AO3" s="43"/>
-    </row>
-    <row r="4" spans="1:41" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="43" t="s">
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
+      <c r="M3" s="34"/>
+      <c r="N3" s="34"/>
+      <c r="O3" s="34"/>
+      <c r="P3" s="34"/>
+      <c r="Q3" s="34"/>
+      <c r="R3" s="34"/>
+      <c r="S3" s="34"/>
+      <c r="T3" s="34"/>
+      <c r="U3" s="34"/>
+      <c r="V3" s="34"/>
+      <c r="W3" s="34"/>
+      <c r="X3" s="34"/>
+      <c r="Y3" s="34"/>
+      <c r="Z3" s="34"/>
+      <c r="AA3" s="34"/>
+      <c r="AB3" s="34"/>
+      <c r="AC3" s="34"/>
+      <c r="AD3" s="34"/>
+      <c r="AE3" s="34"/>
+      <c r="AF3" s="34"/>
+      <c r="AG3" s="34"/>
+      <c r="AH3" s="34"/>
+      <c r="AI3" s="34"/>
+      <c r="AJ3" s="34"/>
+      <c r="AK3" s="34"/>
+      <c r="AL3" s="34"/>
+      <c r="AM3" s="34"/>
+      <c r="AN3" s="34"/>
+      <c r="AO3" s="34"/>
+    </row>
+    <row r="4" spans="1:41" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="43"/>
-      <c r="M4" s="43"/>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="43"/>
-      <c r="T4" s="43"/>
-      <c r="U4" s="43"/>
-      <c r="V4" s="43"/>
-      <c r="W4" s="43"/>
-      <c r="X4" s="43"/>
-      <c r="Y4" s="43"/>
-      <c r="Z4" s="43"/>
-      <c r="AA4" s="43"/>
-      <c r="AB4" s="43"/>
-      <c r="AC4" s="43"/>
-      <c r="AD4" s="43"/>
-      <c r="AE4" s="43"/>
-      <c r="AF4" s="43"/>
-      <c r="AG4" s="43"/>
-      <c r="AH4" s="43"/>
-      <c r="AI4" s="43"/>
-      <c r="AJ4" s="43"/>
-      <c r="AK4" s="43"/>
-      <c r="AL4" s="43"/>
-      <c r="AM4" s="43"/>
-      <c r="AN4" s="43"/>
-      <c r="AO4" s="43"/>
-    </row>
-    <row r="5" spans="1:41" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="34"/>
+      <c r="P4" s="34"/>
+      <c r="Q4" s="34"/>
+      <c r="R4" s="34"/>
+      <c r="S4" s="34"/>
+      <c r="T4" s="34"/>
+      <c r="U4" s="34"/>
+      <c r="V4" s="34"/>
+      <c r="W4" s="34"/>
+      <c r="X4" s="34"/>
+      <c r="Y4" s="34"/>
+      <c r="Z4" s="34"/>
+      <c r="AA4" s="34"/>
+      <c r="AB4" s="34"/>
+      <c r="AC4" s="34"/>
+      <c r="AD4" s="34"/>
+      <c r="AE4" s="34"/>
+      <c r="AF4" s="34"/>
+      <c r="AG4" s="34"/>
+      <c r="AH4" s="34"/>
+      <c r="AI4" s="34"/>
+      <c r="AJ4" s="34"/>
+      <c r="AK4" s="34"/>
+      <c r="AL4" s="34"/>
+      <c r="AM4" s="34"/>
+      <c r="AN4" s="34"/>
+      <c r="AO4" s="34"/>
+    </row>
+    <row r="5" spans="1:41" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -3821,49 +4007,49 @@
       <c r="AA5" s="3"/>
       <c r="AB5" s="3"/>
     </row>
-    <row r="6" spans="1:41" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:41" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="57" t="s">
+      <c r="B6" s="37"/>
+      <c r="C6" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="60" t="s">
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
-      <c r="L6" s="62"/>
-      <c r="M6" s="46" t="s">
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
+      <c r="J6" s="75"/>
+      <c r="K6" s="75"/>
+      <c r="L6" s="76"/>
+      <c r="M6" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="N6" s="69"/>
-      <c r="O6" s="69"/>
-      <c r="P6" s="69"/>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="69"/>
-      <c r="S6" s="69"/>
-      <c r="T6" s="70"/>
-      <c r="U6" s="55" t="s">
+      <c r="N6" s="72"/>
+      <c r="O6" s="72"/>
+      <c r="P6" s="72"/>
+      <c r="Q6" s="72"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="73"/>
+      <c r="U6" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="55"/>
-      <c r="W6" s="55"/>
-      <c r="X6" s="55"/>
-      <c r="Y6" s="55"/>
-      <c r="Z6" s="55"/>
-      <c r="AA6" s="55"/>
-      <c r="AB6" s="55"/>
-      <c r="AC6" s="55"/>
-      <c r="AD6" s="55"/>
-      <c r="AE6" s="55"/>
-      <c r="AF6" s="55"/>
+      <c r="V6" s="32"/>
+      <c r="W6" s="32"/>
+      <c r="X6" s="32"/>
+      <c r="Y6" s="32"/>
+      <c r="Z6" s="32"/>
+      <c r="AA6" s="32"/>
+      <c r="AB6" s="32"/>
+      <c r="AC6" s="32"/>
+      <c r="AD6" s="32"/>
+      <c r="AE6" s="32"/>
+      <c r="AF6" s="32"/>
       <c r="AG6" s="66" t="s">
         <v>27</v>
       </c>
@@ -3876,165 +4062,165 @@
       <c r="AN6" s="66"/>
       <c r="AO6" s="66"/>
     </row>
-    <row r="7" spans="1:41" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="67" t="s">
+    <row r="7" spans="1:41" ht="29.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="68"/>
-      <c r="C7" s="68"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="63" t="s">
+      <c r="B7" s="71"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="71"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="64"/>
-      <c r="L7" s="64"/>
-      <c r="M7" s="64"/>
-      <c r="N7" s="64"/>
-      <c r="O7" s="64"/>
-      <c r="P7" s="64"/>
-      <c r="Q7" s="64"/>
-      <c r="R7" s="64"/>
-      <c r="S7" s="64"/>
-      <c r="T7" s="64"/>
-      <c r="U7" s="64"/>
-      <c r="V7" s="64"/>
-      <c r="W7" s="64"/>
-      <c r="X7" s="64"/>
-      <c r="Y7" s="64"/>
-      <c r="Z7" s="64"/>
-      <c r="AA7" s="64"/>
-      <c r="AB7" s="64"/>
-      <c r="AC7" s="64"/>
-      <c r="AD7" s="64"/>
-      <c r="AE7" s="64"/>
-      <c r="AF7" s="64"/>
-      <c r="AG7" s="64"/>
-      <c r="AH7" s="64"/>
-      <c r="AI7" s="64"/>
-      <c r="AJ7" s="64"/>
-      <c r="AK7" s="64"/>
-      <c r="AL7" s="64"/>
-      <c r="AM7" s="64"/>
-      <c r="AN7" s="64"/>
-      <c r="AO7" s="65"/>
-    </row>
-    <row r="8" spans="1:41" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="35" t="s">
+      <c r="H7" s="63"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="63"/>
+      <c r="K7" s="63"/>
+      <c r="L7" s="63"/>
+      <c r="M7" s="63"/>
+      <c r="N7" s="63"/>
+      <c r="O7" s="63"/>
+      <c r="P7" s="63"/>
+      <c r="Q7" s="63"/>
+      <c r="R7" s="63"/>
+      <c r="S7" s="63"/>
+      <c r="T7" s="63"/>
+      <c r="U7" s="63"/>
+      <c r="V7" s="63"/>
+      <c r="W7" s="63"/>
+      <c r="X7" s="63"/>
+      <c r="Y7" s="63"/>
+      <c r="Z7" s="63"/>
+      <c r="AA7" s="63"/>
+      <c r="AB7" s="63"/>
+      <c r="AC7" s="63"/>
+      <c r="AD7" s="63"/>
+      <c r="AE7" s="63"/>
+      <c r="AF7" s="63"/>
+      <c r="AG7" s="63"/>
+      <c r="AH7" s="63"/>
+      <c r="AI7" s="63"/>
+      <c r="AJ7" s="63"/>
+      <c r="AK7" s="63"/>
+      <c r="AL7" s="63"/>
+      <c r="AM7" s="63"/>
+      <c r="AN7" s="63"/>
+      <c r="AO7" s="64"/>
+    </row>
+    <row r="8" spans="1:41" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="57" t="s">
+      <c r="B8" s="44"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="58"/>
-      <c r="H8" s="58"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="58"/>
-      <c r="K8" s="58"/>
-      <c r="L8" s="58"/>
-      <c r="M8" s="58"/>
-      <c r="N8" s="58"/>
-      <c r="O8" s="58"/>
-      <c r="P8" s="58"/>
-      <c r="Q8" s="58"/>
-      <c r="R8" s="58"/>
-      <c r="S8" s="58"/>
-      <c r="T8" s="58"/>
-      <c r="U8" s="58"/>
-      <c r="V8" s="58"/>
-      <c r="W8" s="58"/>
-      <c r="X8" s="58"/>
-      <c r="Y8" s="58"/>
-      <c r="Z8" s="58"/>
-      <c r="AA8" s="58"/>
-      <c r="AB8" s="58"/>
-      <c r="AC8" s="58"/>
-      <c r="AD8" s="58"/>
-      <c r="AE8" s="58"/>
-      <c r="AF8" s="58"/>
-      <c r="AG8" s="58"/>
-      <c r="AH8" s="58"/>
-      <c r="AI8" s="58"/>
-      <c r="AJ8" s="58"/>
-      <c r="AK8" s="58"/>
-      <c r="AL8" s="58"/>
-      <c r="AM8" s="58"/>
-      <c r="AN8" s="58"/>
-      <c r="AO8" s="59"/>
-    </row>
-    <row r="9" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="68"/>
+      <c r="K8" s="68"/>
+      <c r="L8" s="68"/>
+      <c r="M8" s="68"/>
+      <c r="N8" s="68"/>
+      <c r="O8" s="68"/>
+      <c r="P8" s="68"/>
+      <c r="Q8" s="68"/>
+      <c r="R8" s="68"/>
+      <c r="S8" s="68"/>
+      <c r="T8" s="68"/>
+      <c r="U8" s="68"/>
+      <c r="V8" s="68"/>
+      <c r="W8" s="68"/>
+      <c r="X8" s="68"/>
+      <c r="Y8" s="68"/>
+      <c r="Z8" s="68"/>
+      <c r="AA8" s="68"/>
+      <c r="AB8" s="68"/>
+      <c r="AC8" s="68"/>
+      <c r="AD8" s="68"/>
+      <c r="AE8" s="68"/>
+      <c r="AF8" s="68"/>
+      <c r="AG8" s="68"/>
+      <c r="AH8" s="68"/>
+      <c r="AI8" s="68"/>
+      <c r="AJ8" s="68"/>
+      <c r="AK8" s="68"/>
+      <c r="AL8" s="68"/>
+      <c r="AM8" s="68"/>
+      <c r="AN8" s="68"/>
+      <c r="AO8" s="69"/>
+    </row>
+    <row r="9" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="6"/>
     </row>
-    <row r="10" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="41" t="s">
+    <row r="10" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
       <c r="I10" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="J10" s="52" t="s">
+      <c r="J10" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="K10" s="53"/>
-      <c r="L10" s="53"/>
-      <c r="M10" s="53"/>
-      <c r="N10" s="53"/>
-      <c r="O10" s="53"/>
-      <c r="P10" s="53"/>
-      <c r="Q10" s="53"/>
-      <c r="R10" s="53"/>
-      <c r="S10" s="53"/>
-      <c r="T10" s="53"/>
-      <c r="U10" s="53"/>
-      <c r="V10" s="53"/>
-      <c r="W10" s="53"/>
-      <c r="X10" s="53"/>
-      <c r="Y10" s="53"/>
-      <c r="Z10" s="53"/>
-      <c r="AA10" s="53"/>
-      <c r="AB10" s="53"/>
-      <c r="AC10" s="53"/>
-      <c r="AD10" s="53"/>
-      <c r="AE10" s="53"/>
-      <c r="AF10" s="53"/>
-      <c r="AG10" s="53"/>
-      <c r="AH10" s="53"/>
-      <c r="AI10" s="53"/>
-      <c r="AJ10" s="53"/>
-      <c r="AK10" s="53"/>
-      <c r="AL10" s="53"/>
-      <c r="AM10" s="53"/>
-      <c r="AN10" s="53"/>
-      <c r="AO10" s="54"/>
-    </row>
-    <row r="11" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="41"/>
-      <c r="B11" s="41"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="31"/>
+      <c r="R10" s="31"/>
+      <c r="S10" s="31"/>
+      <c r="T10" s="31"/>
+      <c r="U10" s="31"/>
+      <c r="V10" s="31"/>
+      <c r="W10" s="31"/>
+      <c r="X10" s="31"/>
+      <c r="Y10" s="31"/>
+      <c r="Z10" s="31"/>
+      <c r="AA10" s="31"/>
+      <c r="AB10" s="31"/>
+      <c r="AC10" s="31"/>
+      <c r="AD10" s="31"/>
+      <c r="AE10" s="31"/>
+      <c r="AF10" s="31"/>
+      <c r="AG10" s="31"/>
+      <c r="AH10" s="31"/>
+      <c r="AI10" s="31"/>
+      <c r="AJ10" s="31"/>
+      <c r="AK10" s="31"/>
+      <c r="AL10" s="31"/>
+      <c r="AM10" s="31"/>
+      <c r="AN10" s="31"/>
+      <c r="AO10" s="65"/>
+    </row>
+    <row r="11" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="50"/>
+      <c r="B11" s="50"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
       <c r="I11" s="14" t="s">
         <v>10</v>
       </c>
@@ -4135,7 +4321,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:41" s="23" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:41" s="23" customFormat="1" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>1</v>
       </c>
@@ -4186,7 +4372,7 @@
       <c r="AN12" s="21"/>
       <c r="AO12" s="21"/>
     </row>
-    <row r="13" spans="1:41" s="23" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:41" s="23" customFormat="1" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>2</v>
       </c>
@@ -4237,7 +4423,7 @@
       <c r="AN13" s="21"/>
       <c r="AO13" s="21"/>
     </row>
-    <row r="14" spans="1:41" s="23" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:41" s="23" customFormat="1" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>3</v>
       </c>
@@ -4288,7 +4474,7 @@
       <c r="AN14" s="21"/>
       <c r="AO14" s="21"/>
     </row>
-    <row r="15" spans="1:41" s="23" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:41" s="23" customFormat="1" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
         <v>4</v>
       </c>
@@ -4339,7 +4525,7 @@
       <c r="AN15" s="21"/>
       <c r="AO15" s="21"/>
     </row>
-    <row r="16" spans="1:41" s="23" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:41" s="23" customFormat="1" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>5</v>
       </c>
@@ -4390,7 +4576,7 @@
       <c r="AN16" s="21"/>
       <c r="AO16" s="21"/>
     </row>
-    <row r="17" spans="1:41" s="23" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:41" s="23" customFormat="1" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
         <v>6</v>
       </c>
@@ -4441,7 +4627,7 @@
       <c r="AN17" s="21"/>
       <c r="AO17" s="21"/>
     </row>
-    <row r="18" spans="1:41" s="23" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:41" s="23" customFormat="1" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <v>7</v>
       </c>
@@ -4492,7 +4678,7 @@
       <c r="AN18" s="21"/>
       <c r="AO18" s="21"/>
     </row>
-    <row r="19" spans="1:41" s="23" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:41" s="23" customFormat="1" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
         <v>8</v>
       </c>
@@ -4543,7 +4729,7 @@
       <c r="AN19" s="21"/>
       <c r="AO19" s="21"/>
     </row>
-    <row r="20" spans="1:41" s="23" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:41" s="23" customFormat="1" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
         <v>9</v>
       </c>
@@ -4594,7 +4780,7 @@
       <c r="AN20" s="21"/>
       <c r="AO20" s="21"/>
     </row>
-    <row r="21" spans="1:41" s="23" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:41" s="23" customFormat="1" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7">
         <v>10</v>
       </c>
@@ -4645,7 +4831,7 @@
       <c r="AN21" s="21"/>
       <c r="AO21" s="21"/>
     </row>
-    <row r="22" spans="1:41" s="23" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:41" s="23" customFormat="1" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7">
         <v>11</v>
       </c>
@@ -4696,7 +4882,7 @@
       <c r="AN22" s="21"/>
       <c r="AO22" s="21"/>
     </row>
-    <row r="23" spans="1:41" s="23" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:41" s="23" customFormat="1" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7">
         <v>12</v>
       </c>
@@ -4747,7 +4933,7 @@
       <c r="AN23" s="21"/>
       <c r="AO23" s="21"/>
     </row>
-    <row r="24" spans="1:41" s="23" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:41" s="23" customFormat="1" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
         <v>13</v>
       </c>
@@ -4798,215 +4984,214 @@
       <c r="AN24" s="21"/>
       <c r="AO24" s="21"/>
     </row>
-    <row r="25" spans="1:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="15"/>
     </row>
-    <row r="26" spans="1:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="15"/>
     </row>
-    <row r="27" spans="1:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="15"/>
     </row>
-    <row r="28" spans="1:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:41" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="15"/>
     </row>
-    <row r="29" spans="1:41" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="32" t="s">
+    <row r="29" spans="1:41" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="33"/>
-      <c r="C29" s="33"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="33"/>
-      <c r="H29" s="33"/>
-      <c r="I29" s="33"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="33"/>
-      <c r="L29" s="33"/>
-      <c r="M29" s="33"/>
-      <c r="N29" s="33"/>
-      <c r="O29" s="33"/>
-      <c r="P29" s="33"/>
-      <c r="Q29" s="33"/>
-      <c r="R29" s="33"/>
-      <c r="S29" s="33"/>
-      <c r="T29" s="33"/>
-      <c r="U29" s="33"/>
-      <c r="V29" s="34"/>
-      <c r="W29" s="32" t="s">
+      <c r="B29" s="54"/>
+      <c r="C29" s="54"/>
+      <c r="D29" s="54"/>
+      <c r="E29" s="54"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="54"/>
+      <c r="K29" s="54"/>
+      <c r="L29" s="54"/>
+      <c r="M29" s="54"/>
+      <c r="N29" s="54"/>
+      <c r="O29" s="54"/>
+      <c r="P29" s="54"/>
+      <c r="Q29" s="54"/>
+      <c r="R29" s="54"/>
+      <c r="S29" s="54"/>
+      <c r="T29" s="54"/>
+      <c r="U29" s="54"/>
+      <c r="V29" s="55"/>
+      <c r="W29" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="X29" s="33"/>
-      <c r="Y29" s="33"/>
-      <c r="Z29" s="33"/>
-      <c r="AA29" s="33"/>
-      <c r="AB29" s="33"/>
-      <c r="AC29" s="33"/>
-      <c r="AD29" s="33"/>
-      <c r="AE29" s="33"/>
-      <c r="AF29" s="33"/>
-      <c r="AG29" s="33"/>
-      <c r="AH29" s="33"/>
-      <c r="AI29" s="33"/>
-      <c r="AJ29" s="33"/>
-      <c r="AK29" s="33"/>
-      <c r="AL29" s="33"/>
-      <c r="AM29" s="33"/>
-      <c r="AN29" s="33"/>
-      <c r="AO29" s="34"/>
-    </row>
-    <row r="30" spans="1:41" ht="45.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="71" t="s">
+      <c r="X29" s="54"/>
+      <c r="Y29" s="54"/>
+      <c r="Z29" s="54"/>
+      <c r="AA29" s="54"/>
+      <c r="AB29" s="54"/>
+      <c r="AC29" s="54"/>
+      <c r="AD29" s="54"/>
+      <c r="AE29" s="54"/>
+      <c r="AF29" s="54"/>
+      <c r="AG29" s="54"/>
+      <c r="AH29" s="54"/>
+      <c r="AI29" s="54"/>
+      <c r="AJ29" s="54"/>
+      <c r="AK29" s="54"/>
+      <c r="AL29" s="54"/>
+      <c r="AM29" s="54"/>
+      <c r="AN29" s="54"/>
+      <c r="AO29" s="55"/>
+    </row>
+    <row r="30" spans="1:41" ht="45.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="72"/>
-      <c r="C30" s="72"/>
-      <c r="D30" s="72"/>
-      <c r="E30" s="72"/>
-      <c r="F30" s="72"/>
-      <c r="G30" s="72"/>
-      <c r="H30" s="72"/>
-      <c r="I30" s="72"/>
-      <c r="J30" s="72"/>
-      <c r="K30" s="72"/>
-      <c r="L30" s="72"/>
-      <c r="M30" s="72"/>
-      <c r="N30" s="72"/>
-      <c r="O30" s="72"/>
-      <c r="P30" s="72"/>
-      <c r="Q30" s="72"/>
-      <c r="R30" s="72"/>
-      <c r="S30" s="72"/>
-      <c r="T30" s="72"/>
-      <c r="U30" s="72"/>
-      <c r="V30" s="73"/>
-      <c r="W30" s="71"/>
-      <c r="X30" s="72"/>
-      <c r="Y30" s="72"/>
-      <c r="Z30" s="72"/>
-      <c r="AA30" s="72"/>
-      <c r="AB30" s="72"/>
-      <c r="AC30" s="72"/>
-      <c r="AD30" s="72"/>
-      <c r="AE30" s="72"/>
-      <c r="AF30" s="72"/>
-      <c r="AG30" s="72"/>
-      <c r="AH30" s="72"/>
-      <c r="AI30" s="72"/>
-      <c r="AJ30" s="72"/>
-      <c r="AK30" s="72"/>
-      <c r="AL30" s="72"/>
-      <c r="AM30" s="72"/>
-      <c r="AN30" s="72"/>
-      <c r="AO30" s="73"/>
-    </row>
-    <row r="31" spans="1:41" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="71" t="s">
+      <c r="B30" s="57"/>
+      <c r="C30" s="57"/>
+      <c r="D30" s="57"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="57"/>
+      <c r="L30" s="57"/>
+      <c r="M30" s="57"/>
+      <c r="N30" s="57"/>
+      <c r="O30" s="57"/>
+      <c r="P30" s="57"/>
+      <c r="Q30" s="57"/>
+      <c r="R30" s="57"/>
+      <c r="S30" s="57"/>
+      <c r="T30" s="57"/>
+      <c r="U30" s="57"/>
+      <c r="V30" s="58"/>
+      <c r="W30" s="56"/>
+      <c r="X30" s="57"/>
+      <c r="Y30" s="57"/>
+      <c r="Z30" s="57"/>
+      <c r="AA30" s="57"/>
+      <c r="AB30" s="57"/>
+      <c r="AC30" s="57"/>
+      <c r="AD30" s="57"/>
+      <c r="AE30" s="57"/>
+      <c r="AF30" s="57"/>
+      <c r="AG30" s="57"/>
+      <c r="AH30" s="57"/>
+      <c r="AI30" s="57"/>
+      <c r="AJ30" s="57"/>
+      <c r="AK30" s="57"/>
+      <c r="AL30" s="57"/>
+      <c r="AM30" s="57"/>
+      <c r="AN30" s="57"/>
+      <c r="AO30" s="58"/>
+    </row>
+    <row r="31" spans="1:41" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="72"/>
-      <c r="C31" s="72"/>
-      <c r="D31" s="72"/>
-      <c r="E31" s="72"/>
-      <c r="F31" s="72"/>
-      <c r="G31" s="72"/>
-      <c r="H31" s="72"/>
-      <c r="I31" s="72"/>
-      <c r="J31" s="72"/>
-      <c r="K31" s="72"/>
-      <c r="L31" s="72"/>
-      <c r="M31" s="72"/>
-      <c r="N31" s="72"/>
-      <c r="O31" s="72"/>
-      <c r="P31" s="72"/>
-      <c r="Q31" s="72"/>
-      <c r="R31" s="72"/>
-      <c r="S31" s="72"/>
-      <c r="T31" s="72"/>
-      <c r="U31" s="72"/>
-      <c r="V31" s="73"/>
-      <c r="W31" s="71"/>
-      <c r="X31" s="72"/>
-      <c r="Y31" s="72"/>
-      <c r="Z31" s="72"/>
-      <c r="AA31" s="72"/>
-      <c r="AB31" s="72"/>
-      <c r="AC31" s="72"/>
-      <c r="AD31" s="72"/>
-      <c r="AE31" s="72"/>
-      <c r="AF31" s="72"/>
-      <c r="AG31" s="72"/>
-      <c r="AH31" s="72"/>
-      <c r="AI31" s="72"/>
-      <c r="AJ31" s="72"/>
-      <c r="AK31" s="72"/>
-      <c r="AL31" s="72"/>
-      <c r="AM31" s="72"/>
-      <c r="AN31" s="72"/>
-      <c r="AO31" s="73"/>
-    </row>
-    <row r="32" spans="1:41" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="74" t="s">
+      <c r="B31" s="57"/>
+      <c r="C31" s="57"/>
+      <c r="D31" s="57"/>
+      <c r="E31" s="57"/>
+      <c r="F31" s="57"/>
+      <c r="G31" s="57"/>
+      <c r="H31" s="57"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="57"/>
+      <c r="K31" s="57"/>
+      <c r="L31" s="57"/>
+      <c r="M31" s="57"/>
+      <c r="N31" s="57"/>
+      <c r="O31" s="57"/>
+      <c r="P31" s="57"/>
+      <c r="Q31" s="57"/>
+      <c r="R31" s="57"/>
+      <c r="S31" s="57"/>
+      <c r="T31" s="57"/>
+      <c r="U31" s="57"/>
+      <c r="V31" s="58"/>
+      <c r="W31" s="56"/>
+      <c r="X31" s="57"/>
+      <c r="Y31" s="57"/>
+      <c r="Z31" s="57"/>
+      <c r="AA31" s="57"/>
+      <c r="AB31" s="57"/>
+      <c r="AC31" s="57"/>
+      <c r="AD31" s="57"/>
+      <c r="AE31" s="57"/>
+      <c r="AF31" s="57"/>
+      <c r="AG31" s="57"/>
+      <c r="AH31" s="57"/>
+      <c r="AI31" s="57"/>
+      <c r="AJ31" s="57"/>
+      <c r="AK31" s="57"/>
+      <c r="AL31" s="57"/>
+      <c r="AM31" s="57"/>
+      <c r="AN31" s="57"/>
+      <c r="AO31" s="58"/>
+    </row>
+    <row r="32" spans="1:41" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="B32" s="75"/>
-      <c r="C32" s="75"/>
-      <c r="D32" s="75"/>
-      <c r="E32" s="75"/>
-      <c r="F32" s="75"/>
-      <c r="G32" s="75"/>
-      <c r="H32" s="75"/>
-      <c r="I32" s="75"/>
-      <c r="J32" s="75"/>
-      <c r="K32" s="75"/>
-      <c r="L32" s="75"/>
-      <c r="M32" s="75"/>
-      <c r="N32" s="75"/>
-      <c r="O32" s="75"/>
-      <c r="P32" s="75"/>
-      <c r="Q32" s="75"/>
-      <c r="R32" s="75"/>
-      <c r="S32" s="75"/>
-      <c r="T32" s="75"/>
-      <c r="U32" s="75"/>
-      <c r="V32" s="76"/>
-      <c r="W32" s="71" t="s">
+      <c r="B32" s="60"/>
+      <c r="C32" s="60"/>
+      <c r="D32" s="60"/>
+      <c r="E32" s="60"/>
+      <c r="F32" s="60"/>
+      <c r="G32" s="60"/>
+      <c r="H32" s="60"/>
+      <c r="I32" s="60"/>
+      <c r="J32" s="60"/>
+      <c r="K32" s="60"/>
+      <c r="L32" s="60"/>
+      <c r="M32" s="60"/>
+      <c r="N32" s="60"/>
+      <c r="O32" s="60"/>
+      <c r="P32" s="60"/>
+      <c r="Q32" s="60"/>
+      <c r="R32" s="60"/>
+      <c r="S32" s="60"/>
+      <c r="T32" s="60"/>
+      <c r="U32" s="60"/>
+      <c r="V32" s="61"/>
+      <c r="W32" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="X32" s="72"/>
-      <c r="Y32" s="72"/>
-      <c r="Z32" s="72"/>
-      <c r="AA32" s="72"/>
-      <c r="AB32" s="72"/>
-      <c r="AC32" s="72"/>
-      <c r="AD32" s="72"/>
-      <c r="AE32" s="72"/>
-      <c r="AF32" s="72"/>
-      <c r="AG32" s="72"/>
-      <c r="AH32" s="72"/>
-      <c r="AI32" s="72"/>
-      <c r="AJ32" s="72"/>
-      <c r="AK32" s="72"/>
-      <c r="AL32" s="72"/>
-      <c r="AM32" s="72"/>
-      <c r="AN32" s="72"/>
-      <c r="AO32" s="73"/>
+      <c r="X32" s="57"/>
+      <c r="Y32" s="57"/>
+      <c r="Z32" s="57"/>
+      <c r="AA32" s="57"/>
+      <c r="AB32" s="57"/>
+      <c r="AC32" s="57"/>
+      <c r="AD32" s="57"/>
+      <c r="AE32" s="57"/>
+      <c r="AF32" s="57"/>
+      <c r="AG32" s="57"/>
+      <c r="AH32" s="57"/>
+      <c r="AI32" s="57"/>
+      <c r="AJ32" s="57"/>
+      <c r="AK32" s="57"/>
+      <c r="AL32" s="57"/>
+      <c r="AM32" s="57"/>
+      <c r="AN32" s="57"/>
+      <c r="AO32" s="58"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B12:C17">
     <sortCondition ref="C12:C17"/>
   </sortState>
   <mergeCells count="26">
-    <mergeCell ref="W29:AO29"/>
-    <mergeCell ref="W30:AO30"/>
-    <mergeCell ref="W31:AO31"/>
-    <mergeCell ref="W32:AO32"/>
-    <mergeCell ref="A29:V29"/>
-    <mergeCell ref="A30:V30"/>
-    <mergeCell ref="A31:V31"/>
-    <mergeCell ref="A32:V32"/>
+    <mergeCell ref="A1:AO1"/>
+    <mergeCell ref="A2:AO2"/>
+    <mergeCell ref="A3:AO3"/>
+    <mergeCell ref="A4:AO4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="G6:L6"/>
     <mergeCell ref="G7:AO7"/>
     <mergeCell ref="J10:AO10"/>
     <mergeCell ref="U6:AF6"/>
@@ -5018,13 +5203,14 @@
     <mergeCell ref="D8:AO8"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="M6:T6"/>
-    <mergeCell ref="A1:AO1"/>
-    <mergeCell ref="A2:AO2"/>
-    <mergeCell ref="A3:AO3"/>
-    <mergeCell ref="A4:AO4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="G6:L6"/>
+    <mergeCell ref="W29:AO29"/>
+    <mergeCell ref="W30:AO30"/>
+    <mergeCell ref="W31:AO31"/>
+    <mergeCell ref="W32:AO32"/>
+    <mergeCell ref="A29:V29"/>
+    <mergeCell ref="A30:V30"/>
+    <mergeCell ref="A31:V31"/>
+    <mergeCell ref="A32:V32"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.11811023622047245" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="54" orientation="portrait" r:id="rId1"/>

--- a/Calificaciones.xlsx
+++ b/Calificaciones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Intro-python-cientifico-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F14846A0-69D2-4CBA-80F8-80BEDF5601E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6167ADC5-76AD-41A8-8C54-777E293155E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="6060" windowWidth="26310" windowHeight="13785" xr2:uid="{CE0BC579-6CE5-40D7-ACC9-BFD6CA7E6FB4}"/>
+    <workbookView xWindow="14685" yWindow="5970" windowWidth="26310" windowHeight="13785" xr2:uid="{CE0BC579-6CE5-40D7-ACC9-BFD6CA7E6FB4}"/>
   </bookViews>
   <sheets>
     <sheet name="ACTA CALIFICACIONES" sheetId="2" r:id="rId1"/>
@@ -19,19 +19,10 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">ASISTENCIA!$A$10:$AO$24</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -252,10 +243,10 @@
     <t>E_total</t>
   </si>
   <si>
-    <t>ESPINOSA CUELLAR JOSE SAMUEL</t>
-  </si>
-  <si>
     <t>HERNANDEZ JOSUE ANDRADE</t>
+  </si>
+  <si>
+    <t>ESPINOSA CUELLAR JOSUE SAMUEL</t>
   </si>
 </sst>
 </file>
@@ -607,6 +598,72 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -619,70 +676,49 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -701,51 +737,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1966,32 +1957,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
-      <c r="T1" s="34"/>
-      <c r="U1" s="34"/>
-      <c r="V1" s="34"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="34"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="35"/>
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
@@ -2008,32 +1999,32 @@
       <c r="AL1" s="1"/>
     </row>
     <row r="2" spans="1:38" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
-      <c r="N2" s="34"/>
-      <c r="O2" s="34"/>
-      <c r="P2" s="34"/>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
-      <c r="T2" s="34"/>
-      <c r="U2" s="34"/>
-      <c r="V2" s="34"/>
-      <c r="W2" s="34"/>
-      <c r="X2" s="34"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="35"/>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
       <c r="AA2" s="1"/>
@@ -2050,32 +2041,32 @@
       <c r="AL2" s="1"/>
     </row>
     <row r="3" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="35"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35"/>
-      <c r="N3" s="35"/>
-      <c r="O3" s="35"/>
-      <c r="P3" s="35"/>
-      <c r="Q3" s="35"/>
-      <c r="R3" s="35"/>
-      <c r="S3" s="35"/>
-      <c r="T3" s="35"/>
-      <c r="U3" s="35"/>
-      <c r="V3" s="35"/>
-      <c r="W3" s="35"/>
-      <c r="X3" s="35"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="36"/>
+      <c r="M3" s="36"/>
+      <c r="N3" s="36"/>
+      <c r="O3" s="36"/>
+      <c r="P3" s="36"/>
+      <c r="Q3" s="36"/>
+      <c r="R3" s="36"/>
+      <c r="S3" s="36"/>
+      <c r="T3" s="36"/>
+      <c r="U3" s="36"/>
+      <c r="V3" s="36"/>
+      <c r="W3" s="36"/>
+      <c r="X3" s="36"/>
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
       <c r="AA3" s="3"/>
@@ -2092,32 +2083,32 @@
       <c r="AL3" s="3"/>
     </row>
     <row r="4" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="35"/>
-      <c r="M4" s="35"/>
-      <c r="N4" s="35"/>
-      <c r="O4" s="35"/>
-      <c r="P4" s="35"/>
-      <c r="Q4" s="35"/>
-      <c r="R4" s="35"/>
-      <c r="S4" s="35"/>
-      <c r="T4" s="35"/>
-      <c r="U4" s="35"/>
-      <c r="V4" s="35"/>
-      <c r="W4" s="35"/>
-      <c r="X4" s="35"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="36"/>
+      <c r="T4" s="36"/>
+      <c r="U4" s="36"/>
+      <c r="V4" s="36"/>
+      <c r="W4" s="36"/>
+      <c r="X4" s="36"/>
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
       <c r="AA4" s="3"/>
@@ -2174,24 +2165,24 @@
       <c r="AL5" s="3"/>
     </row>
     <row r="6" spans="1:38" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="37"/>
-      <c r="C6" s="38" t="s">
+      <c r="B6" s="38"/>
+      <c r="C6" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="41" t="s">
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="H6" s="41"/>
-      <c r="I6" s="42" t="s">
+      <c r="H6" s="42"/>
+      <c r="I6" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="J6" s="43"/>
+      <c r="J6" s="44"/>
       <c r="K6" s="29"/>
       <c r="L6" s="29"/>
       <c r="M6" s="29"/>
@@ -2209,41 +2200,41 @@
       <c r="Y6" s="5"/>
     </row>
     <row r="7" spans="1:38" ht="29.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="45" t="s">
+      <c r="B7" s="45"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
-      <c r="K7" s="45"/>
-      <c r="L7" s="45"/>
-      <c r="M7" s="45"/>
-      <c r="N7" s="45"/>
-      <c r="O7" s="45"/>
-      <c r="P7" s="45"/>
-      <c r="Q7" s="45"/>
-      <c r="R7" s="45"/>
-      <c r="S7" s="45"/>
-      <c r="T7" s="45"/>
-      <c r="U7" s="45"/>
-      <c r="V7" s="45"/>
-      <c r="W7" s="45"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="30"/>
+      <c r="Q7" s="30"/>
+      <c r="R7" s="30"/>
+      <c r="S7" s="30"/>
+      <c r="T7" s="30"/>
+      <c r="U7" s="30"/>
+      <c r="V7" s="30"/>
+      <c r="W7" s="30"/>
       <c r="X7" s="46"/>
     </row>
     <row r="8" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="44"/>
-      <c r="C8" s="44"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
       <c r="D8" s="47" t="s">
         <v>29</v>
       </c>
@@ -2289,23 +2280,23 @@
       <c r="I10" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J10" s="30" t="s">
+      <c r="J10" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="31"/>
-      <c r="N10" s="31"/>
-      <c r="O10" s="31"/>
-      <c r="P10" s="31"/>
-      <c r="Q10" s="31"/>
-      <c r="R10" s="31"/>
-      <c r="S10" s="31"/>
-      <c r="T10" s="31"/>
-      <c r="U10" s="31"/>
-      <c r="V10" s="31"/>
-      <c r="W10" s="31"/>
-      <c r="X10" s="32"/>
+      <c r="K10" s="53"/>
+      <c r="L10" s="53"/>
+      <c r="M10" s="53"/>
+      <c r="N10" s="53"/>
+      <c r="O10" s="53"/>
+      <c r="P10" s="53"/>
+      <c r="Q10" s="53"/>
+      <c r="R10" s="53"/>
+      <c r="S10" s="53"/>
+      <c r="T10" s="53"/>
+      <c r="U10" s="53"/>
+      <c r="V10" s="53"/>
+      <c r="W10" s="53"/>
+      <c r="X10" s="54"/>
     </row>
     <row r="11" spans="1:38" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="50"/>
@@ -2361,7 +2352,7 @@
       <c r="W11" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="X11" s="33"/>
+      <c r="X11" s="55"/>
     </row>
     <row r="12" spans="1:38" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
@@ -2393,13 +2384,19 @@
       <c r="M12" s="24">
         <v>10</v>
       </c>
-      <c r="N12" s="24"/>
-      <c r="O12" s="24"/>
+      <c r="N12" s="24">
+        <v>0</v>
+      </c>
+      <c r="O12" s="24">
+        <v>0</v>
+      </c>
       <c r="P12" s="24"/>
       <c r="Q12" s="24"/>
       <c r="R12" s="24"/>
       <c r="S12" s="24"/>
-      <c r="T12" s="24"/>
+      <c r="T12" s="24">
+        <v>9</v>
+      </c>
       <c r="U12" s="24"/>
       <c r="V12" s="24"/>
       <c r="W12" s="24"/>
@@ -2435,13 +2432,19 @@
       <c r="M13" s="24">
         <v>10</v>
       </c>
-      <c r="N13" s="24"/>
-      <c r="O13" s="24"/>
+      <c r="N13" s="24">
+        <v>10</v>
+      </c>
+      <c r="O13" s="24">
+        <v>10</v>
+      </c>
       <c r="P13" s="24"/>
       <c r="Q13" s="24"/>
       <c r="R13" s="24"/>
       <c r="S13" s="24"/>
-      <c r="T13" s="24"/>
+      <c r="T13" s="24">
+        <v>10</v>
+      </c>
       <c r="U13" s="24"/>
       <c r="V13" s="24"/>
       <c r="W13" s="24"/>
@@ -2475,13 +2478,19 @@
       <c r="M14" s="24">
         <v>8</v>
       </c>
-      <c r="N14" s="24"/>
-      <c r="O14" s="24"/>
+      <c r="N14" s="24">
+        <v>5</v>
+      </c>
+      <c r="O14" s="24">
+        <v>6</v>
+      </c>
       <c r="P14" s="24"/>
       <c r="Q14" s="24"/>
       <c r="R14" s="24"/>
       <c r="S14" s="24"/>
-      <c r="T14" s="24"/>
+      <c r="T14" s="24">
+        <v>10</v>
+      </c>
       <c r="U14" s="24"/>
       <c r="V14" s="24"/>
       <c r="W14" s="24"/>
@@ -2517,13 +2526,19 @@
       <c r="M15" s="24">
         <v>10</v>
       </c>
-      <c r="N15" s="24"/>
-      <c r="O15" s="24"/>
+      <c r="N15" s="24">
+        <v>9</v>
+      </c>
+      <c r="O15" s="24">
+        <v>9</v>
+      </c>
       <c r="P15" s="24"/>
       <c r="Q15" s="24"/>
       <c r="R15" s="24"/>
       <c r="S15" s="24"/>
-      <c r="T15" s="24"/>
+      <c r="T15" s="24">
+        <v>10</v>
+      </c>
       <c r="U15" s="24"/>
       <c r="V15" s="24"/>
       <c r="W15" s="24"/>
@@ -2559,13 +2574,19 @@
       <c r="M16" s="24">
         <v>10</v>
       </c>
-      <c r="N16" s="24"/>
-      <c r="O16" s="24"/>
+      <c r="N16" s="24">
+        <v>7</v>
+      </c>
+      <c r="O16" s="24">
+        <v>9</v>
+      </c>
       <c r="P16" s="24"/>
       <c r="Q16" s="24"/>
       <c r="R16" s="24"/>
       <c r="S16" s="24"/>
-      <c r="T16" s="24"/>
+      <c r="T16" s="24">
+        <v>10</v>
+      </c>
       <c r="U16" s="24"/>
       <c r="V16" s="24"/>
       <c r="W16" s="24"/>
@@ -2601,13 +2622,19 @@
       <c r="M17" s="24">
         <v>8</v>
       </c>
-      <c r="N17" s="24"/>
-      <c r="O17" s="24"/>
+      <c r="N17" s="24">
+        <v>7</v>
+      </c>
+      <c r="O17" s="24">
+        <v>5</v>
+      </c>
       <c r="P17" s="24"/>
       <c r="Q17" s="24"/>
       <c r="R17" s="24"/>
       <c r="S17" s="24"/>
-      <c r="T17" s="24"/>
+      <c r="T17" s="24">
+        <v>9</v>
+      </c>
       <c r="U17" s="24"/>
       <c r="V17" s="24"/>
       <c r="W17" s="24"/>
@@ -2643,13 +2670,19 @@
       <c r="M18" s="24">
         <v>10</v>
       </c>
-      <c r="N18" s="24"/>
-      <c r="O18" s="24"/>
+      <c r="N18" s="24">
+        <v>10</v>
+      </c>
+      <c r="O18" s="24">
+        <v>10</v>
+      </c>
       <c r="P18" s="24"/>
       <c r="Q18" s="24"/>
       <c r="R18" s="24"/>
       <c r="S18" s="24"/>
-      <c r="T18" s="24"/>
+      <c r="T18" s="24">
+        <v>9</v>
+      </c>
       <c r="U18" s="24"/>
       <c r="V18" s="24"/>
       <c r="W18" s="24"/>
@@ -2685,13 +2718,19 @@
       <c r="M19" s="24">
         <v>8</v>
       </c>
-      <c r="N19" s="24"/>
-      <c r="O19" s="24"/>
+      <c r="N19" s="24">
+        <v>10</v>
+      </c>
+      <c r="O19" s="24">
+        <v>10</v>
+      </c>
       <c r="P19" s="24"/>
       <c r="Q19" s="24"/>
       <c r="R19" s="24"/>
       <c r="S19" s="24"/>
-      <c r="T19" s="24"/>
+      <c r="T19" s="24">
+        <v>10</v>
+      </c>
       <c r="U19" s="24"/>
       <c r="V19" s="24"/>
       <c r="W19" s="24"/>
@@ -2727,13 +2766,19 @@
       <c r="M20" s="24">
         <v>8</v>
       </c>
-      <c r="N20" s="24"/>
-      <c r="O20" s="24"/>
+      <c r="N20" s="24">
+        <v>10</v>
+      </c>
+      <c r="O20" s="24">
+        <v>10</v>
+      </c>
       <c r="P20" s="24"/>
       <c r="Q20" s="24"/>
       <c r="R20" s="24"/>
       <c r="S20" s="24"/>
-      <c r="T20" s="24"/>
+      <c r="T20" s="24">
+        <v>10</v>
+      </c>
       <c r="U20" s="24"/>
       <c r="V20" s="24"/>
       <c r="W20" s="24"/>
@@ -2769,13 +2814,19 @@
       <c r="M21" s="24">
         <v>10</v>
       </c>
-      <c r="N21" s="24"/>
-      <c r="O21" s="24"/>
+      <c r="N21" s="24">
+        <v>10</v>
+      </c>
+      <c r="O21" s="24">
+        <v>10</v>
+      </c>
       <c r="P21" s="24"/>
       <c r="Q21" s="24"/>
       <c r="R21" s="24"/>
       <c r="S21" s="24"/>
-      <c r="T21" s="24"/>
+      <c r="T21" s="24">
+        <v>10</v>
+      </c>
       <c r="U21" s="24"/>
       <c r="V21" s="24"/>
       <c r="W21" s="24"/>
@@ -2811,13 +2862,19 @@
       <c r="M22" s="24">
         <v>8</v>
       </c>
-      <c r="N22" s="24"/>
-      <c r="O22" s="24"/>
+      <c r="N22" s="24">
+        <v>10</v>
+      </c>
+      <c r="O22" s="24">
+        <v>10</v>
+      </c>
       <c r="P22" s="24"/>
       <c r="Q22" s="24"/>
       <c r="R22" s="24"/>
       <c r="S22" s="24"/>
-      <c r="T22" s="24"/>
+      <c r="T22" s="24">
+        <v>10</v>
+      </c>
       <c r="U22" s="24"/>
       <c r="V22" s="24"/>
       <c r="W22" s="24"/>
@@ -2853,13 +2910,19 @@
       <c r="M23" s="24">
         <v>10</v>
       </c>
-      <c r="N23" s="24"/>
-      <c r="O23" s="24"/>
+      <c r="N23" s="24">
+        <v>10</v>
+      </c>
+      <c r="O23" s="24">
+        <v>9</v>
+      </c>
       <c r="P23" s="24"/>
       <c r="Q23" s="24"/>
       <c r="R23" s="24"/>
       <c r="S23" s="24"/>
-      <c r="T23" s="24"/>
+      <c r="T23" s="24">
+        <v>10</v>
+      </c>
       <c r="U23" s="24"/>
       <c r="V23" s="24"/>
       <c r="W23" s="24"/>
@@ -2895,13 +2958,19 @@
       <c r="M24" s="24">
         <v>8</v>
       </c>
-      <c r="N24" s="24"/>
-      <c r="O24" s="24"/>
+      <c r="N24" s="24">
+        <v>4</v>
+      </c>
+      <c r="O24" s="24">
+        <v>5</v>
+      </c>
       <c r="P24" s="24"/>
       <c r="Q24" s="24"/>
       <c r="R24" s="24"/>
       <c r="S24" s="24"/>
-      <c r="T24" s="24"/>
+      <c r="T24" s="24">
+        <v>10</v>
+      </c>
       <c r="U24" s="24"/>
       <c r="V24" s="24"/>
       <c r="W24" s="24"/>
@@ -2913,7 +2982,7 @@
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
@@ -2935,13 +3004,17 @@
       <c r="M25" s="24">
         <v>10</v>
       </c>
-      <c r="N25" s="24"/>
+      <c r="N25" s="24">
+        <v>10</v>
+      </c>
       <c r="O25" s="24"/>
       <c r="P25" s="24"/>
       <c r="Q25" s="24"/>
       <c r="R25" s="24"/>
       <c r="S25" s="24"/>
-      <c r="T25" s="24"/>
+      <c r="T25" s="24">
+        <v>10</v>
+      </c>
       <c r="U25" s="24"/>
       <c r="V25" s="24"/>
       <c r="W25" s="24"/>
@@ -2953,7 +3026,7 @@
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
@@ -2973,13 +3046,19 @@
       <c r="M26" s="24">
         <v>8</v>
       </c>
-      <c r="N26" s="24"/>
-      <c r="O26" s="24"/>
+      <c r="N26" s="24">
+        <v>4</v>
+      </c>
+      <c r="O26" s="24">
+        <v>7</v>
+      </c>
       <c r="P26" s="24"/>
       <c r="Q26" s="24"/>
       <c r="R26" s="24"/>
       <c r="S26" s="24"/>
-      <c r="T26" s="24"/>
+      <c r="T26" s="24">
+        <v>10</v>
+      </c>
       <c r="U26" s="24"/>
       <c r="V26" s="24"/>
       <c r="W26" s="24"/>
@@ -2999,133 +3078,131 @@
       <c r="B29" s="6"/>
     </row>
     <row r="30" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="52" t="s">
+      <c r="A30" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="B30" s="52"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="52"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="53" t="s">
+      <c r="B30" s="31"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="31"/>
+      <c r="I30" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="J30" s="54"/>
-      <c r="K30" s="54"/>
-      <c r="L30" s="54"/>
-      <c r="M30" s="54"/>
-      <c r="N30" s="54"/>
-      <c r="O30" s="54"/>
-      <c r="P30" s="54"/>
-      <c r="Q30" s="54"/>
-      <c r="R30" s="54"/>
-      <c r="S30" s="54"/>
-      <c r="T30" s="54"/>
-      <c r="U30" s="54"/>
-      <c r="V30" s="54"/>
-      <c r="W30" s="54"/>
-      <c r="X30" s="55"/>
+      <c r="J30" s="33"/>
+      <c r="K30" s="33"/>
+      <c r="L30" s="33"/>
+      <c r="M30" s="33"/>
+      <c r="N30" s="33"/>
+      <c r="O30" s="33"/>
+      <c r="P30" s="33"/>
+      <c r="Q30" s="33"/>
+      <c r="R30" s="33"/>
+      <c r="S30" s="33"/>
+      <c r="T30" s="33"/>
+      <c r="U30" s="33"/>
+      <c r="V30" s="33"/>
+      <c r="W30" s="33"/>
+      <c r="X30" s="34"/>
     </row>
     <row r="31" spans="1:24" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="45" t="s">
+      <c r="A31" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="45"/>
-      <c r="C31" s="45"/>
-      <c r="D31" s="45"/>
-      <c r="E31" s="45"/>
-      <c r="F31" s="45"/>
-      <c r="G31" s="45"/>
-      <c r="H31" s="45"/>
-      <c r="I31" s="45"/>
-      <c r="J31" s="45"/>
-      <c r="K31" s="45"/>
-      <c r="L31" s="45"/>
-      <c r="M31" s="45"/>
-      <c r="N31" s="45"/>
-      <c r="O31" s="45"/>
-      <c r="P31" s="45"/>
-      <c r="Q31" s="45"/>
-      <c r="R31" s="45"/>
-      <c r="S31" s="45"/>
-      <c r="T31" s="45"/>
-      <c r="U31" s="45"/>
-      <c r="V31" s="45"/>
-      <c r="W31" s="45"/>
-      <c r="X31" s="45"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="30"/>
+      <c r="N31" s="30"/>
+      <c r="O31" s="30"/>
+      <c r="P31" s="30"/>
+      <c r="Q31" s="30"/>
+      <c r="R31" s="30"/>
+      <c r="S31" s="30"/>
+      <c r="T31" s="30"/>
+      <c r="U31" s="30"/>
+      <c r="V31" s="30"/>
+      <c r="W31" s="30"/>
+      <c r="X31" s="30"/>
     </row>
     <row r="32" spans="1:24" ht="45.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="45" t="s">
+      <c r="A32" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="45"/>
-      <c r="C32" s="45"/>
-      <c r="D32" s="45"/>
-      <c r="E32" s="45"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="45"/>
-      <c r="H32" s="45"/>
-      <c r="I32" s="45"/>
-      <c r="J32" s="45"/>
-      <c r="K32" s="45"/>
-      <c r="L32" s="45"/>
-      <c r="M32" s="45"/>
-      <c r="N32" s="45"/>
-      <c r="O32" s="45"/>
-      <c r="P32" s="45"/>
-      <c r="Q32" s="45"/>
-      <c r="R32" s="45"/>
-      <c r="S32" s="45"/>
-      <c r="T32" s="45"/>
-      <c r="U32" s="45"/>
-      <c r="V32" s="45"/>
-      <c r="W32" s="45"/>
-      <c r="X32" s="45"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="30"/>
+      <c r="Q32" s="30"/>
+      <c r="R32" s="30"/>
+      <c r="S32" s="30"/>
+      <c r="T32" s="30"/>
+      <c r="U32" s="30"/>
+      <c r="V32" s="30"/>
+      <c r="W32" s="30"/>
+      <c r="X32" s="30"/>
     </row>
     <row r="33" spans="1:24" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="45" t="s">
+      <c r="A33" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="B33" s="45"/>
-      <c r="C33" s="45"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="45"/>
-      <c r="F33" s="45"/>
-      <c r="G33" s="45"/>
-      <c r="H33" s="45"/>
-      <c r="I33" s="45" t="s">
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="J33" s="45"/>
-      <c r="K33" s="45"/>
-      <c r="L33" s="45"/>
-      <c r="M33" s="45"/>
-      <c r="N33" s="45"/>
-      <c r="O33" s="45"/>
-      <c r="P33" s="45"/>
-      <c r="Q33" s="45"/>
-      <c r="R33" s="45"/>
-      <c r="S33" s="45"/>
-      <c r="T33" s="45"/>
-      <c r="U33" s="45"/>
-      <c r="V33" s="45"/>
-      <c r="W33" s="45"/>
-      <c r="X33" s="45"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="30"/>
+      <c r="L33" s="30"/>
+      <c r="M33" s="30"/>
+      <c r="N33" s="30"/>
+      <c r="O33" s="30"/>
+      <c r="P33" s="30"/>
+      <c r="Q33" s="30"/>
+      <c r="R33" s="30"/>
+      <c r="S33" s="30"/>
+      <c r="T33" s="30"/>
+      <c r="U33" s="30"/>
+      <c r="V33" s="30"/>
+      <c r="W33" s="30"/>
+      <c r="X33" s="30"/>
     </row>
     <row r="34" spans="1:24" ht="26.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:X7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:X8"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
     <mergeCell ref="C10:H11"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="I33:X33"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="I30:X30"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="I31:X31"/>
-    <mergeCell ref="A32:H32"/>
-    <mergeCell ref="I32:X32"/>
     <mergeCell ref="J10:W10"/>
     <mergeCell ref="X10:X11"/>
     <mergeCell ref="A1:X1"/>
@@ -3136,12 +3213,14 @@
     <mergeCell ref="C6:F6"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="I6:J6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:X7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:X8"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="I33:X33"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="I30:X30"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="I31:X31"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="I32:X32"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -3798,184 +3877,184 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
-      <c r="T1" s="34"/>
-      <c r="U1" s="34"/>
-      <c r="V1" s="34"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="34"/>
-      <c r="Z1" s="34"/>
-      <c r="AA1" s="34"/>
-      <c r="AB1" s="34"/>
-      <c r="AC1" s="34"/>
-      <c r="AD1" s="34"/>
-      <c r="AE1" s="34"/>
-      <c r="AF1" s="34"/>
-      <c r="AG1" s="34"/>
-      <c r="AH1" s="34"/>
-      <c r="AI1" s="34"/>
-      <c r="AJ1" s="34"/>
-      <c r="AK1" s="34"/>
-      <c r="AL1" s="34"/>
-      <c r="AM1" s="34"/>
-      <c r="AN1" s="34"/>
-      <c r="AO1" s="34"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="35"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="35"/>
+      <c r="AA1" s="35"/>
+      <c r="AB1" s="35"/>
+      <c r="AC1" s="35"/>
+      <c r="AD1" s="35"/>
+      <c r="AE1" s="35"/>
+      <c r="AF1" s="35"/>
+      <c r="AG1" s="35"/>
+      <c r="AH1" s="35"/>
+      <c r="AI1" s="35"/>
+      <c r="AJ1" s="35"/>
+      <c r="AK1" s="35"/>
+      <c r="AL1" s="35"/>
+      <c r="AM1" s="35"/>
+      <c r="AN1" s="35"/>
+      <c r="AO1" s="35"/>
     </row>
     <row r="2" spans="1:41" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
-      <c r="N2" s="34"/>
-      <c r="O2" s="34"/>
-      <c r="P2" s="34"/>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
-      <c r="T2" s="34"/>
-      <c r="U2" s="34"/>
-      <c r="V2" s="34"/>
-      <c r="W2" s="34"/>
-      <c r="X2" s="34"/>
-      <c r="Y2" s="34"/>
-      <c r="Z2" s="34"/>
-      <c r="AA2" s="34"/>
-      <c r="AB2" s="34"/>
-      <c r="AC2" s="34"/>
-      <c r="AD2" s="34"/>
-      <c r="AE2" s="34"/>
-      <c r="AF2" s="34"/>
-      <c r="AG2" s="34"/>
-      <c r="AH2" s="34"/>
-      <c r="AI2" s="34"/>
-      <c r="AJ2" s="34"/>
-      <c r="AK2" s="34"/>
-      <c r="AL2" s="34"/>
-      <c r="AM2" s="34"/>
-      <c r="AN2" s="34"/>
-      <c r="AO2" s="34"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="35"/>
+      <c r="Y2" s="35"/>
+      <c r="Z2" s="35"/>
+      <c r="AA2" s="35"/>
+      <c r="AB2" s="35"/>
+      <c r="AC2" s="35"/>
+      <c r="AD2" s="35"/>
+      <c r="AE2" s="35"/>
+      <c r="AF2" s="35"/>
+      <c r="AG2" s="35"/>
+      <c r="AH2" s="35"/>
+      <c r="AI2" s="35"/>
+      <c r="AJ2" s="35"/>
+      <c r="AK2" s="35"/>
+      <c r="AL2" s="35"/>
+      <c r="AM2" s="35"/>
+      <c r="AN2" s="35"/>
+      <c r="AO2" s="35"/>
     </row>
     <row r="3" spans="1:41" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
-      <c r="M3" s="34"/>
-      <c r="N3" s="34"/>
-      <c r="O3" s="34"/>
-      <c r="P3" s="34"/>
-      <c r="Q3" s="34"/>
-      <c r="R3" s="34"/>
-      <c r="S3" s="34"/>
-      <c r="T3" s="34"/>
-      <c r="U3" s="34"/>
-      <c r="V3" s="34"/>
-      <c r="W3" s="34"/>
-      <c r="X3" s="34"/>
-      <c r="Y3" s="34"/>
-      <c r="Z3" s="34"/>
-      <c r="AA3" s="34"/>
-      <c r="AB3" s="34"/>
-      <c r="AC3" s="34"/>
-      <c r="AD3" s="34"/>
-      <c r="AE3" s="34"/>
-      <c r="AF3" s="34"/>
-      <c r="AG3" s="34"/>
-      <c r="AH3" s="34"/>
-      <c r="AI3" s="34"/>
-      <c r="AJ3" s="34"/>
-      <c r="AK3" s="34"/>
-      <c r="AL3" s="34"/>
-      <c r="AM3" s="34"/>
-      <c r="AN3" s="34"/>
-      <c r="AO3" s="34"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
+      <c r="O3" s="35"/>
+      <c r="P3" s="35"/>
+      <c r="Q3" s="35"/>
+      <c r="R3" s="35"/>
+      <c r="S3" s="35"/>
+      <c r="T3" s="35"/>
+      <c r="U3" s="35"/>
+      <c r="V3" s="35"/>
+      <c r="W3" s="35"/>
+      <c r="X3" s="35"/>
+      <c r="Y3" s="35"/>
+      <c r="Z3" s="35"/>
+      <c r="AA3" s="35"/>
+      <c r="AB3" s="35"/>
+      <c r="AC3" s="35"/>
+      <c r="AD3" s="35"/>
+      <c r="AE3" s="35"/>
+      <c r="AF3" s="35"/>
+      <c r="AG3" s="35"/>
+      <c r="AH3" s="35"/>
+      <c r="AI3" s="35"/>
+      <c r="AJ3" s="35"/>
+      <c r="AK3" s="35"/>
+      <c r="AL3" s="35"/>
+      <c r="AM3" s="35"/>
+      <c r="AN3" s="35"/>
+      <c r="AO3" s="35"/>
     </row>
     <row r="4" spans="1:41" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="34"/>
-      <c r="K4" s="34"/>
-      <c r="L4" s="34"/>
-      <c r="M4" s="34"/>
-      <c r="N4" s="34"/>
-      <c r="O4" s="34"/>
-      <c r="P4" s="34"/>
-      <c r="Q4" s="34"/>
-      <c r="R4" s="34"/>
-      <c r="S4" s="34"/>
-      <c r="T4" s="34"/>
-      <c r="U4" s="34"/>
-      <c r="V4" s="34"/>
-      <c r="W4" s="34"/>
-      <c r="X4" s="34"/>
-      <c r="Y4" s="34"/>
-      <c r="Z4" s="34"/>
-      <c r="AA4" s="34"/>
-      <c r="AB4" s="34"/>
-      <c r="AC4" s="34"/>
-      <c r="AD4" s="34"/>
-      <c r="AE4" s="34"/>
-      <c r="AF4" s="34"/>
-      <c r="AG4" s="34"/>
-      <c r="AH4" s="34"/>
-      <c r="AI4" s="34"/>
-      <c r="AJ4" s="34"/>
-      <c r="AK4" s="34"/>
-      <c r="AL4" s="34"/>
-      <c r="AM4" s="34"/>
-      <c r="AN4" s="34"/>
-      <c r="AO4" s="34"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="35"/>
+      <c r="O4" s="35"/>
+      <c r="P4" s="35"/>
+      <c r="Q4" s="35"/>
+      <c r="R4" s="35"/>
+      <c r="S4" s="35"/>
+      <c r="T4" s="35"/>
+      <c r="U4" s="35"/>
+      <c r="V4" s="35"/>
+      <c r="W4" s="35"/>
+      <c r="X4" s="35"/>
+      <c r="Y4" s="35"/>
+      <c r="Z4" s="35"/>
+      <c r="AA4" s="35"/>
+      <c r="AB4" s="35"/>
+      <c r="AC4" s="35"/>
+      <c r="AD4" s="35"/>
+      <c r="AE4" s="35"/>
+      <c r="AF4" s="35"/>
+      <c r="AG4" s="35"/>
+      <c r="AH4" s="35"/>
+      <c r="AI4" s="35"/>
+      <c r="AJ4" s="35"/>
+      <c r="AK4" s="35"/>
+      <c r="AL4" s="35"/>
+      <c r="AM4" s="35"/>
+      <c r="AN4" s="35"/>
+      <c r="AO4" s="35"/>
     </row>
     <row r="5" spans="1:41" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4"/>
@@ -4008,48 +4087,48 @@
       <c r="AB5" s="3"/>
     </row>
     <row r="6" spans="1:41" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="37"/>
-      <c r="C6" s="67" t="s">
+      <c r="B6" s="38"/>
+      <c r="C6" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="74" t="s">
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
-      <c r="J6" s="75"/>
-      <c r="K6" s="75"/>
-      <c r="L6" s="76"/>
-      <c r="M6" s="38" t="s">
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="60"/>
+      <c r="K6" s="60"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="N6" s="72"/>
-      <c r="O6" s="72"/>
-      <c r="P6" s="72"/>
-      <c r="Q6" s="72"/>
-      <c r="R6" s="72"/>
-      <c r="S6" s="72"/>
-      <c r="T6" s="73"/>
-      <c r="U6" s="32" t="s">
+      <c r="N6" s="69"/>
+      <c r="O6" s="69"/>
+      <c r="P6" s="69"/>
+      <c r="Q6" s="69"/>
+      <c r="R6" s="69"/>
+      <c r="S6" s="69"/>
+      <c r="T6" s="70"/>
+      <c r="U6" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="32"/>
-      <c r="W6" s="32"/>
-      <c r="X6" s="32"/>
-      <c r="Y6" s="32"/>
-      <c r="Z6" s="32"/>
-      <c r="AA6" s="32"/>
-      <c r="AB6" s="32"/>
-      <c r="AC6" s="32"/>
-      <c r="AD6" s="32"/>
-      <c r="AE6" s="32"/>
-      <c r="AF6" s="32"/>
+      <c r="V6" s="54"/>
+      <c r="W6" s="54"/>
+      <c r="X6" s="54"/>
+      <c r="Y6" s="54"/>
+      <c r="Z6" s="54"/>
+      <c r="AA6" s="54"/>
+      <c r="AB6" s="54"/>
+      <c r="AC6" s="54"/>
+      <c r="AD6" s="54"/>
+      <c r="AE6" s="54"/>
+      <c r="AF6" s="54"/>
       <c r="AG6" s="66" t="s">
         <v>27</v>
       </c>
@@ -4063,14 +4142,14 @@
       <c r="AO6" s="66"/>
     </row>
     <row r="7" spans="1:41" ht="29.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="70" t="s">
+      <c r="A7" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="71"/>
-      <c r="C7" s="71"/>
-      <c r="D7" s="71"/>
-      <c r="E7" s="71"/>
-      <c r="F7" s="71"/>
+      <c r="B7" s="68"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
       <c r="G7" s="62" t="s">
         <v>28</v>
       </c>
@@ -4110,51 +4189,51 @@
       <c r="AO7" s="64"/>
     </row>
     <row r="8" spans="1:41" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="44"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="67" t="s">
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
-      <c r="J8" s="68"/>
-      <c r="K8" s="68"/>
-      <c r="L8" s="68"/>
-      <c r="M8" s="68"/>
-      <c r="N8" s="68"/>
-      <c r="O8" s="68"/>
-      <c r="P8" s="68"/>
-      <c r="Q8" s="68"/>
-      <c r="R8" s="68"/>
-      <c r="S8" s="68"/>
-      <c r="T8" s="68"/>
-      <c r="U8" s="68"/>
-      <c r="V8" s="68"/>
-      <c r="W8" s="68"/>
-      <c r="X8" s="68"/>
-      <c r="Y8" s="68"/>
-      <c r="Z8" s="68"/>
-      <c r="AA8" s="68"/>
-      <c r="AB8" s="68"/>
-      <c r="AC8" s="68"/>
-      <c r="AD8" s="68"/>
-      <c r="AE8" s="68"/>
-      <c r="AF8" s="68"/>
-      <c r="AG8" s="68"/>
-      <c r="AH8" s="68"/>
-      <c r="AI8" s="68"/>
-      <c r="AJ8" s="68"/>
-      <c r="AK8" s="68"/>
-      <c r="AL8" s="68"/>
-      <c r="AM8" s="68"/>
-      <c r="AN8" s="68"/>
-      <c r="AO8" s="69"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="57"/>
+      <c r="M8" s="57"/>
+      <c r="N8" s="57"/>
+      <c r="O8" s="57"/>
+      <c r="P8" s="57"/>
+      <c r="Q8" s="57"/>
+      <c r="R8" s="57"/>
+      <c r="S8" s="57"/>
+      <c r="T8" s="57"/>
+      <c r="U8" s="57"/>
+      <c r="V8" s="57"/>
+      <c r="W8" s="57"/>
+      <c r="X8" s="57"/>
+      <c r="Y8" s="57"/>
+      <c r="Z8" s="57"/>
+      <c r="AA8" s="57"/>
+      <c r="AB8" s="57"/>
+      <c r="AC8" s="57"/>
+      <c r="AD8" s="57"/>
+      <c r="AE8" s="57"/>
+      <c r="AF8" s="57"/>
+      <c r="AG8" s="57"/>
+      <c r="AH8" s="57"/>
+      <c r="AI8" s="57"/>
+      <c r="AJ8" s="57"/>
+      <c r="AK8" s="57"/>
+      <c r="AL8" s="57"/>
+      <c r="AM8" s="57"/>
+      <c r="AN8" s="57"/>
+      <c r="AO8" s="58"/>
     </row>
     <row r="9" spans="1:41" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="6"/>
@@ -4177,39 +4256,39 @@
       <c r="I10" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="J10" s="30" t="s">
+      <c r="J10" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="31"/>
-      <c r="N10" s="31"/>
-      <c r="O10" s="31"/>
-      <c r="P10" s="31"/>
-      <c r="Q10" s="31"/>
-      <c r="R10" s="31"/>
-      <c r="S10" s="31"/>
-      <c r="T10" s="31"/>
-      <c r="U10" s="31"/>
-      <c r="V10" s="31"/>
-      <c r="W10" s="31"/>
-      <c r="X10" s="31"/>
-      <c r="Y10" s="31"/>
-      <c r="Z10" s="31"/>
-      <c r="AA10" s="31"/>
-      <c r="AB10" s="31"/>
-      <c r="AC10" s="31"/>
-      <c r="AD10" s="31"/>
-      <c r="AE10" s="31"/>
-      <c r="AF10" s="31"/>
-      <c r="AG10" s="31"/>
-      <c r="AH10" s="31"/>
-      <c r="AI10" s="31"/>
-      <c r="AJ10" s="31"/>
-      <c r="AK10" s="31"/>
-      <c r="AL10" s="31"/>
-      <c r="AM10" s="31"/>
-      <c r="AN10" s="31"/>
+      <c r="K10" s="53"/>
+      <c r="L10" s="53"/>
+      <c r="M10" s="53"/>
+      <c r="N10" s="53"/>
+      <c r="O10" s="53"/>
+      <c r="P10" s="53"/>
+      <c r="Q10" s="53"/>
+      <c r="R10" s="53"/>
+      <c r="S10" s="53"/>
+      <c r="T10" s="53"/>
+      <c r="U10" s="53"/>
+      <c r="V10" s="53"/>
+      <c r="W10" s="53"/>
+      <c r="X10" s="53"/>
+      <c r="Y10" s="53"/>
+      <c r="Z10" s="53"/>
+      <c r="AA10" s="53"/>
+      <c r="AB10" s="53"/>
+      <c r="AC10" s="53"/>
+      <c r="AD10" s="53"/>
+      <c r="AE10" s="53"/>
+      <c r="AF10" s="53"/>
+      <c r="AG10" s="53"/>
+      <c r="AH10" s="53"/>
+      <c r="AI10" s="53"/>
+      <c r="AJ10" s="53"/>
+      <c r="AK10" s="53"/>
+      <c r="AL10" s="53"/>
+      <c r="AM10" s="53"/>
+      <c r="AN10" s="53"/>
       <c r="AO10" s="65"/>
     </row>
     <row r="11" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4997,201 +5076,202 @@
       <c r="B28" s="15"/>
     </row>
     <row r="29" spans="1:41" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="53" t="s">
+      <c r="A29" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="54"/>
-      <c r="C29" s="54"/>
-      <c r="D29" s="54"/>
-      <c r="E29" s="54"/>
-      <c r="F29" s="54"/>
-      <c r="G29" s="54"/>
-      <c r="H29" s="54"/>
-      <c r="I29" s="54"/>
-      <c r="J29" s="54"/>
-      <c r="K29" s="54"/>
-      <c r="L29" s="54"/>
-      <c r="M29" s="54"/>
-      <c r="N29" s="54"/>
-      <c r="O29" s="54"/>
-      <c r="P29" s="54"/>
-      <c r="Q29" s="54"/>
-      <c r="R29" s="54"/>
-      <c r="S29" s="54"/>
-      <c r="T29" s="54"/>
-      <c r="U29" s="54"/>
-      <c r="V29" s="55"/>
-      <c r="W29" s="53" t="s">
+      <c r="B29" s="33"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="33"/>
+      <c r="M29" s="33"/>
+      <c r="N29" s="33"/>
+      <c r="O29" s="33"/>
+      <c r="P29" s="33"/>
+      <c r="Q29" s="33"/>
+      <c r="R29" s="33"/>
+      <c r="S29" s="33"/>
+      <c r="T29" s="33"/>
+      <c r="U29" s="33"/>
+      <c r="V29" s="34"/>
+      <c r="W29" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="X29" s="54"/>
-      <c r="Y29" s="54"/>
-      <c r="Z29" s="54"/>
-      <c r="AA29" s="54"/>
-      <c r="AB29" s="54"/>
-      <c r="AC29" s="54"/>
-      <c r="AD29" s="54"/>
-      <c r="AE29" s="54"/>
-      <c r="AF29" s="54"/>
-      <c r="AG29" s="54"/>
-      <c r="AH29" s="54"/>
-      <c r="AI29" s="54"/>
-      <c r="AJ29" s="54"/>
-      <c r="AK29" s="54"/>
-      <c r="AL29" s="54"/>
-      <c r="AM29" s="54"/>
-      <c r="AN29" s="54"/>
-      <c r="AO29" s="55"/>
+      <c r="X29" s="33"/>
+      <c r="Y29" s="33"/>
+      <c r="Z29" s="33"/>
+      <c r="AA29" s="33"/>
+      <c r="AB29" s="33"/>
+      <c r="AC29" s="33"/>
+      <c r="AD29" s="33"/>
+      <c r="AE29" s="33"/>
+      <c r="AF29" s="33"/>
+      <c r="AG29" s="33"/>
+      <c r="AH29" s="33"/>
+      <c r="AI29" s="33"/>
+      <c r="AJ29" s="33"/>
+      <c r="AK29" s="33"/>
+      <c r="AL29" s="33"/>
+      <c r="AM29" s="33"/>
+      <c r="AN29" s="33"/>
+      <c r="AO29" s="34"/>
     </row>
     <row r="30" spans="1:41" ht="45.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="56" t="s">
+      <c r="A30" s="71" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="57"/>
-      <c r="C30" s="57"/>
-      <c r="D30" s="57"/>
-      <c r="E30" s="57"/>
-      <c r="F30" s="57"/>
-      <c r="G30" s="57"/>
-      <c r="H30" s="57"/>
-      <c r="I30" s="57"/>
-      <c r="J30" s="57"/>
-      <c r="K30" s="57"/>
-      <c r="L30" s="57"/>
-      <c r="M30" s="57"/>
-      <c r="N30" s="57"/>
-      <c r="O30" s="57"/>
-      <c r="P30" s="57"/>
-      <c r="Q30" s="57"/>
-      <c r="R30" s="57"/>
-      <c r="S30" s="57"/>
-      <c r="T30" s="57"/>
-      <c r="U30" s="57"/>
-      <c r="V30" s="58"/>
-      <c r="W30" s="56"/>
-      <c r="X30" s="57"/>
-      <c r="Y30" s="57"/>
-      <c r="Z30" s="57"/>
-      <c r="AA30" s="57"/>
-      <c r="AB30" s="57"/>
-      <c r="AC30" s="57"/>
-      <c r="AD30" s="57"/>
-      <c r="AE30" s="57"/>
-      <c r="AF30" s="57"/>
-      <c r="AG30" s="57"/>
-      <c r="AH30" s="57"/>
-      <c r="AI30" s="57"/>
-      <c r="AJ30" s="57"/>
-      <c r="AK30" s="57"/>
-      <c r="AL30" s="57"/>
-      <c r="AM30" s="57"/>
-      <c r="AN30" s="57"/>
-      <c r="AO30" s="58"/>
+      <c r="B30" s="72"/>
+      <c r="C30" s="72"/>
+      <c r="D30" s="72"/>
+      <c r="E30" s="72"/>
+      <c r="F30" s="72"/>
+      <c r="G30" s="72"/>
+      <c r="H30" s="72"/>
+      <c r="I30" s="72"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="72"/>
+      <c r="M30" s="72"/>
+      <c r="N30" s="72"/>
+      <c r="O30" s="72"/>
+      <c r="P30" s="72"/>
+      <c r="Q30" s="72"/>
+      <c r="R30" s="72"/>
+      <c r="S30" s="72"/>
+      <c r="T30" s="72"/>
+      <c r="U30" s="72"/>
+      <c r="V30" s="73"/>
+      <c r="W30" s="71"/>
+      <c r="X30" s="72"/>
+      <c r="Y30" s="72"/>
+      <c r="Z30" s="72"/>
+      <c r="AA30" s="72"/>
+      <c r="AB30" s="72"/>
+      <c r="AC30" s="72"/>
+      <c r="AD30" s="72"/>
+      <c r="AE30" s="72"/>
+      <c r="AF30" s="72"/>
+      <c r="AG30" s="72"/>
+      <c r="AH30" s="72"/>
+      <c r="AI30" s="72"/>
+      <c r="AJ30" s="72"/>
+      <c r="AK30" s="72"/>
+      <c r="AL30" s="72"/>
+      <c r="AM30" s="72"/>
+      <c r="AN30" s="72"/>
+      <c r="AO30" s="73"/>
     </row>
     <row r="31" spans="1:41" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="56" t="s">
+      <c r="A31" s="71" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="57"/>
-      <c r="C31" s="57"/>
-      <c r="D31" s="57"/>
-      <c r="E31" s="57"/>
-      <c r="F31" s="57"/>
-      <c r="G31" s="57"/>
-      <c r="H31" s="57"/>
-      <c r="I31" s="57"/>
-      <c r="J31" s="57"/>
-      <c r="K31" s="57"/>
-      <c r="L31" s="57"/>
-      <c r="M31" s="57"/>
-      <c r="N31" s="57"/>
-      <c r="O31" s="57"/>
-      <c r="P31" s="57"/>
-      <c r="Q31" s="57"/>
-      <c r="R31" s="57"/>
-      <c r="S31" s="57"/>
-      <c r="T31" s="57"/>
-      <c r="U31" s="57"/>
-      <c r="V31" s="58"/>
-      <c r="W31" s="56"/>
-      <c r="X31" s="57"/>
-      <c r="Y31" s="57"/>
-      <c r="Z31" s="57"/>
-      <c r="AA31" s="57"/>
-      <c r="AB31" s="57"/>
-      <c r="AC31" s="57"/>
-      <c r="AD31" s="57"/>
-      <c r="AE31" s="57"/>
-      <c r="AF31" s="57"/>
-      <c r="AG31" s="57"/>
-      <c r="AH31" s="57"/>
-      <c r="AI31" s="57"/>
-      <c r="AJ31" s="57"/>
-      <c r="AK31" s="57"/>
-      <c r="AL31" s="57"/>
-      <c r="AM31" s="57"/>
-      <c r="AN31" s="57"/>
-      <c r="AO31" s="58"/>
+      <c r="B31" s="72"/>
+      <c r="C31" s="72"/>
+      <c r="D31" s="72"/>
+      <c r="E31" s="72"/>
+      <c r="F31" s="72"/>
+      <c r="G31" s="72"/>
+      <c r="H31" s="72"/>
+      <c r="I31" s="72"/>
+      <c r="J31" s="72"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="72"/>
+      <c r="M31" s="72"/>
+      <c r="N31" s="72"/>
+      <c r="O31" s="72"/>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="72"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="72"/>
+      <c r="T31" s="72"/>
+      <c r="U31" s="72"/>
+      <c r="V31" s="73"/>
+      <c r="W31" s="71"/>
+      <c r="X31" s="72"/>
+      <c r="Y31" s="72"/>
+      <c r="Z31" s="72"/>
+      <c r="AA31" s="72"/>
+      <c r="AB31" s="72"/>
+      <c r="AC31" s="72"/>
+      <c r="AD31" s="72"/>
+      <c r="AE31" s="72"/>
+      <c r="AF31" s="72"/>
+      <c r="AG31" s="72"/>
+      <c r="AH31" s="72"/>
+      <c r="AI31" s="72"/>
+      <c r="AJ31" s="72"/>
+      <c r="AK31" s="72"/>
+      <c r="AL31" s="72"/>
+      <c r="AM31" s="72"/>
+      <c r="AN31" s="72"/>
+      <c r="AO31" s="73"/>
     </row>
     <row r="32" spans="1:41" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="59" t="s">
+      <c r="A32" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="B32" s="60"/>
-      <c r="C32" s="60"/>
-      <c r="D32" s="60"/>
-      <c r="E32" s="60"/>
-      <c r="F32" s="60"/>
-      <c r="G32" s="60"/>
-      <c r="H32" s="60"/>
-      <c r="I32" s="60"/>
-      <c r="J32" s="60"/>
-      <c r="K32" s="60"/>
-      <c r="L32" s="60"/>
-      <c r="M32" s="60"/>
-      <c r="N32" s="60"/>
-      <c r="O32" s="60"/>
-      <c r="P32" s="60"/>
-      <c r="Q32" s="60"/>
-      <c r="R32" s="60"/>
-      <c r="S32" s="60"/>
-      <c r="T32" s="60"/>
-      <c r="U32" s="60"/>
-      <c r="V32" s="61"/>
-      <c r="W32" s="56" t="s">
+      <c r="B32" s="75"/>
+      <c r="C32" s="75"/>
+      <c r="D32" s="75"/>
+      <c r="E32" s="75"/>
+      <c r="F32" s="75"/>
+      <c r="G32" s="75"/>
+      <c r="H32" s="75"/>
+      <c r="I32" s="75"/>
+      <c r="J32" s="75"/>
+      <c r="K32" s="75"/>
+      <c r="L32" s="75"/>
+      <c r="M32" s="75"/>
+      <c r="N32" s="75"/>
+      <c r="O32" s="75"/>
+      <c r="P32" s="75"/>
+      <c r="Q32" s="75"/>
+      <c r="R32" s="75"/>
+      <c r="S32" s="75"/>
+      <c r="T32" s="75"/>
+      <c r="U32" s="75"/>
+      <c r="V32" s="76"/>
+      <c r="W32" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="X32" s="57"/>
-      <c r="Y32" s="57"/>
-      <c r="Z32" s="57"/>
-      <c r="AA32" s="57"/>
-      <c r="AB32" s="57"/>
-      <c r="AC32" s="57"/>
-      <c r="AD32" s="57"/>
-      <c r="AE32" s="57"/>
-      <c r="AF32" s="57"/>
-      <c r="AG32" s="57"/>
-      <c r="AH32" s="57"/>
-      <c r="AI32" s="57"/>
-      <c r="AJ32" s="57"/>
-      <c r="AK32" s="57"/>
-      <c r="AL32" s="57"/>
-      <c r="AM32" s="57"/>
-      <c r="AN32" s="57"/>
-      <c r="AO32" s="58"/>
+      <c r="X32" s="72"/>
+      <c r="Y32" s="72"/>
+      <c r="Z32" s="72"/>
+      <c r="AA32" s="72"/>
+      <c r="AB32" s="72"/>
+      <c r="AC32" s="72"/>
+      <c r="AD32" s="72"/>
+      <c r="AE32" s="72"/>
+      <c r="AF32" s="72"/>
+      <c r="AG32" s="72"/>
+      <c r="AH32" s="72"/>
+      <c r="AI32" s="72"/>
+      <c r="AJ32" s="72"/>
+      <c r="AK32" s="72"/>
+      <c r="AL32" s="72"/>
+      <c r="AM32" s="72"/>
+      <c r="AN32" s="72"/>
+      <c r="AO32" s="73"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B12:C17">
     <sortCondition ref="C12:C17"/>
   </sortState>
   <mergeCells count="26">
-    <mergeCell ref="A1:AO1"/>
-    <mergeCell ref="A2:AO2"/>
-    <mergeCell ref="A3:AO3"/>
-    <mergeCell ref="A4:AO4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="G6:L6"/>
+    <mergeCell ref="W29:AO29"/>
+    <mergeCell ref="W30:AO30"/>
+    <mergeCell ref="W31:AO31"/>
+    <mergeCell ref="W32:AO32"/>
+    <mergeCell ref="A29:V29"/>
+    <mergeCell ref="A30:V30"/>
+    <mergeCell ref="A31:V31"/>
+    <mergeCell ref="A32:V32"/>
     <mergeCell ref="G7:AO7"/>
     <mergeCell ref="J10:AO10"/>
     <mergeCell ref="U6:AF6"/>
@@ -5203,14 +5283,13 @@
     <mergeCell ref="D8:AO8"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="M6:T6"/>
-    <mergeCell ref="W29:AO29"/>
-    <mergeCell ref="W30:AO30"/>
-    <mergeCell ref="W31:AO31"/>
-    <mergeCell ref="W32:AO32"/>
-    <mergeCell ref="A29:V29"/>
-    <mergeCell ref="A30:V30"/>
-    <mergeCell ref="A31:V31"/>
-    <mergeCell ref="A32:V32"/>
+    <mergeCell ref="A1:AO1"/>
+    <mergeCell ref="A2:AO2"/>
+    <mergeCell ref="A3:AO3"/>
+    <mergeCell ref="A4:AO4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="G6:L6"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.11811023622047245" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="54" orientation="portrait" r:id="rId1"/>
